--- a/Карина-бот-WhatsApp/google-sheets/Расписание_Октябрь_2026.xlsx
+++ b/Карина-бот-WhatsApp/google-sheets/Расписание_Октябрь_2026.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Как заполнять" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Октябрь 2026'!$A$1:$K$437</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Октябрь 2026'!$A$1:$L$437</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -553,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K437"/>
+  <dimension ref="A1:L437"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -564,9 +564,10 @@
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -612,15 +613,20 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Статус записи</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Создано</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Статус слота</t>
         </is>
@@ -649,10 +655,11 @@
       <c r="F2" s="5" t="n"/>
       <c r="G2" s="6" t="n"/>
       <c r="H2" s="6" t="n"/>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="7" t="n"/>
-      <c r="K2" s="3">
-        <f>IF(OR(E2&lt;&gt;"",I2&lt;&gt;""),"Занято",IF(AND(F1="Повторный приём (1 час)",A1=A2),"Занято","Свободно"))</f>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="7" t="n"/>
+      <c r="L2" s="3">
+        <f>IF(OR(E2&lt;&gt;"",J2&lt;&gt;""),"Занято",IF(AND(F1="Повторный приём (1 час)",A1=A2),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -679,10 +686,11 @@
       <c r="F3" s="11" t="n"/>
       <c r="G3" s="12" t="n"/>
       <c r="H3" s="12" t="n"/>
-      <c r="I3" s="9" t="n"/>
-      <c r="J3" s="13" t="n"/>
-      <c r="K3" s="9">
-        <f>IF(OR(E3&lt;&gt;"",I3&lt;&gt;""),"Занято",IF(AND(F2="Повторный приём (1 час)",A2=A3),"Занято","Свободно"))</f>
+      <c r="I3" s="11" t="n"/>
+      <c r="J3" s="9" t="n"/>
+      <c r="K3" s="13" t="n"/>
+      <c r="L3" s="9">
+        <f>IF(OR(E3&lt;&gt;"",J3&lt;&gt;""),"Занято",IF(AND(F2="Повторный приём (1 час)",A2=A3),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -709,10 +717,11 @@
       <c r="F4" s="11" t="n"/>
       <c r="G4" s="12" t="n"/>
       <c r="H4" s="12" t="n"/>
-      <c r="I4" s="9" t="n"/>
-      <c r="J4" s="13" t="n"/>
-      <c r="K4" s="9">
-        <f>IF(OR(E4&lt;&gt;"",I4&lt;&gt;""),"Занято",IF(AND(F3="Повторный приём (1 час)",A3=A4),"Занято","Свободно"))</f>
+      <c r="I4" s="11" t="n"/>
+      <c r="J4" s="9" t="n"/>
+      <c r="K4" s="13" t="n"/>
+      <c r="L4" s="9">
+        <f>IF(OR(E4&lt;&gt;"",J4&lt;&gt;""),"Занято",IF(AND(F3="Повторный приём (1 час)",A3=A4),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -739,10 +748,11 @@
       <c r="F5" s="11" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
-      <c r="I5" s="9" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="9">
-        <f>IF(OR(E5&lt;&gt;"",I5&lt;&gt;""),"Занято",IF(AND(F4="Повторный приём (1 час)",A4=A5),"Занято","Свободно"))</f>
+      <c r="I5" s="11" t="n"/>
+      <c r="J5" s="9" t="n"/>
+      <c r="K5" s="13" t="n"/>
+      <c r="L5" s="9">
+        <f>IF(OR(E5&lt;&gt;"",J5&lt;&gt;""),"Занято",IF(AND(F4="Повторный приём (1 час)",A4=A5),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -769,10 +779,11 @@
       <c r="F6" s="11" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
-      <c r="I6" s="9" t="n"/>
-      <c r="J6" s="13" t="n"/>
-      <c r="K6" s="9">
-        <f>IF(OR(E6&lt;&gt;"",I6&lt;&gt;""),"Занято",IF(AND(F5="Повторный приём (1 час)",A5=A6),"Занято","Свободно"))</f>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="9" t="n"/>
+      <c r="K6" s="13" t="n"/>
+      <c r="L6" s="9">
+        <f>IF(OR(E6&lt;&gt;"",J6&lt;&gt;""),"Занято",IF(AND(F5="Повторный приём (1 час)",A5=A6),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -799,10 +810,11 @@
       <c r="F7" s="11" t="n"/>
       <c r="G7" s="12" t="n"/>
       <c r="H7" s="12" t="n"/>
-      <c r="I7" s="9" t="n"/>
-      <c r="J7" s="13" t="n"/>
-      <c r="K7" s="9">
-        <f>IF(OR(E7&lt;&gt;"",I7&lt;&gt;""),"Занято",IF(AND(F6="Повторный приём (1 час)",A6=A7),"Занято","Свободно"))</f>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="9" t="n"/>
+      <c r="K7" s="13" t="n"/>
+      <c r="L7" s="9">
+        <f>IF(OR(E7&lt;&gt;"",J7&lt;&gt;""),"Занято",IF(AND(F6="Повторный приём (1 час)",A6=A7),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -829,10 +841,11 @@
       <c r="F8" s="11" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
-      <c r="I8" s="9" t="n"/>
-      <c r="J8" s="13" t="n"/>
-      <c r="K8" s="9">
-        <f>IF(OR(E8&lt;&gt;"",I8&lt;&gt;""),"Занято",IF(AND(F7="Повторный приём (1 час)",A7=A8),"Занято","Свободно"))</f>
+      <c r="I8" s="11" t="n"/>
+      <c r="J8" s="9" t="n"/>
+      <c r="K8" s="13" t="n"/>
+      <c r="L8" s="9">
+        <f>IF(OR(E8&lt;&gt;"",J8&lt;&gt;""),"Занято",IF(AND(F7="Повторный приём (1 час)",A7=A8),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -859,10 +872,11 @@
       <c r="F9" s="11" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
-      <c r="I9" s="9" t="n"/>
-      <c r="J9" s="13" t="n"/>
-      <c r="K9" s="9">
-        <f>IF(OR(E9&lt;&gt;"",I9&lt;&gt;""),"Занято",IF(AND(F8="Повторный приём (1 час)",A8=A9),"Занято","Свободно"))</f>
+      <c r="I9" s="11" t="n"/>
+      <c r="J9" s="9" t="n"/>
+      <c r="K9" s="13" t="n"/>
+      <c r="L9" s="9">
+        <f>IF(OR(E9&lt;&gt;"",J9&lt;&gt;""),"Занято",IF(AND(F8="Повторный приём (1 час)",A8=A9),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -889,10 +903,11 @@
       <c r="F10" s="11" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
-      <c r="I10" s="9" t="n"/>
-      <c r="J10" s="13" t="n"/>
-      <c r="K10" s="9">
-        <f>IF(OR(E10&lt;&gt;"",I10&lt;&gt;""),"Занято",IF(AND(F9="Повторный приём (1 час)",A9=A10),"Занято","Свободно"))</f>
+      <c r="I10" s="11" t="n"/>
+      <c r="J10" s="9" t="n"/>
+      <c r="K10" s="13" t="n"/>
+      <c r="L10" s="9">
+        <f>IF(OR(E10&lt;&gt;"",J10&lt;&gt;""),"Занято",IF(AND(F9="Повторный приём (1 час)",A9=A10),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -919,10 +934,11 @@
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
-      <c r="I11" s="9" t="n"/>
-      <c r="J11" s="13" t="n"/>
-      <c r="K11" s="9">
-        <f>IF(OR(E11&lt;&gt;"",I11&lt;&gt;""),"Занято",IF(AND(F10="Повторный приём (1 час)",A10=A11),"Занято","Свободно"))</f>
+      <c r="I11" s="11" t="n"/>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="13" t="n"/>
+      <c r="L11" s="9">
+        <f>IF(OR(E11&lt;&gt;"",J11&lt;&gt;""),"Занято",IF(AND(F10="Повторный приём (1 час)",A10=A11),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -949,10 +965,11 @@
       <c r="F12" s="11" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="n"/>
-      <c r="I12" s="9" t="n"/>
-      <c r="J12" s="13" t="n"/>
-      <c r="K12" s="9">
-        <f>IF(OR(E12&lt;&gt;"",I12&lt;&gt;""),"Занято",IF(AND(F11="Повторный приём (1 час)",A11=A12),"Занято","Свободно"))</f>
+      <c r="I12" s="11" t="n"/>
+      <c r="J12" s="9" t="n"/>
+      <c r="K12" s="13" t="n"/>
+      <c r="L12" s="9">
+        <f>IF(OR(E12&lt;&gt;"",J12&lt;&gt;""),"Занято",IF(AND(F11="Повторный приём (1 час)",A11=A12),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -979,10 +996,11 @@
       <c r="F13" s="11" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
-      <c r="I13" s="9" t="n"/>
-      <c r="J13" s="13" t="n"/>
-      <c r="K13" s="9">
-        <f>IF(OR(E13&lt;&gt;"",I13&lt;&gt;""),"Занято",IF(AND(F12="Повторный приём (1 час)",A12=A13),"Занято","Свободно"))</f>
+      <c r="I13" s="11" t="n"/>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="13" t="n"/>
+      <c r="L13" s="9">
+        <f>IF(OR(E13&lt;&gt;"",J13&lt;&gt;""),"Занято",IF(AND(F12="Повторный приём (1 час)",A12=A13),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1009,10 +1027,11 @@
       <c r="F14" s="11" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="13" t="n"/>
-      <c r="K14" s="9">
-        <f>IF(OR(E14&lt;&gt;"",I14&lt;&gt;""),"Занято",IF(AND(F13="Повторный приём (1 час)",A13=A14),"Занято","Свободно"))</f>
+      <c r="I14" s="11" t="n"/>
+      <c r="J14" s="9" t="n"/>
+      <c r="K14" s="13" t="n"/>
+      <c r="L14" s="9">
+        <f>IF(OR(E14&lt;&gt;"",J14&lt;&gt;""),"Занято",IF(AND(F13="Повторный приём (1 час)",A13=A14),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1039,10 +1058,11 @@
       <c r="F15" s="11" t="n"/>
       <c r="G15" s="12" t="n"/>
       <c r="H15" s="12" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="13" t="n"/>
-      <c r="K15" s="9">
-        <f>IF(OR(E15&lt;&gt;"",I15&lt;&gt;""),"Занято",IF(AND(F14="Повторный приём (1 час)",A14=A15),"Занято","Свободно"))</f>
+      <c r="I15" s="11" t="n"/>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="13" t="n"/>
+      <c r="L15" s="9">
+        <f>IF(OR(E15&lt;&gt;"",J15&lt;&gt;""),"Занято",IF(AND(F14="Повторный приём (1 час)",A14=A15),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1069,10 +1089,11 @@
       <c r="F16" s="11" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="13" t="n"/>
-      <c r="K16" s="9">
-        <f>IF(OR(E16&lt;&gt;"",I16&lt;&gt;""),"Занято",IF(AND(F15="Повторный приём (1 час)",A15=A16),"Занято","Свободно"))</f>
+      <c r="I16" s="11" t="n"/>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="13" t="n"/>
+      <c r="L16" s="9">
+        <f>IF(OR(E16&lt;&gt;"",J16&lt;&gt;""),"Занято",IF(AND(F15="Повторный приём (1 час)",A15=A16),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1099,10 +1120,11 @@
       <c r="F17" s="11" t="n"/>
       <c r="G17" s="12" t="n"/>
       <c r="H17" s="12" t="n"/>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="13" t="n"/>
-      <c r="K17" s="9">
-        <f>IF(OR(E17&lt;&gt;"",I17&lt;&gt;""),"Занято",IF(AND(F16="Повторный приём (1 час)",A16=A17),"Занято","Свободно"))</f>
+      <c r="I17" s="11" t="n"/>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="13" t="n"/>
+      <c r="L17" s="9">
+        <f>IF(OR(E17&lt;&gt;"",J17&lt;&gt;""),"Занято",IF(AND(F16="Повторный приём (1 час)",A16=A17),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1129,10 +1151,11 @@
       <c r="F18" s="11" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="n"/>
-      <c r="I18" s="9" t="n"/>
-      <c r="J18" s="13" t="n"/>
-      <c r="K18" s="9">
-        <f>IF(OR(E18&lt;&gt;"",I18&lt;&gt;""),"Занято",IF(AND(F17="Повторный приём (1 час)",A17=A18),"Занято","Свободно"))</f>
+      <c r="I18" s="11" t="n"/>
+      <c r="J18" s="9" t="n"/>
+      <c r="K18" s="13" t="n"/>
+      <c r="L18" s="9">
+        <f>IF(OR(E18&lt;&gt;"",J18&lt;&gt;""),"Занято",IF(AND(F17="Повторный приём (1 час)",A17=A18),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1159,10 +1182,11 @@
       <c r="F19" s="11" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
-      <c r="I19" s="9" t="n"/>
-      <c r="J19" s="13" t="n"/>
-      <c r="K19" s="9">
-        <f>IF(OR(E19&lt;&gt;"",I19&lt;&gt;""),"Занято",IF(AND(F18="Повторный приём (1 час)",A18=A19),"Занято","Свободно"))</f>
+      <c r="I19" s="11" t="n"/>
+      <c r="J19" s="9" t="n"/>
+      <c r="K19" s="13" t="n"/>
+      <c r="L19" s="9">
+        <f>IF(OR(E19&lt;&gt;"",J19&lt;&gt;""),"Занято",IF(AND(F18="Повторный приём (1 час)",A18=A19),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1189,10 +1213,11 @@
       <c r="F20" s="17" t="n"/>
       <c r="G20" s="18" t="n"/>
       <c r="H20" s="18" t="n"/>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="19" t="n"/>
-      <c r="K20" s="15">
-        <f>IF(OR(E20&lt;&gt;"",I20&lt;&gt;""),"Занято",IF(AND(F19="Повторный приём (1 час)",A19=A20),"Занято","Свободно"))</f>
+      <c r="I20" s="17" t="n"/>
+      <c r="J20" s="15" t="n"/>
+      <c r="K20" s="19" t="n"/>
+      <c r="L20" s="15">
+        <f>IF(OR(E20&lt;&gt;"",J20&lt;&gt;""),"Занято",IF(AND(F19="Повторный приём (1 час)",A19=A20),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1219,10 +1244,11 @@
       <c r="F21" s="23" t="n"/>
       <c r="G21" s="24" t="n"/>
       <c r="H21" s="24" t="n"/>
-      <c r="I21" s="21" t="n"/>
-      <c r="J21" s="25" t="n"/>
-      <c r="K21" s="21">
-        <f>IF(OR(E21&lt;&gt;"",I21&lt;&gt;""),"Занято",IF(AND(F20="Повторный приём (1 час)",A20=A21),"Занято","Свободно"))</f>
+      <c r="I21" s="23" t="n"/>
+      <c r="J21" s="21" t="n"/>
+      <c r="K21" s="25" t="n"/>
+      <c r="L21" s="21">
+        <f>IF(OR(E21&lt;&gt;"",J21&lt;&gt;""),"Занято",IF(AND(F20="Повторный приём (1 час)",A20=A21),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1249,10 +1275,11 @@
       <c r="F22" s="23" t="n"/>
       <c r="G22" s="24" t="n"/>
       <c r="H22" s="24" t="n"/>
-      <c r="I22" s="21" t="n"/>
-      <c r="J22" s="25" t="n"/>
-      <c r="K22" s="21">
-        <f>IF(OR(E22&lt;&gt;"",I22&lt;&gt;""),"Занято",IF(AND(F21="Повторный приём (1 час)",A21=A22),"Занято","Свободно"))</f>
+      <c r="I22" s="23" t="n"/>
+      <c r="J22" s="21" t="n"/>
+      <c r="K22" s="25" t="n"/>
+      <c r="L22" s="21">
+        <f>IF(OR(E22&lt;&gt;"",J22&lt;&gt;""),"Занято",IF(AND(F21="Повторный приём (1 час)",A21=A22),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1279,10 +1306,11 @@
       <c r="F23" s="23" t="n"/>
       <c r="G23" s="24" t="n"/>
       <c r="H23" s="24" t="n"/>
-      <c r="I23" s="21" t="n"/>
-      <c r="J23" s="25" t="n"/>
-      <c r="K23" s="21">
-        <f>IF(OR(E23&lt;&gt;"",I23&lt;&gt;""),"Занято",IF(AND(F22="Повторный приём (1 час)",A22=A23),"Занято","Свободно"))</f>
+      <c r="I23" s="23" t="n"/>
+      <c r="J23" s="21" t="n"/>
+      <c r="K23" s="25" t="n"/>
+      <c r="L23" s="21">
+        <f>IF(OR(E23&lt;&gt;"",J23&lt;&gt;""),"Занято",IF(AND(F22="Повторный приём (1 час)",A22=A23),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1309,10 +1337,11 @@
       <c r="F24" s="23" t="n"/>
       <c r="G24" s="24" t="n"/>
       <c r="H24" s="24" t="n"/>
-      <c r="I24" s="21" t="n"/>
-      <c r="J24" s="25" t="n"/>
-      <c r="K24" s="21">
-        <f>IF(OR(E24&lt;&gt;"",I24&lt;&gt;""),"Занято",IF(AND(F23="Повторный приём (1 час)",A23=A24),"Занято","Свободно"))</f>
+      <c r="I24" s="23" t="n"/>
+      <c r="J24" s="21" t="n"/>
+      <c r="K24" s="25" t="n"/>
+      <c r="L24" s="21">
+        <f>IF(OR(E24&lt;&gt;"",J24&lt;&gt;""),"Занято",IF(AND(F23="Повторный приём (1 час)",A23=A24),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1339,10 +1368,11 @@
       <c r="F25" s="23" t="n"/>
       <c r="G25" s="24" t="n"/>
       <c r="H25" s="24" t="n"/>
-      <c r="I25" s="21" t="n"/>
-      <c r="J25" s="25" t="n"/>
-      <c r="K25" s="21">
-        <f>IF(OR(E25&lt;&gt;"",I25&lt;&gt;""),"Занято",IF(AND(F24="Повторный приём (1 час)",A24=A25),"Занято","Свободно"))</f>
+      <c r="I25" s="23" t="n"/>
+      <c r="J25" s="21" t="n"/>
+      <c r="K25" s="25" t="n"/>
+      <c r="L25" s="21">
+        <f>IF(OR(E25&lt;&gt;"",J25&lt;&gt;""),"Занято",IF(AND(F24="Повторный приём (1 час)",A24=A25),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1369,10 +1399,11 @@
       <c r="F26" s="23" t="n"/>
       <c r="G26" s="24" t="n"/>
       <c r="H26" s="24" t="n"/>
-      <c r="I26" s="21" t="n"/>
-      <c r="J26" s="25" t="n"/>
-      <c r="K26" s="21">
-        <f>IF(OR(E26&lt;&gt;"",I26&lt;&gt;""),"Занято",IF(AND(F25="Повторный приём (1 час)",A25=A26),"Занято","Свободно"))</f>
+      <c r="I26" s="23" t="n"/>
+      <c r="J26" s="21" t="n"/>
+      <c r="K26" s="25" t="n"/>
+      <c r="L26" s="21">
+        <f>IF(OR(E26&lt;&gt;"",J26&lt;&gt;""),"Занято",IF(AND(F25="Повторный приём (1 час)",A25=A26),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1399,10 +1430,11 @@
       <c r="F27" s="23" t="n"/>
       <c r="G27" s="24" t="n"/>
       <c r="H27" s="24" t="n"/>
-      <c r="I27" s="21" t="n"/>
-      <c r="J27" s="25" t="n"/>
-      <c r="K27" s="21">
-        <f>IF(OR(E27&lt;&gt;"",I27&lt;&gt;""),"Занято",IF(AND(F26="Повторный приём (1 час)",A26=A27),"Занято","Свободно"))</f>
+      <c r="I27" s="23" t="n"/>
+      <c r="J27" s="21" t="n"/>
+      <c r="K27" s="25" t="n"/>
+      <c r="L27" s="21">
+        <f>IF(OR(E27&lt;&gt;"",J27&lt;&gt;""),"Занято",IF(AND(F26="Повторный приём (1 час)",A26=A27),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1429,10 +1461,11 @@
       <c r="F28" s="23" t="n"/>
       <c r="G28" s="24" t="n"/>
       <c r="H28" s="24" t="n"/>
-      <c r="I28" s="21" t="n"/>
-      <c r="J28" s="25" t="n"/>
-      <c r="K28" s="21">
-        <f>IF(OR(E28&lt;&gt;"",I28&lt;&gt;""),"Занято",IF(AND(F27="Повторный приём (1 час)",A27=A28),"Занято","Свободно"))</f>
+      <c r="I28" s="23" t="n"/>
+      <c r="J28" s="21" t="n"/>
+      <c r="K28" s="25" t="n"/>
+      <c r="L28" s="21">
+        <f>IF(OR(E28&lt;&gt;"",J28&lt;&gt;""),"Занято",IF(AND(F27="Повторный приём (1 час)",A27=A28),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1459,10 +1492,11 @@
       <c r="F29" s="23" t="n"/>
       <c r="G29" s="24" t="n"/>
       <c r="H29" s="24" t="n"/>
-      <c r="I29" s="21" t="n"/>
-      <c r="J29" s="25" t="n"/>
-      <c r="K29" s="21">
-        <f>IF(OR(E29&lt;&gt;"",I29&lt;&gt;""),"Занято",IF(AND(F28="Повторный приём (1 час)",A28=A29),"Занято","Свободно"))</f>
+      <c r="I29" s="23" t="n"/>
+      <c r="J29" s="21" t="n"/>
+      <c r="K29" s="25" t="n"/>
+      <c r="L29" s="21">
+        <f>IF(OR(E29&lt;&gt;"",J29&lt;&gt;""),"Занято",IF(AND(F28="Повторный приём (1 час)",A28=A29),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1489,10 +1523,11 @@
       <c r="F30" s="23" t="n"/>
       <c r="G30" s="24" t="n"/>
       <c r="H30" s="24" t="n"/>
-      <c r="I30" s="21" t="n"/>
-      <c r="J30" s="25" t="n"/>
-      <c r="K30" s="21">
-        <f>IF(OR(E30&lt;&gt;"",I30&lt;&gt;""),"Занято",IF(AND(F29="Повторный приём (1 час)",A29=A30),"Занято","Свободно"))</f>
+      <c r="I30" s="23" t="n"/>
+      <c r="J30" s="21" t="n"/>
+      <c r="K30" s="25" t="n"/>
+      <c r="L30" s="21">
+        <f>IF(OR(E30&lt;&gt;"",J30&lt;&gt;""),"Занято",IF(AND(F29="Повторный приём (1 час)",A29=A30),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1519,10 +1554,11 @@
       <c r="F31" s="23" t="n"/>
       <c r="G31" s="24" t="n"/>
       <c r="H31" s="24" t="n"/>
-      <c r="I31" s="21" t="n"/>
-      <c r="J31" s="25" t="n"/>
-      <c r="K31" s="21">
-        <f>IF(OR(E31&lt;&gt;"",I31&lt;&gt;""),"Занято",IF(AND(F30="Повторный приём (1 час)",A30=A31),"Занято","Свободно"))</f>
+      <c r="I31" s="23" t="n"/>
+      <c r="J31" s="21" t="n"/>
+      <c r="K31" s="25" t="n"/>
+      <c r="L31" s="21">
+        <f>IF(OR(E31&lt;&gt;"",J31&lt;&gt;""),"Занято",IF(AND(F30="Повторный приём (1 час)",A30=A31),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1549,10 +1585,11 @@
       <c r="F32" s="23" t="n"/>
       <c r="G32" s="24" t="n"/>
       <c r="H32" s="24" t="n"/>
-      <c r="I32" s="21" t="n"/>
-      <c r="J32" s="25" t="n"/>
-      <c r="K32" s="21">
-        <f>IF(OR(E32&lt;&gt;"",I32&lt;&gt;""),"Занято",IF(AND(F31="Повторный приём (1 час)",A31=A32),"Занято","Свободно"))</f>
+      <c r="I32" s="23" t="n"/>
+      <c r="J32" s="21" t="n"/>
+      <c r="K32" s="25" t="n"/>
+      <c r="L32" s="21">
+        <f>IF(OR(E32&lt;&gt;"",J32&lt;&gt;""),"Занято",IF(AND(F31="Повторный приём (1 час)",A31=A32),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1579,10 +1616,11 @@
       <c r="F33" s="23" t="n"/>
       <c r="G33" s="24" t="n"/>
       <c r="H33" s="24" t="n"/>
-      <c r="I33" s="21" t="n"/>
-      <c r="J33" s="25" t="n"/>
-      <c r="K33" s="21">
-        <f>IF(OR(E33&lt;&gt;"",I33&lt;&gt;""),"Занято",IF(AND(F32="Повторный приём (1 час)",A32=A33),"Занято","Свободно"))</f>
+      <c r="I33" s="23" t="n"/>
+      <c r="J33" s="21" t="n"/>
+      <c r="K33" s="25" t="n"/>
+      <c r="L33" s="21">
+        <f>IF(OR(E33&lt;&gt;"",J33&lt;&gt;""),"Занято",IF(AND(F32="Повторный приём (1 час)",A32=A33),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1609,10 +1647,11 @@
       <c r="F34" s="23" t="n"/>
       <c r="G34" s="24" t="n"/>
       <c r="H34" s="24" t="n"/>
-      <c r="I34" s="21" t="n"/>
-      <c r="J34" s="25" t="n"/>
-      <c r="K34" s="21">
-        <f>IF(OR(E34&lt;&gt;"",I34&lt;&gt;""),"Занято",IF(AND(F33="Повторный приём (1 час)",A33=A34),"Занято","Свободно"))</f>
+      <c r="I34" s="23" t="n"/>
+      <c r="J34" s="21" t="n"/>
+      <c r="K34" s="25" t="n"/>
+      <c r="L34" s="21">
+        <f>IF(OR(E34&lt;&gt;"",J34&lt;&gt;""),"Занято",IF(AND(F33="Повторный приём (1 час)",A33=A34),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1639,10 +1678,11 @@
       <c r="F35" s="23" t="n"/>
       <c r="G35" s="24" t="n"/>
       <c r="H35" s="24" t="n"/>
-      <c r="I35" s="21" t="n"/>
-      <c r="J35" s="25" t="n"/>
-      <c r="K35" s="21">
-        <f>IF(OR(E35&lt;&gt;"",I35&lt;&gt;""),"Занято",IF(AND(F34="Повторный приём (1 час)",A34=A35),"Занято","Свободно"))</f>
+      <c r="I35" s="23" t="n"/>
+      <c r="J35" s="21" t="n"/>
+      <c r="K35" s="25" t="n"/>
+      <c r="L35" s="21">
+        <f>IF(OR(E35&lt;&gt;"",J35&lt;&gt;""),"Занято",IF(AND(F34="Повторный приём (1 час)",A34=A35),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1669,10 +1709,11 @@
       <c r="F36" s="23" t="n"/>
       <c r="G36" s="24" t="n"/>
       <c r="H36" s="24" t="n"/>
-      <c r="I36" s="21" t="n"/>
-      <c r="J36" s="25" t="n"/>
-      <c r="K36" s="21">
-        <f>IF(OR(E36&lt;&gt;"",I36&lt;&gt;""),"Занято",IF(AND(F35="Повторный приём (1 час)",A35=A36),"Занято","Свободно"))</f>
+      <c r="I36" s="23" t="n"/>
+      <c r="J36" s="21" t="n"/>
+      <c r="K36" s="25" t="n"/>
+      <c r="L36" s="21">
+        <f>IF(OR(E36&lt;&gt;"",J36&lt;&gt;""),"Занято",IF(AND(F35="Повторный приём (1 час)",A35=A36),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1699,10 +1740,11 @@
       <c r="F37" s="23" t="n"/>
       <c r="G37" s="24" t="n"/>
       <c r="H37" s="24" t="n"/>
-      <c r="I37" s="21" t="n"/>
-      <c r="J37" s="25" t="n"/>
-      <c r="K37" s="21">
-        <f>IF(OR(E37&lt;&gt;"",I37&lt;&gt;""),"Занято",IF(AND(F36="Повторный приём (1 час)",A36=A37),"Занято","Свободно"))</f>
+      <c r="I37" s="23" t="n"/>
+      <c r="J37" s="21" t="n"/>
+      <c r="K37" s="25" t="n"/>
+      <c r="L37" s="21">
+        <f>IF(OR(E37&lt;&gt;"",J37&lt;&gt;""),"Занято",IF(AND(F36="Повторный приём (1 час)",A36=A37),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1729,10 +1771,11 @@
       <c r="F38" s="5" t="n"/>
       <c r="G38" s="6" t="n"/>
       <c r="H38" s="6" t="n"/>
-      <c r="I38" s="3" t="n"/>
-      <c r="J38" s="7" t="n"/>
-      <c r="K38" s="3">
-        <f>IF(OR(E38&lt;&gt;"",I38&lt;&gt;""),"Занято",IF(AND(F37="Повторный приём (1 час)",A37=A38),"Занято","Свободно"))</f>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="3" t="n"/>
+      <c r="K38" s="7" t="n"/>
+      <c r="L38" s="3">
+        <f>IF(OR(E38&lt;&gt;"",J38&lt;&gt;""),"Занято",IF(AND(F37="Повторный приём (1 час)",A37=A38),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1759,10 +1802,11 @@
       <c r="F39" s="11" t="n"/>
       <c r="G39" s="12" t="n"/>
       <c r="H39" s="12" t="n"/>
-      <c r="I39" s="9" t="n"/>
-      <c r="J39" s="13" t="n"/>
-      <c r="K39" s="9">
-        <f>IF(OR(E39&lt;&gt;"",I39&lt;&gt;""),"Занято",IF(AND(F38="Повторный приём (1 час)",A38=A39),"Занято","Свободно"))</f>
+      <c r="I39" s="11" t="n"/>
+      <c r="J39" s="9" t="n"/>
+      <c r="K39" s="13" t="n"/>
+      <c r="L39" s="9">
+        <f>IF(OR(E39&lt;&gt;"",J39&lt;&gt;""),"Занято",IF(AND(F38="Повторный приём (1 час)",A38=A39),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1789,10 +1833,11 @@
       <c r="F40" s="11" t="n"/>
       <c r="G40" s="12" t="n"/>
       <c r="H40" s="12" t="n"/>
-      <c r="I40" s="9" t="n"/>
-      <c r="J40" s="13" t="n"/>
-      <c r="K40" s="9">
-        <f>IF(OR(E40&lt;&gt;"",I40&lt;&gt;""),"Занято",IF(AND(F39="Повторный приём (1 час)",A39=A40),"Занято","Свободно"))</f>
+      <c r="I40" s="11" t="n"/>
+      <c r="J40" s="9" t="n"/>
+      <c r="K40" s="13" t="n"/>
+      <c r="L40" s="9">
+        <f>IF(OR(E40&lt;&gt;"",J40&lt;&gt;""),"Занято",IF(AND(F39="Повторный приём (1 час)",A39=A40),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1819,10 +1864,11 @@
       <c r="F41" s="11" t="n"/>
       <c r="G41" s="12" t="n"/>
       <c r="H41" s="12" t="n"/>
-      <c r="I41" s="9" t="n"/>
-      <c r="J41" s="13" t="n"/>
-      <c r="K41" s="9">
-        <f>IF(OR(E41&lt;&gt;"",I41&lt;&gt;""),"Занято",IF(AND(F40="Повторный приём (1 час)",A40=A41),"Занято","Свободно"))</f>
+      <c r="I41" s="11" t="n"/>
+      <c r="J41" s="9" t="n"/>
+      <c r="K41" s="13" t="n"/>
+      <c r="L41" s="9">
+        <f>IF(OR(E41&lt;&gt;"",J41&lt;&gt;""),"Занято",IF(AND(F40="Повторный приём (1 час)",A40=A41),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1849,10 +1895,11 @@
       <c r="F42" s="11" t="n"/>
       <c r="G42" s="12" t="n"/>
       <c r="H42" s="12" t="n"/>
-      <c r="I42" s="9" t="n"/>
-      <c r="J42" s="13" t="n"/>
-      <c r="K42" s="9">
-        <f>IF(OR(E42&lt;&gt;"",I42&lt;&gt;""),"Занято",IF(AND(F41="Повторный приём (1 час)",A41=A42),"Занято","Свободно"))</f>
+      <c r="I42" s="11" t="n"/>
+      <c r="J42" s="9" t="n"/>
+      <c r="K42" s="13" t="n"/>
+      <c r="L42" s="9">
+        <f>IF(OR(E42&lt;&gt;"",J42&lt;&gt;""),"Занято",IF(AND(F41="Повторный приём (1 час)",A41=A42),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1879,10 +1926,11 @@
       <c r="F43" s="11" t="n"/>
       <c r="G43" s="12" t="n"/>
       <c r="H43" s="12" t="n"/>
-      <c r="I43" s="9" t="n"/>
-      <c r="J43" s="13" t="n"/>
-      <c r="K43" s="9">
-        <f>IF(OR(E43&lt;&gt;"",I43&lt;&gt;""),"Занято",IF(AND(F42="Повторный приём (1 час)",A42=A43),"Занято","Свободно"))</f>
+      <c r="I43" s="11" t="n"/>
+      <c r="J43" s="9" t="n"/>
+      <c r="K43" s="13" t="n"/>
+      <c r="L43" s="9">
+        <f>IF(OR(E43&lt;&gt;"",J43&lt;&gt;""),"Занято",IF(AND(F42="Повторный приём (1 час)",A42=A43),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1909,10 +1957,11 @@
       <c r="F44" s="11" t="n"/>
       <c r="G44" s="12" t="n"/>
       <c r="H44" s="12" t="n"/>
-      <c r="I44" s="9" t="n"/>
-      <c r="J44" s="13" t="n"/>
-      <c r="K44" s="9">
-        <f>IF(OR(E44&lt;&gt;"",I44&lt;&gt;""),"Занято",IF(AND(F43="Повторный приём (1 час)",A43=A44),"Занято","Свободно"))</f>
+      <c r="I44" s="11" t="n"/>
+      <c r="J44" s="9" t="n"/>
+      <c r="K44" s="13" t="n"/>
+      <c r="L44" s="9">
+        <f>IF(OR(E44&lt;&gt;"",J44&lt;&gt;""),"Занято",IF(AND(F43="Повторный приём (1 час)",A43=A44),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1939,10 +1988,11 @@
       <c r="F45" s="11" t="n"/>
       <c r="G45" s="12" t="n"/>
       <c r="H45" s="12" t="n"/>
-      <c r="I45" s="9" t="n"/>
-      <c r="J45" s="13" t="n"/>
-      <c r="K45" s="9">
-        <f>IF(OR(E45&lt;&gt;"",I45&lt;&gt;""),"Занято",IF(AND(F44="Повторный приём (1 час)",A44=A45),"Занято","Свободно"))</f>
+      <c r="I45" s="11" t="n"/>
+      <c r="J45" s="9" t="n"/>
+      <c r="K45" s="13" t="n"/>
+      <c r="L45" s="9">
+        <f>IF(OR(E45&lt;&gt;"",J45&lt;&gt;""),"Занято",IF(AND(F44="Повторный приём (1 час)",A44=A45),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1969,10 +2019,11 @@
       <c r="F46" s="17" t="n"/>
       <c r="G46" s="18" t="n"/>
       <c r="H46" s="18" t="n"/>
-      <c r="I46" s="15" t="n"/>
-      <c r="J46" s="19" t="n"/>
-      <c r="K46" s="15">
-        <f>IF(OR(E46&lt;&gt;"",I46&lt;&gt;""),"Занято",IF(AND(F45="Повторный приём (1 час)",A45=A46),"Занято","Свободно"))</f>
+      <c r="I46" s="17" t="n"/>
+      <c r="J46" s="15" t="n"/>
+      <c r="K46" s="19" t="n"/>
+      <c r="L46" s="15">
+        <f>IF(OR(E46&lt;&gt;"",J46&lt;&gt;""),"Занято",IF(AND(F45="Повторный приём (1 час)",A45=A46),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -1999,10 +2050,11 @@
       <c r="F47" s="23" t="n"/>
       <c r="G47" s="24" t="n"/>
       <c r="H47" s="24" t="n"/>
-      <c r="I47" s="21" t="n"/>
-      <c r="J47" s="25" t="n"/>
-      <c r="K47" s="21">
-        <f>IF(OR(E47&lt;&gt;"",I47&lt;&gt;""),"Занято",IF(AND(F46="Повторный приём (1 час)",A46=A47),"Занято","Свободно"))</f>
+      <c r="I47" s="23" t="n"/>
+      <c r="J47" s="21" t="n"/>
+      <c r="K47" s="25" t="n"/>
+      <c r="L47" s="21">
+        <f>IF(OR(E47&lt;&gt;"",J47&lt;&gt;""),"Занято",IF(AND(F46="Повторный приём (1 час)",A46=A47),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2029,10 +2081,11 @@
       <c r="F48" s="23" t="n"/>
       <c r="G48" s="24" t="n"/>
       <c r="H48" s="24" t="n"/>
-      <c r="I48" s="21" t="n"/>
-      <c r="J48" s="25" t="n"/>
-      <c r="K48" s="21">
-        <f>IF(OR(E48&lt;&gt;"",I48&lt;&gt;""),"Занято",IF(AND(F47="Повторный приём (1 час)",A47=A48),"Занято","Свободно"))</f>
+      <c r="I48" s="23" t="n"/>
+      <c r="J48" s="21" t="n"/>
+      <c r="K48" s="25" t="n"/>
+      <c r="L48" s="21">
+        <f>IF(OR(E48&lt;&gt;"",J48&lt;&gt;""),"Занято",IF(AND(F47="Повторный приём (1 час)",A47=A48),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2059,10 +2112,11 @@
       <c r="F49" s="23" t="n"/>
       <c r="G49" s="24" t="n"/>
       <c r="H49" s="24" t="n"/>
-      <c r="I49" s="21" t="n"/>
-      <c r="J49" s="25" t="n"/>
-      <c r="K49" s="21">
-        <f>IF(OR(E49&lt;&gt;"",I49&lt;&gt;""),"Занято",IF(AND(F48="Повторный приём (1 час)",A48=A49),"Занято","Свободно"))</f>
+      <c r="I49" s="23" t="n"/>
+      <c r="J49" s="21" t="n"/>
+      <c r="K49" s="25" t="n"/>
+      <c r="L49" s="21">
+        <f>IF(OR(E49&lt;&gt;"",J49&lt;&gt;""),"Занято",IF(AND(F48="Повторный приём (1 час)",A48=A49),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2089,10 +2143,11 @@
       <c r="F50" s="23" t="n"/>
       <c r="G50" s="24" t="n"/>
       <c r="H50" s="24" t="n"/>
-      <c r="I50" s="21" t="n"/>
-      <c r="J50" s="25" t="n"/>
-      <c r="K50" s="21">
-        <f>IF(OR(E50&lt;&gt;"",I50&lt;&gt;""),"Занято",IF(AND(F49="Повторный приём (1 час)",A49=A50),"Занято","Свободно"))</f>
+      <c r="I50" s="23" t="n"/>
+      <c r="J50" s="21" t="n"/>
+      <c r="K50" s="25" t="n"/>
+      <c r="L50" s="21">
+        <f>IF(OR(E50&lt;&gt;"",J50&lt;&gt;""),"Занято",IF(AND(F49="Повторный приём (1 час)",A49=A50),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2119,10 +2174,11 @@
       <c r="F51" s="23" t="n"/>
       <c r="G51" s="24" t="n"/>
       <c r="H51" s="24" t="n"/>
-      <c r="I51" s="21" t="n"/>
-      <c r="J51" s="25" t="n"/>
-      <c r="K51" s="21">
-        <f>IF(OR(E51&lt;&gt;"",I51&lt;&gt;""),"Занято",IF(AND(F50="Повторный приём (1 час)",A50=A51),"Занято","Свободно"))</f>
+      <c r="I51" s="23" t="n"/>
+      <c r="J51" s="21" t="n"/>
+      <c r="K51" s="25" t="n"/>
+      <c r="L51" s="21">
+        <f>IF(OR(E51&lt;&gt;"",J51&lt;&gt;""),"Занято",IF(AND(F50="Повторный приём (1 час)",A50=A51),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2149,10 +2205,11 @@
       <c r="F52" s="23" t="n"/>
       <c r="G52" s="24" t="n"/>
       <c r="H52" s="24" t="n"/>
-      <c r="I52" s="21" t="n"/>
-      <c r="J52" s="25" t="n"/>
-      <c r="K52" s="21">
-        <f>IF(OR(E52&lt;&gt;"",I52&lt;&gt;""),"Занято",IF(AND(F51="Повторный приём (1 час)",A51=A52),"Занято","Свободно"))</f>
+      <c r="I52" s="23" t="n"/>
+      <c r="J52" s="21" t="n"/>
+      <c r="K52" s="25" t="n"/>
+      <c r="L52" s="21">
+        <f>IF(OR(E52&lt;&gt;"",J52&lt;&gt;""),"Занято",IF(AND(F51="Повторный приём (1 час)",A51=A52),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2179,10 +2236,11 @@
       <c r="F53" s="23" t="n"/>
       <c r="G53" s="24" t="n"/>
       <c r="H53" s="24" t="n"/>
-      <c r="I53" s="21" t="n"/>
-      <c r="J53" s="25" t="n"/>
-      <c r="K53" s="21">
-        <f>IF(OR(E53&lt;&gt;"",I53&lt;&gt;""),"Занято",IF(AND(F52="Повторный приём (1 час)",A52=A53),"Занято","Свободно"))</f>
+      <c r="I53" s="23" t="n"/>
+      <c r="J53" s="21" t="n"/>
+      <c r="K53" s="25" t="n"/>
+      <c r="L53" s="21">
+        <f>IF(OR(E53&lt;&gt;"",J53&lt;&gt;""),"Занято",IF(AND(F52="Повторный приём (1 час)",A52=A53),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2209,10 +2267,11 @@
       <c r="F54" s="23" t="n"/>
       <c r="G54" s="24" t="n"/>
       <c r="H54" s="24" t="n"/>
-      <c r="I54" s="21" t="n"/>
-      <c r="J54" s="25" t="n"/>
-      <c r="K54" s="21">
-        <f>IF(OR(E54&lt;&gt;"",I54&lt;&gt;""),"Занято",IF(AND(F53="Повторный приём (1 час)",A53=A54),"Занято","Свободно"))</f>
+      <c r="I54" s="23" t="n"/>
+      <c r="J54" s="21" t="n"/>
+      <c r="K54" s="25" t="n"/>
+      <c r="L54" s="21">
+        <f>IF(OR(E54&lt;&gt;"",J54&lt;&gt;""),"Занято",IF(AND(F53="Повторный приём (1 час)",A53=A54),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2239,10 +2298,11 @@
       <c r="F55" s="23" t="n"/>
       <c r="G55" s="24" t="n"/>
       <c r="H55" s="24" t="n"/>
-      <c r="I55" s="21" t="n"/>
-      <c r="J55" s="25" t="n"/>
-      <c r="K55" s="21">
-        <f>IF(OR(E55&lt;&gt;"",I55&lt;&gt;""),"Занято",IF(AND(F54="Повторный приём (1 час)",A54=A55),"Занято","Свободно"))</f>
+      <c r="I55" s="23" t="n"/>
+      <c r="J55" s="21" t="n"/>
+      <c r="K55" s="25" t="n"/>
+      <c r="L55" s="21">
+        <f>IF(OR(E55&lt;&gt;"",J55&lt;&gt;""),"Занято",IF(AND(F54="Повторный приём (1 час)",A54=A55),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2269,10 +2329,11 @@
       <c r="F56" s="23" t="n"/>
       <c r="G56" s="24" t="n"/>
       <c r="H56" s="24" t="n"/>
-      <c r="I56" s="21" t="n"/>
-      <c r="J56" s="25" t="n"/>
-      <c r="K56" s="21">
-        <f>IF(OR(E56&lt;&gt;"",I56&lt;&gt;""),"Занято",IF(AND(F55="Повторный приём (1 час)",A55=A56),"Занято","Свободно"))</f>
+      <c r="I56" s="23" t="n"/>
+      <c r="J56" s="21" t="n"/>
+      <c r="K56" s="25" t="n"/>
+      <c r="L56" s="21">
+        <f>IF(OR(E56&lt;&gt;"",J56&lt;&gt;""),"Занято",IF(AND(F55="Повторный приём (1 час)",A55=A56),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2299,10 +2360,11 @@
       <c r="F57" s="23" t="n"/>
       <c r="G57" s="24" t="n"/>
       <c r="H57" s="24" t="n"/>
-      <c r="I57" s="21" t="n"/>
-      <c r="J57" s="25" t="n"/>
-      <c r="K57" s="21">
-        <f>IF(OR(E57&lt;&gt;"",I57&lt;&gt;""),"Занято",IF(AND(F56="Повторный приём (1 час)",A56=A57),"Занято","Свободно"))</f>
+      <c r="I57" s="23" t="n"/>
+      <c r="J57" s="21" t="n"/>
+      <c r="K57" s="25" t="n"/>
+      <c r="L57" s="21">
+        <f>IF(OR(E57&lt;&gt;"",J57&lt;&gt;""),"Занято",IF(AND(F56="Повторный приём (1 час)",A56=A57),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2329,10 +2391,11 @@
       <c r="F58" s="23" t="n"/>
       <c r="G58" s="24" t="n"/>
       <c r="H58" s="24" t="n"/>
-      <c r="I58" s="21" t="n"/>
-      <c r="J58" s="25" t="n"/>
-      <c r="K58" s="21">
-        <f>IF(OR(E58&lt;&gt;"",I58&lt;&gt;""),"Занято",IF(AND(F57="Повторный приём (1 час)",A57=A58),"Занято","Свободно"))</f>
+      <c r="I58" s="23" t="n"/>
+      <c r="J58" s="21" t="n"/>
+      <c r="K58" s="25" t="n"/>
+      <c r="L58" s="21">
+        <f>IF(OR(E58&lt;&gt;"",J58&lt;&gt;""),"Занято",IF(AND(F57="Повторный приём (1 час)",A57=A58),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2359,10 +2422,11 @@
       <c r="F59" s="23" t="n"/>
       <c r="G59" s="24" t="n"/>
       <c r="H59" s="24" t="n"/>
-      <c r="I59" s="21" t="n"/>
-      <c r="J59" s="25" t="n"/>
-      <c r="K59" s="21">
-        <f>IF(OR(E59&lt;&gt;"",I59&lt;&gt;""),"Занято",IF(AND(F58="Повторный приём (1 час)",A58=A59),"Занято","Свободно"))</f>
+      <c r="I59" s="23" t="n"/>
+      <c r="J59" s="21" t="n"/>
+      <c r="K59" s="25" t="n"/>
+      <c r="L59" s="21">
+        <f>IF(OR(E59&lt;&gt;"",J59&lt;&gt;""),"Занято",IF(AND(F58="Повторный приём (1 час)",A58=A59),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2389,10 +2453,11 @@
       <c r="F60" s="23" t="n"/>
       <c r="G60" s="24" t="n"/>
       <c r="H60" s="24" t="n"/>
-      <c r="I60" s="21" t="n"/>
-      <c r="J60" s="25" t="n"/>
-      <c r="K60" s="21">
-        <f>IF(OR(E60&lt;&gt;"",I60&lt;&gt;""),"Занято",IF(AND(F59="Повторный приём (1 час)",A59=A60),"Занято","Свободно"))</f>
+      <c r="I60" s="23" t="n"/>
+      <c r="J60" s="21" t="n"/>
+      <c r="K60" s="25" t="n"/>
+      <c r="L60" s="21">
+        <f>IF(OR(E60&lt;&gt;"",J60&lt;&gt;""),"Занято",IF(AND(F59="Повторный приём (1 час)",A59=A60),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2419,10 +2484,11 @@
       <c r="F61" s="23" t="n"/>
       <c r="G61" s="24" t="n"/>
       <c r="H61" s="24" t="n"/>
-      <c r="I61" s="21" t="n"/>
-      <c r="J61" s="25" t="n"/>
-      <c r="K61" s="21">
-        <f>IF(OR(E61&lt;&gt;"",I61&lt;&gt;""),"Занято",IF(AND(F60="Повторный приём (1 час)",A60=A61),"Занято","Свободно"))</f>
+      <c r="I61" s="23" t="n"/>
+      <c r="J61" s="21" t="n"/>
+      <c r="K61" s="25" t="n"/>
+      <c r="L61" s="21">
+        <f>IF(OR(E61&lt;&gt;"",J61&lt;&gt;""),"Занято",IF(AND(F60="Повторный приём (1 час)",A60=A61),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2449,10 +2515,11 @@
       <c r="F62" s="23" t="n"/>
       <c r="G62" s="24" t="n"/>
       <c r="H62" s="24" t="n"/>
-      <c r="I62" s="21" t="n"/>
-      <c r="J62" s="25" t="n"/>
-      <c r="K62" s="21">
-        <f>IF(OR(E62&lt;&gt;"",I62&lt;&gt;""),"Занято",IF(AND(F61="Повторный приём (1 час)",A61=A62),"Занято","Свободно"))</f>
+      <c r="I62" s="23" t="n"/>
+      <c r="J62" s="21" t="n"/>
+      <c r="K62" s="25" t="n"/>
+      <c r="L62" s="21">
+        <f>IF(OR(E62&lt;&gt;"",J62&lt;&gt;""),"Занято",IF(AND(F61="Повторный приём (1 час)",A61=A62),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2479,10 +2546,11 @@
       <c r="F63" s="23" t="n"/>
       <c r="G63" s="24" t="n"/>
       <c r="H63" s="24" t="n"/>
-      <c r="I63" s="21" t="n"/>
-      <c r="J63" s="25" t="n"/>
-      <c r="K63" s="21">
-        <f>IF(OR(E63&lt;&gt;"",I63&lt;&gt;""),"Занято",IF(AND(F62="Повторный приём (1 час)",A62=A63),"Занято","Свободно"))</f>
+      <c r="I63" s="23" t="n"/>
+      <c r="J63" s="21" t="n"/>
+      <c r="K63" s="25" t="n"/>
+      <c r="L63" s="21">
+        <f>IF(OR(E63&lt;&gt;"",J63&lt;&gt;""),"Занято",IF(AND(F62="Повторный приём (1 час)",A62=A63),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2509,10 +2577,11 @@
       <c r="F64" s="5" t="n"/>
       <c r="G64" s="6" t="n"/>
       <c r="H64" s="6" t="n"/>
-      <c r="I64" s="3" t="n"/>
-      <c r="J64" s="7" t="n"/>
-      <c r="K64" s="3">
-        <f>IF(OR(E64&lt;&gt;"",I64&lt;&gt;""),"Занято",IF(AND(F63="Повторный приём (1 час)",A63=A64),"Занято","Свободно"))</f>
+      <c r="I64" s="5" t="n"/>
+      <c r="J64" s="3" t="n"/>
+      <c r="K64" s="7" t="n"/>
+      <c r="L64" s="3">
+        <f>IF(OR(E64&lt;&gt;"",J64&lt;&gt;""),"Занято",IF(AND(F63="Повторный приём (1 час)",A63=A64),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2539,10 +2608,11 @@
       <c r="F65" s="11" t="n"/>
       <c r="G65" s="12" t="n"/>
       <c r="H65" s="12" t="n"/>
-      <c r="I65" s="9" t="n"/>
-      <c r="J65" s="13" t="n"/>
-      <c r="K65" s="9">
-        <f>IF(OR(E65&lt;&gt;"",I65&lt;&gt;""),"Занято",IF(AND(F64="Повторный приём (1 час)",A64=A65),"Занято","Свободно"))</f>
+      <c r="I65" s="11" t="n"/>
+      <c r="J65" s="9" t="n"/>
+      <c r="K65" s="13" t="n"/>
+      <c r="L65" s="9">
+        <f>IF(OR(E65&lt;&gt;"",J65&lt;&gt;""),"Занято",IF(AND(F64="Повторный приём (1 час)",A64=A65),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2569,10 +2639,11 @@
       <c r="F66" s="11" t="n"/>
       <c r="G66" s="12" t="n"/>
       <c r="H66" s="12" t="n"/>
-      <c r="I66" s="9" t="n"/>
-      <c r="J66" s="13" t="n"/>
-      <c r="K66" s="9">
-        <f>IF(OR(E66&lt;&gt;"",I66&lt;&gt;""),"Занято",IF(AND(F65="Повторный приём (1 час)",A65=A66),"Занято","Свободно"))</f>
+      <c r="I66" s="11" t="n"/>
+      <c r="J66" s="9" t="n"/>
+      <c r="K66" s="13" t="n"/>
+      <c r="L66" s="9">
+        <f>IF(OR(E66&lt;&gt;"",J66&lt;&gt;""),"Занято",IF(AND(F65="Повторный приём (1 час)",A65=A66),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2599,10 +2670,11 @@
       <c r="F67" s="11" t="n"/>
       <c r="G67" s="12" t="n"/>
       <c r="H67" s="12" t="n"/>
-      <c r="I67" s="9" t="n"/>
-      <c r="J67" s="13" t="n"/>
-      <c r="K67" s="9">
-        <f>IF(OR(E67&lt;&gt;"",I67&lt;&gt;""),"Занято",IF(AND(F66="Повторный приём (1 час)",A66=A67),"Занято","Свободно"))</f>
+      <c r="I67" s="11" t="n"/>
+      <c r="J67" s="9" t="n"/>
+      <c r="K67" s="13" t="n"/>
+      <c r="L67" s="9">
+        <f>IF(OR(E67&lt;&gt;"",J67&lt;&gt;""),"Занято",IF(AND(F66="Повторный приём (1 час)",A66=A67),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2629,10 +2701,11 @@
       <c r="F68" s="11" t="n"/>
       <c r="G68" s="12" t="n"/>
       <c r="H68" s="12" t="n"/>
-      <c r="I68" s="9" t="n"/>
-      <c r="J68" s="13" t="n"/>
-      <c r="K68" s="9">
-        <f>IF(OR(E68&lt;&gt;"",I68&lt;&gt;""),"Занято",IF(AND(F67="Повторный приём (1 час)",A67=A68),"Занято","Свободно"))</f>
+      <c r="I68" s="11" t="n"/>
+      <c r="J68" s="9" t="n"/>
+      <c r="K68" s="13" t="n"/>
+      <c r="L68" s="9">
+        <f>IF(OR(E68&lt;&gt;"",J68&lt;&gt;""),"Занято",IF(AND(F67="Повторный приём (1 час)",A67=A68),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2659,10 +2732,11 @@
       <c r="F69" s="11" t="n"/>
       <c r="G69" s="12" t="n"/>
       <c r="H69" s="12" t="n"/>
-      <c r="I69" s="9" t="n"/>
-      <c r="J69" s="13" t="n"/>
-      <c r="K69" s="9">
-        <f>IF(OR(E69&lt;&gt;"",I69&lt;&gt;""),"Занято",IF(AND(F68="Повторный приём (1 час)",A68=A69),"Занято","Свободно"))</f>
+      <c r="I69" s="11" t="n"/>
+      <c r="J69" s="9" t="n"/>
+      <c r="K69" s="13" t="n"/>
+      <c r="L69" s="9">
+        <f>IF(OR(E69&lt;&gt;"",J69&lt;&gt;""),"Занято",IF(AND(F68="Повторный приём (1 час)",A68=A69),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2689,10 +2763,11 @@
       <c r="F70" s="11" t="n"/>
       <c r="G70" s="12" t="n"/>
       <c r="H70" s="12" t="n"/>
-      <c r="I70" s="9" t="n"/>
-      <c r="J70" s="13" t="n"/>
-      <c r="K70" s="9">
-        <f>IF(OR(E70&lt;&gt;"",I70&lt;&gt;""),"Занято",IF(AND(F69="Повторный приём (1 час)",A69=A70),"Занято","Свободно"))</f>
+      <c r="I70" s="11" t="n"/>
+      <c r="J70" s="9" t="n"/>
+      <c r="K70" s="13" t="n"/>
+      <c r="L70" s="9">
+        <f>IF(OR(E70&lt;&gt;"",J70&lt;&gt;""),"Занято",IF(AND(F69="Повторный приём (1 час)",A69=A70),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2719,10 +2794,11 @@
       <c r="F71" s="11" t="n"/>
       <c r="G71" s="12" t="n"/>
       <c r="H71" s="12" t="n"/>
-      <c r="I71" s="9" t="n"/>
-      <c r="J71" s="13" t="n"/>
-      <c r="K71" s="9">
-        <f>IF(OR(E71&lt;&gt;"",I71&lt;&gt;""),"Занято",IF(AND(F70="Повторный приём (1 час)",A70=A71),"Занято","Свободно"))</f>
+      <c r="I71" s="11" t="n"/>
+      <c r="J71" s="9" t="n"/>
+      <c r="K71" s="13" t="n"/>
+      <c r="L71" s="9">
+        <f>IF(OR(E71&lt;&gt;"",J71&lt;&gt;""),"Занято",IF(AND(F70="Повторный приём (1 час)",A70=A71),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2749,10 +2825,11 @@
       <c r="F72" s="11" t="n"/>
       <c r="G72" s="12" t="n"/>
       <c r="H72" s="12" t="n"/>
-      <c r="I72" s="9" t="n"/>
-      <c r="J72" s="13" t="n"/>
-      <c r="K72" s="9">
-        <f>IF(OR(E72&lt;&gt;"",I72&lt;&gt;""),"Занято",IF(AND(F71="Повторный приём (1 час)",A71=A72),"Занято","Свободно"))</f>
+      <c r="I72" s="11" t="n"/>
+      <c r="J72" s="9" t="n"/>
+      <c r="K72" s="13" t="n"/>
+      <c r="L72" s="9">
+        <f>IF(OR(E72&lt;&gt;"",J72&lt;&gt;""),"Занято",IF(AND(F71="Повторный приём (1 час)",A71=A72),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2779,10 +2856,11 @@
       <c r="F73" s="11" t="n"/>
       <c r="G73" s="12" t="n"/>
       <c r="H73" s="12" t="n"/>
-      <c r="I73" s="9" t="n"/>
-      <c r="J73" s="13" t="n"/>
-      <c r="K73" s="9">
-        <f>IF(OR(E73&lt;&gt;"",I73&lt;&gt;""),"Занято",IF(AND(F72="Повторный приём (1 час)",A72=A73),"Занято","Свободно"))</f>
+      <c r="I73" s="11" t="n"/>
+      <c r="J73" s="9" t="n"/>
+      <c r="K73" s="13" t="n"/>
+      <c r="L73" s="9">
+        <f>IF(OR(E73&lt;&gt;"",J73&lt;&gt;""),"Занято",IF(AND(F72="Повторный приём (1 час)",A72=A73),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2809,10 +2887,11 @@
       <c r="F74" s="11" t="n"/>
       <c r="G74" s="12" t="n"/>
       <c r="H74" s="12" t="n"/>
-      <c r="I74" s="9" t="n"/>
-      <c r="J74" s="13" t="n"/>
-      <c r="K74" s="9">
-        <f>IF(OR(E74&lt;&gt;"",I74&lt;&gt;""),"Занято",IF(AND(F73="Повторный приём (1 час)",A73=A74),"Занято","Свободно"))</f>
+      <c r="I74" s="11" t="n"/>
+      <c r="J74" s="9" t="n"/>
+      <c r="K74" s="13" t="n"/>
+      <c r="L74" s="9">
+        <f>IF(OR(E74&lt;&gt;"",J74&lt;&gt;""),"Занято",IF(AND(F73="Повторный приём (1 час)",A73=A74),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2839,10 +2918,11 @@
       <c r="F75" s="11" t="n"/>
       <c r="G75" s="12" t="n"/>
       <c r="H75" s="12" t="n"/>
-      <c r="I75" s="9" t="n"/>
-      <c r="J75" s="13" t="n"/>
-      <c r="K75" s="9">
-        <f>IF(OR(E75&lt;&gt;"",I75&lt;&gt;""),"Занято",IF(AND(F74="Повторный приём (1 час)",A74=A75),"Занято","Свободно"))</f>
+      <c r="I75" s="11" t="n"/>
+      <c r="J75" s="9" t="n"/>
+      <c r="K75" s="13" t="n"/>
+      <c r="L75" s="9">
+        <f>IF(OR(E75&lt;&gt;"",J75&lt;&gt;""),"Занято",IF(AND(F74="Повторный приём (1 час)",A74=A75),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2869,10 +2949,11 @@
       <c r="F76" s="11" t="n"/>
       <c r="G76" s="12" t="n"/>
       <c r="H76" s="12" t="n"/>
-      <c r="I76" s="9" t="n"/>
-      <c r="J76" s="13" t="n"/>
-      <c r="K76" s="9">
-        <f>IF(OR(E76&lt;&gt;"",I76&lt;&gt;""),"Занято",IF(AND(F75="Повторный приём (1 час)",A75=A76),"Занято","Свободно"))</f>
+      <c r="I76" s="11" t="n"/>
+      <c r="J76" s="9" t="n"/>
+      <c r="K76" s="13" t="n"/>
+      <c r="L76" s="9">
+        <f>IF(OR(E76&lt;&gt;"",J76&lt;&gt;""),"Занято",IF(AND(F75="Повторный приём (1 час)",A75=A76),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2899,10 +2980,11 @@
       <c r="F77" s="11" t="n"/>
       <c r="G77" s="12" t="n"/>
       <c r="H77" s="12" t="n"/>
-      <c r="I77" s="9" t="n"/>
-      <c r="J77" s="13" t="n"/>
-      <c r="K77" s="9">
-        <f>IF(OR(E77&lt;&gt;"",I77&lt;&gt;""),"Занято",IF(AND(F76="Повторный приём (1 час)",A76=A77),"Занято","Свободно"))</f>
+      <c r="I77" s="11" t="n"/>
+      <c r="J77" s="9" t="n"/>
+      <c r="K77" s="13" t="n"/>
+      <c r="L77" s="9">
+        <f>IF(OR(E77&lt;&gt;"",J77&lt;&gt;""),"Занято",IF(AND(F76="Повторный приём (1 час)",A76=A77),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2929,10 +3011,11 @@
       <c r="F78" s="11" t="n"/>
       <c r="G78" s="12" t="n"/>
       <c r="H78" s="12" t="n"/>
-      <c r="I78" s="9" t="n"/>
-      <c r="J78" s="13" t="n"/>
-      <c r="K78" s="9">
-        <f>IF(OR(E78&lt;&gt;"",I78&lt;&gt;""),"Занято",IF(AND(F77="Повторный приём (1 час)",A77=A78),"Занято","Свободно"))</f>
+      <c r="I78" s="11" t="n"/>
+      <c r="J78" s="9" t="n"/>
+      <c r="K78" s="13" t="n"/>
+      <c r="L78" s="9">
+        <f>IF(OR(E78&lt;&gt;"",J78&lt;&gt;""),"Занято",IF(AND(F77="Повторный приём (1 час)",A77=A78),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2959,10 +3042,11 @@
       <c r="F79" s="11" t="n"/>
       <c r="G79" s="12" t="n"/>
       <c r="H79" s="12" t="n"/>
-      <c r="I79" s="9" t="n"/>
-      <c r="J79" s="13" t="n"/>
-      <c r="K79" s="9">
-        <f>IF(OR(E79&lt;&gt;"",I79&lt;&gt;""),"Занято",IF(AND(F78="Повторный приём (1 час)",A78=A79),"Занято","Свободно"))</f>
+      <c r="I79" s="11" t="n"/>
+      <c r="J79" s="9" t="n"/>
+      <c r="K79" s="13" t="n"/>
+      <c r="L79" s="9">
+        <f>IF(OR(E79&lt;&gt;"",J79&lt;&gt;""),"Занято",IF(AND(F78="Повторный приём (1 час)",A78=A79),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -2989,10 +3073,11 @@
       <c r="F80" s="11" t="n"/>
       <c r="G80" s="12" t="n"/>
       <c r="H80" s="12" t="n"/>
-      <c r="I80" s="9" t="n"/>
-      <c r="J80" s="13" t="n"/>
-      <c r="K80" s="9">
-        <f>IF(OR(E80&lt;&gt;"",I80&lt;&gt;""),"Занято",IF(AND(F79="Повторный приём (1 час)",A79=A80),"Занято","Свободно"))</f>
+      <c r="I80" s="11" t="n"/>
+      <c r="J80" s="9" t="n"/>
+      <c r="K80" s="13" t="n"/>
+      <c r="L80" s="9">
+        <f>IF(OR(E80&lt;&gt;"",J80&lt;&gt;""),"Занято",IF(AND(F79="Повторный приём (1 час)",A79=A80),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3019,10 +3104,11 @@
       <c r="F81" s="11" t="n"/>
       <c r="G81" s="12" t="n"/>
       <c r="H81" s="12" t="n"/>
-      <c r="I81" s="9" t="n"/>
-      <c r="J81" s="13" t="n"/>
-      <c r="K81" s="9">
-        <f>IF(OR(E81&lt;&gt;"",I81&lt;&gt;""),"Занято",IF(AND(F80="Повторный приём (1 час)",A80=A81),"Занято","Свободно"))</f>
+      <c r="I81" s="11" t="n"/>
+      <c r="J81" s="9" t="n"/>
+      <c r="K81" s="13" t="n"/>
+      <c r="L81" s="9">
+        <f>IF(OR(E81&lt;&gt;"",J81&lt;&gt;""),"Занято",IF(AND(F80="Повторный приём (1 час)",A80=A81),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3049,10 +3135,11 @@
       <c r="F82" s="17" t="n"/>
       <c r="G82" s="18" t="n"/>
       <c r="H82" s="18" t="n"/>
-      <c r="I82" s="15" t="n"/>
-      <c r="J82" s="19" t="n"/>
-      <c r="K82" s="15">
-        <f>IF(OR(E82&lt;&gt;"",I82&lt;&gt;""),"Занято",IF(AND(F81="Повторный приём (1 час)",A81=A82),"Занято","Свободно"))</f>
+      <c r="I82" s="17" t="n"/>
+      <c r="J82" s="15" t="n"/>
+      <c r="K82" s="19" t="n"/>
+      <c r="L82" s="15">
+        <f>IF(OR(E82&lt;&gt;"",J82&lt;&gt;""),"Занято",IF(AND(F81="Повторный приём (1 час)",A81=A82),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3079,10 +3166,11 @@
       <c r="F83" s="23" t="n"/>
       <c r="G83" s="24" t="n"/>
       <c r="H83" s="24" t="n"/>
-      <c r="I83" s="21" t="n"/>
-      <c r="J83" s="25" t="n"/>
-      <c r="K83" s="21">
-        <f>IF(OR(E83&lt;&gt;"",I83&lt;&gt;""),"Занято",IF(AND(F82="Повторный приём (1 час)",A82=A83),"Занято","Свободно"))</f>
+      <c r="I83" s="23" t="n"/>
+      <c r="J83" s="21" t="n"/>
+      <c r="K83" s="25" t="n"/>
+      <c r="L83" s="21">
+        <f>IF(OR(E83&lt;&gt;"",J83&lt;&gt;""),"Занято",IF(AND(F82="Повторный приём (1 час)",A82=A83),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3109,10 +3197,11 @@
       <c r="F84" s="23" t="n"/>
       <c r="G84" s="24" t="n"/>
       <c r="H84" s="24" t="n"/>
-      <c r="I84" s="21" t="n"/>
-      <c r="J84" s="25" t="n"/>
-      <c r="K84" s="21">
-        <f>IF(OR(E84&lt;&gt;"",I84&lt;&gt;""),"Занято",IF(AND(F83="Повторный приём (1 час)",A83=A84),"Занято","Свободно"))</f>
+      <c r="I84" s="23" t="n"/>
+      <c r="J84" s="21" t="n"/>
+      <c r="K84" s="25" t="n"/>
+      <c r="L84" s="21">
+        <f>IF(OR(E84&lt;&gt;"",J84&lt;&gt;""),"Занято",IF(AND(F83="Повторный приём (1 час)",A83=A84),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3139,10 +3228,11 @@
       <c r="F85" s="23" t="n"/>
       <c r="G85" s="24" t="n"/>
       <c r="H85" s="24" t="n"/>
-      <c r="I85" s="21" t="n"/>
-      <c r="J85" s="25" t="n"/>
-      <c r="K85" s="21">
-        <f>IF(OR(E85&lt;&gt;"",I85&lt;&gt;""),"Занято",IF(AND(F84="Повторный приём (1 час)",A84=A85),"Занято","Свободно"))</f>
+      <c r="I85" s="23" t="n"/>
+      <c r="J85" s="21" t="n"/>
+      <c r="K85" s="25" t="n"/>
+      <c r="L85" s="21">
+        <f>IF(OR(E85&lt;&gt;"",J85&lt;&gt;""),"Занято",IF(AND(F84="Повторный приём (1 час)",A84=A85),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3169,10 +3259,11 @@
       <c r="F86" s="23" t="n"/>
       <c r="G86" s="24" t="n"/>
       <c r="H86" s="24" t="n"/>
-      <c r="I86" s="21" t="n"/>
-      <c r="J86" s="25" t="n"/>
-      <c r="K86" s="21">
-        <f>IF(OR(E86&lt;&gt;"",I86&lt;&gt;""),"Занято",IF(AND(F85="Повторный приём (1 час)",A85=A86),"Занято","Свободно"))</f>
+      <c r="I86" s="23" t="n"/>
+      <c r="J86" s="21" t="n"/>
+      <c r="K86" s="25" t="n"/>
+      <c r="L86" s="21">
+        <f>IF(OR(E86&lt;&gt;"",J86&lt;&gt;""),"Занято",IF(AND(F85="Повторный приём (1 час)",A85=A86),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3199,10 +3290,11 @@
       <c r="F87" s="23" t="n"/>
       <c r="G87" s="24" t="n"/>
       <c r="H87" s="24" t="n"/>
-      <c r="I87" s="21" t="n"/>
-      <c r="J87" s="25" t="n"/>
-      <c r="K87" s="21">
-        <f>IF(OR(E87&lt;&gt;"",I87&lt;&gt;""),"Занято",IF(AND(F86="Повторный приём (1 час)",A86=A87),"Занято","Свободно"))</f>
+      <c r="I87" s="23" t="n"/>
+      <c r="J87" s="21" t="n"/>
+      <c r="K87" s="25" t="n"/>
+      <c r="L87" s="21">
+        <f>IF(OR(E87&lt;&gt;"",J87&lt;&gt;""),"Занято",IF(AND(F86="Повторный приём (1 час)",A86=A87),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3229,10 +3321,11 @@
       <c r="F88" s="23" t="n"/>
       <c r="G88" s="24" t="n"/>
       <c r="H88" s="24" t="n"/>
-      <c r="I88" s="21" t="n"/>
-      <c r="J88" s="25" t="n"/>
-      <c r="K88" s="21">
-        <f>IF(OR(E88&lt;&gt;"",I88&lt;&gt;""),"Занято",IF(AND(F87="Повторный приём (1 час)",A87=A88),"Занято","Свободно"))</f>
+      <c r="I88" s="23" t="n"/>
+      <c r="J88" s="21" t="n"/>
+      <c r="K88" s="25" t="n"/>
+      <c r="L88" s="21">
+        <f>IF(OR(E88&lt;&gt;"",J88&lt;&gt;""),"Занято",IF(AND(F87="Повторный приём (1 час)",A87=A88),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3259,10 +3352,11 @@
       <c r="F89" s="23" t="n"/>
       <c r="G89" s="24" t="n"/>
       <c r="H89" s="24" t="n"/>
-      <c r="I89" s="21" t="n"/>
-      <c r="J89" s="25" t="n"/>
-      <c r="K89" s="21">
-        <f>IF(OR(E89&lt;&gt;"",I89&lt;&gt;""),"Занято",IF(AND(F88="Повторный приём (1 час)",A88=A89),"Занято","Свободно"))</f>
+      <c r="I89" s="23" t="n"/>
+      <c r="J89" s="21" t="n"/>
+      <c r="K89" s="25" t="n"/>
+      <c r="L89" s="21">
+        <f>IF(OR(E89&lt;&gt;"",J89&lt;&gt;""),"Занято",IF(AND(F88="Повторный приём (1 час)",A88=A89),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3289,10 +3383,11 @@
       <c r="F90" s="23" t="n"/>
       <c r="G90" s="24" t="n"/>
       <c r="H90" s="24" t="n"/>
-      <c r="I90" s="21" t="n"/>
-      <c r="J90" s="25" t="n"/>
-      <c r="K90" s="21">
-        <f>IF(OR(E90&lt;&gt;"",I90&lt;&gt;""),"Занято",IF(AND(F89="Повторный приём (1 час)",A89=A90),"Занято","Свободно"))</f>
+      <c r="I90" s="23" t="n"/>
+      <c r="J90" s="21" t="n"/>
+      <c r="K90" s="25" t="n"/>
+      <c r="L90" s="21">
+        <f>IF(OR(E90&lt;&gt;"",J90&lt;&gt;""),"Занято",IF(AND(F89="Повторный приём (1 час)",A89=A90),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3319,10 +3414,11 @@
       <c r="F91" s="23" t="n"/>
       <c r="G91" s="24" t="n"/>
       <c r="H91" s="24" t="n"/>
-      <c r="I91" s="21" t="n"/>
-      <c r="J91" s="25" t="n"/>
-      <c r="K91" s="21">
-        <f>IF(OR(E91&lt;&gt;"",I91&lt;&gt;""),"Занято",IF(AND(F90="Повторный приём (1 час)",A90=A91),"Занято","Свободно"))</f>
+      <c r="I91" s="23" t="n"/>
+      <c r="J91" s="21" t="n"/>
+      <c r="K91" s="25" t="n"/>
+      <c r="L91" s="21">
+        <f>IF(OR(E91&lt;&gt;"",J91&lt;&gt;""),"Занято",IF(AND(F90="Повторный приём (1 час)",A90=A91),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3349,10 +3445,11 @@
       <c r="F92" s="23" t="n"/>
       <c r="G92" s="24" t="n"/>
       <c r="H92" s="24" t="n"/>
-      <c r="I92" s="21" t="n"/>
-      <c r="J92" s="25" t="n"/>
-      <c r="K92" s="21">
-        <f>IF(OR(E92&lt;&gt;"",I92&lt;&gt;""),"Занято",IF(AND(F91="Повторный приём (1 час)",A91=A92),"Занято","Свободно"))</f>
+      <c r="I92" s="23" t="n"/>
+      <c r="J92" s="21" t="n"/>
+      <c r="K92" s="25" t="n"/>
+      <c r="L92" s="21">
+        <f>IF(OR(E92&lt;&gt;"",J92&lt;&gt;""),"Занято",IF(AND(F91="Повторный приём (1 час)",A91=A92),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3379,10 +3476,11 @@
       <c r="F93" s="23" t="n"/>
       <c r="G93" s="24" t="n"/>
       <c r="H93" s="24" t="n"/>
-      <c r="I93" s="21" t="n"/>
-      <c r="J93" s="25" t="n"/>
-      <c r="K93" s="21">
-        <f>IF(OR(E93&lt;&gt;"",I93&lt;&gt;""),"Занято",IF(AND(F92="Повторный приём (1 час)",A92=A93),"Занято","Свободно"))</f>
+      <c r="I93" s="23" t="n"/>
+      <c r="J93" s="21" t="n"/>
+      <c r="K93" s="25" t="n"/>
+      <c r="L93" s="21">
+        <f>IF(OR(E93&lt;&gt;"",J93&lt;&gt;""),"Занято",IF(AND(F92="Повторный приём (1 час)",A92=A93),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3409,10 +3507,11 @@
       <c r="F94" s="23" t="n"/>
       <c r="G94" s="24" t="n"/>
       <c r="H94" s="24" t="n"/>
-      <c r="I94" s="21" t="n"/>
-      <c r="J94" s="25" t="n"/>
-      <c r="K94" s="21">
-        <f>IF(OR(E94&lt;&gt;"",I94&lt;&gt;""),"Занято",IF(AND(F93="Повторный приём (1 час)",A93=A94),"Занято","Свободно"))</f>
+      <c r="I94" s="23" t="n"/>
+      <c r="J94" s="21" t="n"/>
+      <c r="K94" s="25" t="n"/>
+      <c r="L94" s="21">
+        <f>IF(OR(E94&lt;&gt;"",J94&lt;&gt;""),"Занято",IF(AND(F93="Повторный приём (1 час)",A93=A94),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3439,10 +3538,11 @@
       <c r="F95" s="23" t="n"/>
       <c r="G95" s="24" t="n"/>
       <c r="H95" s="24" t="n"/>
-      <c r="I95" s="21" t="n"/>
-      <c r="J95" s="25" t="n"/>
-      <c r="K95" s="21">
-        <f>IF(OR(E95&lt;&gt;"",I95&lt;&gt;""),"Занято",IF(AND(F94="Повторный приём (1 час)",A94=A95),"Занято","Свободно"))</f>
+      <c r="I95" s="23" t="n"/>
+      <c r="J95" s="21" t="n"/>
+      <c r="K95" s="25" t="n"/>
+      <c r="L95" s="21">
+        <f>IF(OR(E95&lt;&gt;"",J95&lt;&gt;""),"Занято",IF(AND(F94="Повторный приём (1 час)",A94=A95),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3469,10 +3569,11 @@
       <c r="F96" s="23" t="n"/>
       <c r="G96" s="24" t="n"/>
       <c r="H96" s="24" t="n"/>
-      <c r="I96" s="21" t="n"/>
-      <c r="J96" s="25" t="n"/>
-      <c r="K96" s="21">
-        <f>IF(OR(E96&lt;&gt;"",I96&lt;&gt;""),"Занято",IF(AND(F95="Повторный приём (1 час)",A95=A96),"Занято","Свободно"))</f>
+      <c r="I96" s="23" t="n"/>
+      <c r="J96" s="21" t="n"/>
+      <c r="K96" s="25" t="n"/>
+      <c r="L96" s="21">
+        <f>IF(OR(E96&lt;&gt;"",J96&lt;&gt;""),"Занято",IF(AND(F95="Повторный приём (1 час)",A95=A96),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3499,10 +3600,11 @@
       <c r="F97" s="23" t="n"/>
       <c r="G97" s="24" t="n"/>
       <c r="H97" s="24" t="n"/>
-      <c r="I97" s="21" t="n"/>
-      <c r="J97" s="25" t="n"/>
-      <c r="K97" s="21">
-        <f>IF(OR(E97&lt;&gt;"",I97&lt;&gt;""),"Занято",IF(AND(F96="Повторный приём (1 час)",A96=A97),"Занято","Свободно"))</f>
+      <c r="I97" s="23" t="n"/>
+      <c r="J97" s="21" t="n"/>
+      <c r="K97" s="25" t="n"/>
+      <c r="L97" s="21">
+        <f>IF(OR(E97&lt;&gt;"",J97&lt;&gt;""),"Занято",IF(AND(F96="Повторный приём (1 час)",A96=A97),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3529,10 +3631,11 @@
       <c r="F98" s="23" t="n"/>
       <c r="G98" s="24" t="n"/>
       <c r="H98" s="24" t="n"/>
-      <c r="I98" s="21" t="n"/>
-      <c r="J98" s="25" t="n"/>
-      <c r="K98" s="21">
-        <f>IF(OR(E98&lt;&gt;"",I98&lt;&gt;""),"Занято",IF(AND(F97="Повторный приём (1 час)",A97=A98),"Занято","Свободно"))</f>
+      <c r="I98" s="23" t="n"/>
+      <c r="J98" s="21" t="n"/>
+      <c r="K98" s="25" t="n"/>
+      <c r="L98" s="21">
+        <f>IF(OR(E98&lt;&gt;"",J98&lt;&gt;""),"Занято",IF(AND(F97="Повторный приём (1 час)",A97=A98),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3559,10 +3662,11 @@
       <c r="F99" s="23" t="n"/>
       <c r="G99" s="24" t="n"/>
       <c r="H99" s="24" t="n"/>
-      <c r="I99" s="21" t="n"/>
-      <c r="J99" s="25" t="n"/>
-      <c r="K99" s="21">
-        <f>IF(OR(E99&lt;&gt;"",I99&lt;&gt;""),"Занято",IF(AND(F98="Повторный приём (1 час)",A98=A99),"Занято","Свободно"))</f>
+      <c r="I99" s="23" t="n"/>
+      <c r="J99" s="21" t="n"/>
+      <c r="K99" s="25" t="n"/>
+      <c r="L99" s="21">
+        <f>IF(OR(E99&lt;&gt;"",J99&lt;&gt;""),"Занято",IF(AND(F98="Повторный приём (1 час)",A98=A99),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3589,10 +3693,11 @@
       <c r="F100" s="5" t="n"/>
       <c r="G100" s="6" t="n"/>
       <c r="H100" s="6" t="n"/>
-      <c r="I100" s="3" t="n"/>
-      <c r="J100" s="7" t="n"/>
-      <c r="K100" s="3">
-        <f>IF(OR(E100&lt;&gt;"",I100&lt;&gt;""),"Занято",IF(AND(F99="Повторный приём (1 час)",A99=A100),"Занято","Свободно"))</f>
+      <c r="I100" s="5" t="n"/>
+      <c r="J100" s="3" t="n"/>
+      <c r="K100" s="7" t="n"/>
+      <c r="L100" s="3">
+        <f>IF(OR(E100&lt;&gt;"",J100&lt;&gt;""),"Занято",IF(AND(F99="Повторный приём (1 час)",A99=A100),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3619,10 +3724,11 @@
       <c r="F101" s="11" t="n"/>
       <c r="G101" s="12" t="n"/>
       <c r="H101" s="12" t="n"/>
-      <c r="I101" s="9" t="n"/>
-      <c r="J101" s="13" t="n"/>
-      <c r="K101" s="9">
-        <f>IF(OR(E101&lt;&gt;"",I101&lt;&gt;""),"Занято",IF(AND(F100="Повторный приём (1 час)",A100=A101),"Занято","Свободно"))</f>
+      <c r="I101" s="11" t="n"/>
+      <c r="J101" s="9" t="n"/>
+      <c r="K101" s="13" t="n"/>
+      <c r="L101" s="9">
+        <f>IF(OR(E101&lt;&gt;"",J101&lt;&gt;""),"Занято",IF(AND(F100="Повторный приём (1 час)",A100=A101),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3649,10 +3755,11 @@
       <c r="F102" s="11" t="n"/>
       <c r="G102" s="12" t="n"/>
       <c r="H102" s="12" t="n"/>
-      <c r="I102" s="9" t="n"/>
-      <c r="J102" s="13" t="n"/>
-      <c r="K102" s="9">
-        <f>IF(OR(E102&lt;&gt;"",I102&lt;&gt;""),"Занято",IF(AND(F101="Повторный приём (1 час)",A101=A102),"Занято","Свободно"))</f>
+      <c r="I102" s="11" t="n"/>
+      <c r="J102" s="9" t="n"/>
+      <c r="K102" s="13" t="n"/>
+      <c r="L102" s="9">
+        <f>IF(OR(E102&lt;&gt;"",J102&lt;&gt;""),"Занято",IF(AND(F101="Повторный приём (1 час)",A101=A102),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3679,10 +3786,11 @@
       <c r="F103" s="11" t="n"/>
       <c r="G103" s="12" t="n"/>
       <c r="H103" s="12" t="n"/>
-      <c r="I103" s="9" t="n"/>
-      <c r="J103" s="13" t="n"/>
-      <c r="K103" s="9">
-        <f>IF(OR(E103&lt;&gt;"",I103&lt;&gt;""),"Занято",IF(AND(F102="Повторный приём (1 час)",A102=A103),"Занято","Свободно"))</f>
+      <c r="I103" s="11" t="n"/>
+      <c r="J103" s="9" t="n"/>
+      <c r="K103" s="13" t="n"/>
+      <c r="L103" s="9">
+        <f>IF(OR(E103&lt;&gt;"",J103&lt;&gt;""),"Занято",IF(AND(F102="Повторный приём (1 час)",A102=A103),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3709,10 +3817,11 @@
       <c r="F104" s="11" t="n"/>
       <c r="G104" s="12" t="n"/>
       <c r="H104" s="12" t="n"/>
-      <c r="I104" s="9" t="n"/>
-      <c r="J104" s="13" t="n"/>
-      <c r="K104" s="9">
-        <f>IF(OR(E104&lt;&gt;"",I104&lt;&gt;""),"Занято",IF(AND(F103="Повторный приём (1 час)",A103=A104),"Занято","Свободно"))</f>
+      <c r="I104" s="11" t="n"/>
+      <c r="J104" s="9" t="n"/>
+      <c r="K104" s="13" t="n"/>
+      <c r="L104" s="9">
+        <f>IF(OR(E104&lt;&gt;"",J104&lt;&gt;""),"Занято",IF(AND(F103="Повторный приём (1 час)",A103=A104),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3739,10 +3848,11 @@
       <c r="F105" s="11" t="n"/>
       <c r="G105" s="12" t="n"/>
       <c r="H105" s="12" t="n"/>
-      <c r="I105" s="9" t="n"/>
-      <c r="J105" s="13" t="n"/>
-      <c r="K105" s="9">
-        <f>IF(OR(E105&lt;&gt;"",I105&lt;&gt;""),"Занято",IF(AND(F104="Повторный приём (1 час)",A104=A105),"Занято","Свободно"))</f>
+      <c r="I105" s="11" t="n"/>
+      <c r="J105" s="9" t="n"/>
+      <c r="K105" s="13" t="n"/>
+      <c r="L105" s="9">
+        <f>IF(OR(E105&lt;&gt;"",J105&lt;&gt;""),"Занято",IF(AND(F104="Повторный приём (1 час)",A104=A105),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3769,10 +3879,11 @@
       <c r="F106" s="11" t="n"/>
       <c r="G106" s="12" t="n"/>
       <c r="H106" s="12" t="n"/>
-      <c r="I106" s="9" t="n"/>
-      <c r="J106" s="13" t="n"/>
-      <c r="K106" s="9">
-        <f>IF(OR(E106&lt;&gt;"",I106&lt;&gt;""),"Занято",IF(AND(F105="Повторный приём (1 час)",A105=A106),"Занято","Свободно"))</f>
+      <c r="I106" s="11" t="n"/>
+      <c r="J106" s="9" t="n"/>
+      <c r="K106" s="13" t="n"/>
+      <c r="L106" s="9">
+        <f>IF(OR(E106&lt;&gt;"",J106&lt;&gt;""),"Занято",IF(AND(F105="Повторный приём (1 час)",A105=A106),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3799,10 +3910,11 @@
       <c r="F107" s="11" t="n"/>
       <c r="G107" s="12" t="n"/>
       <c r="H107" s="12" t="n"/>
-      <c r="I107" s="9" t="n"/>
-      <c r="J107" s="13" t="n"/>
-      <c r="K107" s="9">
-        <f>IF(OR(E107&lt;&gt;"",I107&lt;&gt;""),"Занято",IF(AND(F106="Повторный приём (1 час)",A106=A107),"Занято","Свободно"))</f>
+      <c r="I107" s="11" t="n"/>
+      <c r="J107" s="9" t="n"/>
+      <c r="K107" s="13" t="n"/>
+      <c r="L107" s="9">
+        <f>IF(OR(E107&lt;&gt;"",J107&lt;&gt;""),"Занято",IF(AND(F106="Повторный приём (1 час)",A106=A107),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3829,10 +3941,11 @@
       <c r="F108" s="11" t="n"/>
       <c r="G108" s="12" t="n"/>
       <c r="H108" s="12" t="n"/>
-      <c r="I108" s="9" t="n"/>
-      <c r="J108" s="13" t="n"/>
-      <c r="K108" s="9">
-        <f>IF(OR(E108&lt;&gt;"",I108&lt;&gt;""),"Занято",IF(AND(F107="Повторный приём (1 час)",A107=A108),"Занято","Свободно"))</f>
+      <c r="I108" s="11" t="n"/>
+      <c r="J108" s="9" t="n"/>
+      <c r="K108" s="13" t="n"/>
+      <c r="L108" s="9">
+        <f>IF(OR(E108&lt;&gt;"",J108&lt;&gt;""),"Занято",IF(AND(F107="Повторный приём (1 час)",A107=A108),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3859,10 +3972,11 @@
       <c r="F109" s="11" t="n"/>
       <c r="G109" s="12" t="n"/>
       <c r="H109" s="12" t="n"/>
-      <c r="I109" s="9" t="n"/>
-      <c r="J109" s="13" t="n"/>
-      <c r="K109" s="9">
-        <f>IF(OR(E109&lt;&gt;"",I109&lt;&gt;""),"Занято",IF(AND(F108="Повторный приём (1 час)",A108=A109),"Занято","Свободно"))</f>
+      <c r="I109" s="11" t="n"/>
+      <c r="J109" s="9" t="n"/>
+      <c r="K109" s="13" t="n"/>
+      <c r="L109" s="9">
+        <f>IF(OR(E109&lt;&gt;"",J109&lt;&gt;""),"Занято",IF(AND(F108="Повторный приём (1 час)",A108=A109),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3889,10 +4003,11 @@
       <c r="F110" s="11" t="n"/>
       <c r="G110" s="12" t="n"/>
       <c r="H110" s="12" t="n"/>
-      <c r="I110" s="9" t="n"/>
-      <c r="J110" s="13" t="n"/>
-      <c r="K110" s="9">
-        <f>IF(OR(E110&lt;&gt;"",I110&lt;&gt;""),"Занято",IF(AND(F109="Повторный приём (1 час)",A109=A110),"Занято","Свободно"))</f>
+      <c r="I110" s="11" t="n"/>
+      <c r="J110" s="9" t="n"/>
+      <c r="K110" s="13" t="n"/>
+      <c r="L110" s="9">
+        <f>IF(OR(E110&lt;&gt;"",J110&lt;&gt;""),"Занято",IF(AND(F109="Повторный приём (1 час)",A109=A110),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3919,10 +4034,11 @@
       <c r="F111" s="11" t="n"/>
       <c r="G111" s="12" t="n"/>
       <c r="H111" s="12" t="n"/>
-      <c r="I111" s="9" t="n"/>
-      <c r="J111" s="13" t="n"/>
-      <c r="K111" s="9">
-        <f>IF(OR(E111&lt;&gt;"",I111&lt;&gt;""),"Занято",IF(AND(F110="Повторный приём (1 час)",A110=A111),"Занято","Свободно"))</f>
+      <c r="I111" s="11" t="n"/>
+      <c r="J111" s="9" t="n"/>
+      <c r="K111" s="13" t="n"/>
+      <c r="L111" s="9">
+        <f>IF(OR(E111&lt;&gt;"",J111&lt;&gt;""),"Занято",IF(AND(F110="Повторный приём (1 час)",A110=A111),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3949,10 +4065,11 @@
       <c r="F112" s="11" t="n"/>
       <c r="G112" s="12" t="n"/>
       <c r="H112" s="12" t="n"/>
-      <c r="I112" s="9" t="n"/>
-      <c r="J112" s="13" t="n"/>
-      <c r="K112" s="9">
-        <f>IF(OR(E112&lt;&gt;"",I112&lt;&gt;""),"Занято",IF(AND(F111="Повторный приём (1 час)",A111=A112),"Занято","Свободно"))</f>
+      <c r="I112" s="11" t="n"/>
+      <c r="J112" s="9" t="n"/>
+      <c r="K112" s="13" t="n"/>
+      <c r="L112" s="9">
+        <f>IF(OR(E112&lt;&gt;"",J112&lt;&gt;""),"Занято",IF(AND(F111="Повторный приём (1 час)",A111=A112),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -3979,10 +4096,11 @@
       <c r="F113" s="11" t="n"/>
       <c r="G113" s="12" t="n"/>
       <c r="H113" s="12" t="n"/>
-      <c r="I113" s="9" t="n"/>
-      <c r="J113" s="13" t="n"/>
-      <c r="K113" s="9">
-        <f>IF(OR(E113&lt;&gt;"",I113&lt;&gt;""),"Занято",IF(AND(F112="Повторный приём (1 час)",A112=A113),"Занято","Свободно"))</f>
+      <c r="I113" s="11" t="n"/>
+      <c r="J113" s="9" t="n"/>
+      <c r="K113" s="13" t="n"/>
+      <c r="L113" s="9">
+        <f>IF(OR(E113&lt;&gt;"",J113&lt;&gt;""),"Занято",IF(AND(F112="Повторный приём (1 час)",A112=A113),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4009,10 +4127,11 @@
       <c r="F114" s="11" t="n"/>
       <c r="G114" s="12" t="n"/>
       <c r="H114" s="12" t="n"/>
-      <c r="I114" s="9" t="n"/>
-      <c r="J114" s="13" t="n"/>
-      <c r="K114" s="9">
-        <f>IF(OR(E114&lt;&gt;"",I114&lt;&gt;""),"Занято",IF(AND(F113="Повторный приём (1 час)",A113=A114),"Занято","Свободно"))</f>
+      <c r="I114" s="11" t="n"/>
+      <c r="J114" s="9" t="n"/>
+      <c r="K114" s="13" t="n"/>
+      <c r="L114" s="9">
+        <f>IF(OR(E114&lt;&gt;"",J114&lt;&gt;""),"Занято",IF(AND(F113="Повторный приём (1 час)",A113=A114),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4039,10 +4158,11 @@
       <c r="F115" s="11" t="n"/>
       <c r="G115" s="12" t="n"/>
       <c r="H115" s="12" t="n"/>
-      <c r="I115" s="9" t="n"/>
-      <c r="J115" s="13" t="n"/>
-      <c r="K115" s="9">
-        <f>IF(OR(E115&lt;&gt;"",I115&lt;&gt;""),"Занято",IF(AND(F114="Повторный приём (1 час)",A114=A115),"Занято","Свободно"))</f>
+      <c r="I115" s="11" t="n"/>
+      <c r="J115" s="9" t="n"/>
+      <c r="K115" s="13" t="n"/>
+      <c r="L115" s="9">
+        <f>IF(OR(E115&lt;&gt;"",J115&lt;&gt;""),"Занято",IF(AND(F114="Повторный приём (1 час)",A114=A115),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4069,10 +4189,11 @@
       <c r="F116" s="11" t="n"/>
       <c r="G116" s="12" t="n"/>
       <c r="H116" s="12" t="n"/>
-      <c r="I116" s="9" t="n"/>
-      <c r="J116" s="13" t="n"/>
-      <c r="K116" s="9">
-        <f>IF(OR(E116&lt;&gt;"",I116&lt;&gt;""),"Занято",IF(AND(F115="Повторный приём (1 час)",A115=A116),"Занято","Свободно"))</f>
+      <c r="I116" s="11" t="n"/>
+      <c r="J116" s="9" t="n"/>
+      <c r="K116" s="13" t="n"/>
+      <c r="L116" s="9">
+        <f>IF(OR(E116&lt;&gt;"",J116&lt;&gt;""),"Занято",IF(AND(F115="Повторный приём (1 час)",A115=A116),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4099,10 +4220,11 @@
       <c r="F117" s="11" t="n"/>
       <c r="G117" s="12" t="n"/>
       <c r="H117" s="12" t="n"/>
-      <c r="I117" s="9" t="n"/>
-      <c r="J117" s="13" t="n"/>
-      <c r="K117" s="9">
-        <f>IF(OR(E117&lt;&gt;"",I117&lt;&gt;""),"Занято",IF(AND(F116="Повторный приём (1 час)",A116=A117),"Занято","Свободно"))</f>
+      <c r="I117" s="11" t="n"/>
+      <c r="J117" s="9" t="n"/>
+      <c r="K117" s="13" t="n"/>
+      <c r="L117" s="9">
+        <f>IF(OR(E117&lt;&gt;"",J117&lt;&gt;""),"Занято",IF(AND(F116="Повторный приём (1 час)",A116=A117),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4129,10 +4251,11 @@
       <c r="F118" s="17" t="n"/>
       <c r="G118" s="18" t="n"/>
       <c r="H118" s="18" t="n"/>
-      <c r="I118" s="15" t="n"/>
-      <c r="J118" s="19" t="n"/>
-      <c r="K118" s="15">
-        <f>IF(OR(E118&lt;&gt;"",I118&lt;&gt;""),"Занято",IF(AND(F117="Повторный приём (1 час)",A117=A118),"Занято","Свободно"))</f>
+      <c r="I118" s="17" t="n"/>
+      <c r="J118" s="15" t="n"/>
+      <c r="K118" s="19" t="n"/>
+      <c r="L118" s="15">
+        <f>IF(OR(E118&lt;&gt;"",J118&lt;&gt;""),"Занято",IF(AND(F117="Повторный приём (1 час)",A117=A118),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4159,10 +4282,11 @@
       <c r="F119" s="23" t="n"/>
       <c r="G119" s="24" t="n"/>
       <c r="H119" s="24" t="n"/>
-      <c r="I119" s="21" t="n"/>
-      <c r="J119" s="25" t="n"/>
-      <c r="K119" s="21">
-        <f>IF(OR(E119&lt;&gt;"",I119&lt;&gt;""),"Занято",IF(AND(F118="Повторный приём (1 час)",A118=A119),"Занято","Свободно"))</f>
+      <c r="I119" s="23" t="n"/>
+      <c r="J119" s="21" t="n"/>
+      <c r="K119" s="25" t="n"/>
+      <c r="L119" s="21">
+        <f>IF(OR(E119&lt;&gt;"",J119&lt;&gt;""),"Занято",IF(AND(F118="Повторный приём (1 час)",A118=A119),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4189,10 +4313,11 @@
       <c r="F120" s="23" t="n"/>
       <c r="G120" s="24" t="n"/>
       <c r="H120" s="24" t="n"/>
-      <c r="I120" s="21" t="n"/>
-      <c r="J120" s="25" t="n"/>
-      <c r="K120" s="21">
-        <f>IF(OR(E120&lt;&gt;"",I120&lt;&gt;""),"Занято",IF(AND(F119="Повторный приём (1 час)",A119=A120),"Занято","Свободно"))</f>
+      <c r="I120" s="23" t="n"/>
+      <c r="J120" s="21" t="n"/>
+      <c r="K120" s="25" t="n"/>
+      <c r="L120" s="21">
+        <f>IF(OR(E120&lt;&gt;"",J120&lt;&gt;""),"Занято",IF(AND(F119="Повторный приём (1 час)",A119=A120),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4219,10 +4344,11 @@
       <c r="F121" s="23" t="n"/>
       <c r="G121" s="24" t="n"/>
       <c r="H121" s="24" t="n"/>
-      <c r="I121" s="21" t="n"/>
-      <c r="J121" s="25" t="n"/>
-      <c r="K121" s="21">
-        <f>IF(OR(E121&lt;&gt;"",I121&lt;&gt;""),"Занято",IF(AND(F120="Повторный приём (1 час)",A120=A121),"Занято","Свободно"))</f>
+      <c r="I121" s="23" t="n"/>
+      <c r="J121" s="21" t="n"/>
+      <c r="K121" s="25" t="n"/>
+      <c r="L121" s="21">
+        <f>IF(OR(E121&lt;&gt;"",J121&lt;&gt;""),"Занято",IF(AND(F120="Повторный приём (1 час)",A120=A121),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4249,10 +4375,11 @@
       <c r="F122" s="23" t="n"/>
       <c r="G122" s="24" t="n"/>
       <c r="H122" s="24" t="n"/>
-      <c r="I122" s="21" t="n"/>
-      <c r="J122" s="25" t="n"/>
-      <c r="K122" s="21">
-        <f>IF(OR(E122&lt;&gt;"",I122&lt;&gt;""),"Занято",IF(AND(F121="Повторный приём (1 час)",A121=A122),"Занято","Свободно"))</f>
+      <c r="I122" s="23" t="n"/>
+      <c r="J122" s="21" t="n"/>
+      <c r="K122" s="25" t="n"/>
+      <c r="L122" s="21">
+        <f>IF(OR(E122&lt;&gt;"",J122&lt;&gt;""),"Занято",IF(AND(F121="Повторный приём (1 час)",A121=A122),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4279,10 +4406,11 @@
       <c r="F123" s="23" t="n"/>
       <c r="G123" s="24" t="n"/>
       <c r="H123" s="24" t="n"/>
-      <c r="I123" s="21" t="n"/>
-      <c r="J123" s="25" t="n"/>
-      <c r="K123" s="21">
-        <f>IF(OR(E123&lt;&gt;"",I123&lt;&gt;""),"Занято",IF(AND(F122="Повторный приём (1 час)",A122=A123),"Занято","Свободно"))</f>
+      <c r="I123" s="23" t="n"/>
+      <c r="J123" s="21" t="n"/>
+      <c r="K123" s="25" t="n"/>
+      <c r="L123" s="21">
+        <f>IF(OR(E123&lt;&gt;"",J123&lt;&gt;""),"Занято",IF(AND(F122="Повторный приём (1 час)",A122=A123),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4309,10 +4437,11 @@
       <c r="F124" s="23" t="n"/>
       <c r="G124" s="24" t="n"/>
       <c r="H124" s="24" t="n"/>
-      <c r="I124" s="21" t="n"/>
-      <c r="J124" s="25" t="n"/>
-      <c r="K124" s="21">
-        <f>IF(OR(E124&lt;&gt;"",I124&lt;&gt;""),"Занято",IF(AND(F123="Повторный приём (1 час)",A123=A124),"Занято","Свободно"))</f>
+      <c r="I124" s="23" t="n"/>
+      <c r="J124" s="21" t="n"/>
+      <c r="K124" s="25" t="n"/>
+      <c r="L124" s="21">
+        <f>IF(OR(E124&lt;&gt;"",J124&lt;&gt;""),"Занято",IF(AND(F123="Повторный приём (1 час)",A123=A124),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4339,10 +4468,11 @@
       <c r="F125" s="23" t="n"/>
       <c r="G125" s="24" t="n"/>
       <c r="H125" s="24" t="n"/>
-      <c r="I125" s="21" t="n"/>
-      <c r="J125" s="25" t="n"/>
-      <c r="K125" s="21">
-        <f>IF(OR(E125&lt;&gt;"",I125&lt;&gt;""),"Занято",IF(AND(F124="Повторный приём (1 час)",A124=A125),"Занято","Свободно"))</f>
+      <c r="I125" s="23" t="n"/>
+      <c r="J125" s="21" t="n"/>
+      <c r="K125" s="25" t="n"/>
+      <c r="L125" s="21">
+        <f>IF(OR(E125&lt;&gt;"",J125&lt;&gt;""),"Занято",IF(AND(F124="Повторный приём (1 час)",A124=A125),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4369,10 +4499,11 @@
       <c r="F126" s="23" t="n"/>
       <c r="G126" s="24" t="n"/>
       <c r="H126" s="24" t="n"/>
-      <c r="I126" s="21" t="n"/>
-      <c r="J126" s="25" t="n"/>
-      <c r="K126" s="21">
-        <f>IF(OR(E126&lt;&gt;"",I126&lt;&gt;""),"Занято",IF(AND(F125="Повторный приём (1 час)",A125=A126),"Занято","Свободно"))</f>
+      <c r="I126" s="23" t="n"/>
+      <c r="J126" s="21" t="n"/>
+      <c r="K126" s="25" t="n"/>
+      <c r="L126" s="21">
+        <f>IF(OR(E126&lt;&gt;"",J126&lt;&gt;""),"Занято",IF(AND(F125="Повторный приём (1 час)",A125=A126),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4399,10 +4530,11 @@
       <c r="F127" s="23" t="n"/>
       <c r="G127" s="24" t="n"/>
       <c r="H127" s="24" t="n"/>
-      <c r="I127" s="21" t="n"/>
-      <c r="J127" s="25" t="n"/>
-      <c r="K127" s="21">
-        <f>IF(OR(E127&lt;&gt;"",I127&lt;&gt;""),"Занято",IF(AND(F126="Повторный приём (1 час)",A126=A127),"Занято","Свободно"))</f>
+      <c r="I127" s="23" t="n"/>
+      <c r="J127" s="21" t="n"/>
+      <c r="K127" s="25" t="n"/>
+      <c r="L127" s="21">
+        <f>IF(OR(E127&lt;&gt;"",J127&lt;&gt;""),"Занято",IF(AND(F126="Повторный приём (1 час)",A126=A127),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4429,10 +4561,11 @@
       <c r="F128" s="23" t="n"/>
       <c r="G128" s="24" t="n"/>
       <c r="H128" s="24" t="n"/>
-      <c r="I128" s="21" t="n"/>
-      <c r="J128" s="25" t="n"/>
-      <c r="K128" s="21">
-        <f>IF(OR(E128&lt;&gt;"",I128&lt;&gt;""),"Занято",IF(AND(F127="Повторный приём (1 час)",A127=A128),"Занято","Свободно"))</f>
+      <c r="I128" s="23" t="n"/>
+      <c r="J128" s="21" t="n"/>
+      <c r="K128" s="25" t="n"/>
+      <c r="L128" s="21">
+        <f>IF(OR(E128&lt;&gt;"",J128&lt;&gt;""),"Занято",IF(AND(F127="Повторный приём (1 час)",A127=A128),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4459,10 +4592,11 @@
       <c r="F129" s="23" t="n"/>
       <c r="G129" s="24" t="n"/>
       <c r="H129" s="24" t="n"/>
-      <c r="I129" s="21" t="n"/>
-      <c r="J129" s="25" t="n"/>
-      <c r="K129" s="21">
-        <f>IF(OR(E129&lt;&gt;"",I129&lt;&gt;""),"Занято",IF(AND(F128="Повторный приём (1 час)",A128=A129),"Занято","Свободно"))</f>
+      <c r="I129" s="23" t="n"/>
+      <c r="J129" s="21" t="n"/>
+      <c r="K129" s="25" t="n"/>
+      <c r="L129" s="21">
+        <f>IF(OR(E129&lt;&gt;"",J129&lt;&gt;""),"Занято",IF(AND(F128="Повторный приём (1 час)",A128=A129),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4489,10 +4623,11 @@
       <c r="F130" s="23" t="n"/>
       <c r="G130" s="24" t="n"/>
       <c r="H130" s="24" t="n"/>
-      <c r="I130" s="21" t="n"/>
-      <c r="J130" s="25" t="n"/>
-      <c r="K130" s="21">
-        <f>IF(OR(E130&lt;&gt;"",I130&lt;&gt;""),"Занято",IF(AND(F129="Повторный приём (1 час)",A129=A130),"Занято","Свободно"))</f>
+      <c r="I130" s="23" t="n"/>
+      <c r="J130" s="21" t="n"/>
+      <c r="K130" s="25" t="n"/>
+      <c r="L130" s="21">
+        <f>IF(OR(E130&lt;&gt;"",J130&lt;&gt;""),"Занято",IF(AND(F129="Повторный приём (1 час)",A129=A130),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4519,10 +4654,11 @@
       <c r="F131" s="23" t="n"/>
       <c r="G131" s="24" t="n"/>
       <c r="H131" s="24" t="n"/>
-      <c r="I131" s="21" t="n"/>
-      <c r="J131" s="25" t="n"/>
-      <c r="K131" s="21">
-        <f>IF(OR(E131&lt;&gt;"",I131&lt;&gt;""),"Занято",IF(AND(F130="Повторный приём (1 час)",A130=A131),"Занято","Свободно"))</f>
+      <c r="I131" s="23" t="n"/>
+      <c r="J131" s="21" t="n"/>
+      <c r="K131" s="25" t="n"/>
+      <c r="L131" s="21">
+        <f>IF(OR(E131&lt;&gt;"",J131&lt;&gt;""),"Занято",IF(AND(F130="Повторный приём (1 час)",A130=A131),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4549,10 +4685,11 @@
       <c r="F132" s="23" t="n"/>
       <c r="G132" s="24" t="n"/>
       <c r="H132" s="24" t="n"/>
-      <c r="I132" s="21" t="n"/>
-      <c r="J132" s="25" t="n"/>
-      <c r="K132" s="21">
-        <f>IF(OR(E132&lt;&gt;"",I132&lt;&gt;""),"Занято",IF(AND(F131="Повторный приём (1 час)",A131=A132),"Занято","Свободно"))</f>
+      <c r="I132" s="23" t="n"/>
+      <c r="J132" s="21" t="n"/>
+      <c r="K132" s="25" t="n"/>
+      <c r="L132" s="21">
+        <f>IF(OR(E132&lt;&gt;"",J132&lt;&gt;""),"Занято",IF(AND(F131="Повторный приём (1 час)",A131=A132),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4579,10 +4716,11 @@
       <c r="F133" s="23" t="n"/>
       <c r="G133" s="24" t="n"/>
       <c r="H133" s="24" t="n"/>
-      <c r="I133" s="21" t="n"/>
-      <c r="J133" s="25" t="n"/>
-      <c r="K133" s="21">
-        <f>IF(OR(E133&lt;&gt;"",I133&lt;&gt;""),"Занято",IF(AND(F132="Повторный приём (1 час)",A132=A133),"Занято","Свободно"))</f>
+      <c r="I133" s="23" t="n"/>
+      <c r="J133" s="21" t="n"/>
+      <c r="K133" s="25" t="n"/>
+      <c r="L133" s="21">
+        <f>IF(OR(E133&lt;&gt;"",J133&lt;&gt;""),"Занято",IF(AND(F132="Повторный приём (1 час)",A132=A133),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4609,10 +4747,11 @@
       <c r="F134" s="23" t="n"/>
       <c r="G134" s="24" t="n"/>
       <c r="H134" s="24" t="n"/>
-      <c r="I134" s="21" t="n"/>
-      <c r="J134" s="25" t="n"/>
-      <c r="K134" s="21">
-        <f>IF(OR(E134&lt;&gt;"",I134&lt;&gt;""),"Занято",IF(AND(F133="Повторный приём (1 час)",A133=A134),"Занято","Свободно"))</f>
+      <c r="I134" s="23" t="n"/>
+      <c r="J134" s="21" t="n"/>
+      <c r="K134" s="25" t="n"/>
+      <c r="L134" s="21">
+        <f>IF(OR(E134&lt;&gt;"",J134&lt;&gt;""),"Занято",IF(AND(F133="Повторный приём (1 час)",A133=A134),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4639,10 +4778,11 @@
       <c r="F135" s="23" t="n"/>
       <c r="G135" s="24" t="n"/>
       <c r="H135" s="24" t="n"/>
-      <c r="I135" s="21" t="n"/>
-      <c r="J135" s="25" t="n"/>
-      <c r="K135" s="21">
-        <f>IF(OR(E135&lt;&gt;"",I135&lt;&gt;""),"Занято",IF(AND(F134="Повторный приём (1 час)",A134=A135),"Занято","Свободно"))</f>
+      <c r="I135" s="23" t="n"/>
+      <c r="J135" s="21" t="n"/>
+      <c r="K135" s="25" t="n"/>
+      <c r="L135" s="21">
+        <f>IF(OR(E135&lt;&gt;"",J135&lt;&gt;""),"Занято",IF(AND(F134="Повторный приём (1 час)",A134=A135),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4669,10 +4809,11 @@
       <c r="F136" s="5" t="n"/>
       <c r="G136" s="6" t="n"/>
       <c r="H136" s="6" t="n"/>
-      <c r="I136" s="3" t="n"/>
-      <c r="J136" s="7" t="n"/>
-      <c r="K136" s="3">
-        <f>IF(OR(E136&lt;&gt;"",I136&lt;&gt;""),"Занято",IF(AND(F135="Повторный приём (1 час)",A135=A136),"Занято","Свободно"))</f>
+      <c r="I136" s="5" t="n"/>
+      <c r="J136" s="3" t="n"/>
+      <c r="K136" s="7" t="n"/>
+      <c r="L136" s="3">
+        <f>IF(OR(E136&lt;&gt;"",J136&lt;&gt;""),"Занято",IF(AND(F135="Повторный приём (1 час)",A135=A136),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4699,10 +4840,11 @@
       <c r="F137" s="11" t="n"/>
       <c r="G137" s="12" t="n"/>
       <c r="H137" s="12" t="n"/>
-      <c r="I137" s="9" t="n"/>
-      <c r="J137" s="13" t="n"/>
-      <c r="K137" s="9">
-        <f>IF(OR(E137&lt;&gt;"",I137&lt;&gt;""),"Занято",IF(AND(F136="Повторный приём (1 час)",A136=A137),"Занято","Свободно"))</f>
+      <c r="I137" s="11" t="n"/>
+      <c r="J137" s="9" t="n"/>
+      <c r="K137" s="13" t="n"/>
+      <c r="L137" s="9">
+        <f>IF(OR(E137&lt;&gt;"",J137&lt;&gt;""),"Занято",IF(AND(F136="Повторный приём (1 час)",A136=A137),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4729,10 +4871,11 @@
       <c r="F138" s="11" t="n"/>
       <c r="G138" s="12" t="n"/>
       <c r="H138" s="12" t="n"/>
-      <c r="I138" s="9" t="n"/>
-      <c r="J138" s="13" t="n"/>
-      <c r="K138" s="9">
-        <f>IF(OR(E138&lt;&gt;"",I138&lt;&gt;""),"Занято",IF(AND(F137="Повторный приём (1 час)",A137=A138),"Занято","Свободно"))</f>
+      <c r="I138" s="11" t="n"/>
+      <c r="J138" s="9" t="n"/>
+      <c r="K138" s="13" t="n"/>
+      <c r="L138" s="9">
+        <f>IF(OR(E138&lt;&gt;"",J138&lt;&gt;""),"Занято",IF(AND(F137="Повторный приём (1 час)",A137=A138),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4759,10 +4902,11 @@
       <c r="F139" s="11" t="n"/>
       <c r="G139" s="12" t="n"/>
       <c r="H139" s="12" t="n"/>
-      <c r="I139" s="9" t="n"/>
-      <c r="J139" s="13" t="n"/>
-      <c r="K139" s="9">
-        <f>IF(OR(E139&lt;&gt;"",I139&lt;&gt;""),"Занято",IF(AND(F138="Повторный приём (1 час)",A138=A139),"Занято","Свободно"))</f>
+      <c r="I139" s="11" t="n"/>
+      <c r="J139" s="9" t="n"/>
+      <c r="K139" s="13" t="n"/>
+      <c r="L139" s="9">
+        <f>IF(OR(E139&lt;&gt;"",J139&lt;&gt;""),"Занято",IF(AND(F138="Повторный приём (1 час)",A138=A139),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4789,10 +4933,11 @@
       <c r="F140" s="11" t="n"/>
       <c r="G140" s="12" t="n"/>
       <c r="H140" s="12" t="n"/>
-      <c r="I140" s="9" t="n"/>
-      <c r="J140" s="13" t="n"/>
-      <c r="K140" s="9">
-        <f>IF(OR(E140&lt;&gt;"",I140&lt;&gt;""),"Занято",IF(AND(F139="Повторный приём (1 час)",A139=A140),"Занято","Свободно"))</f>
+      <c r="I140" s="11" t="n"/>
+      <c r="J140" s="9" t="n"/>
+      <c r="K140" s="13" t="n"/>
+      <c r="L140" s="9">
+        <f>IF(OR(E140&lt;&gt;"",J140&lt;&gt;""),"Занято",IF(AND(F139="Повторный приём (1 час)",A139=A140),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4819,10 +4964,11 @@
       <c r="F141" s="11" t="n"/>
       <c r="G141" s="12" t="n"/>
       <c r="H141" s="12" t="n"/>
-      <c r="I141" s="9" t="n"/>
-      <c r="J141" s="13" t="n"/>
-      <c r="K141" s="9">
-        <f>IF(OR(E141&lt;&gt;"",I141&lt;&gt;""),"Занято",IF(AND(F140="Повторный приём (1 час)",A140=A141),"Занято","Свободно"))</f>
+      <c r="I141" s="11" t="n"/>
+      <c r="J141" s="9" t="n"/>
+      <c r="K141" s="13" t="n"/>
+      <c r="L141" s="9">
+        <f>IF(OR(E141&lt;&gt;"",J141&lt;&gt;""),"Занято",IF(AND(F140="Повторный приём (1 час)",A140=A141),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4849,10 +4995,11 @@
       <c r="F142" s="11" t="n"/>
       <c r="G142" s="12" t="n"/>
       <c r="H142" s="12" t="n"/>
-      <c r="I142" s="9" t="n"/>
-      <c r="J142" s="13" t="n"/>
-      <c r="K142" s="9">
-        <f>IF(OR(E142&lt;&gt;"",I142&lt;&gt;""),"Занято",IF(AND(F141="Повторный приём (1 час)",A141=A142),"Занято","Свободно"))</f>
+      <c r="I142" s="11" t="n"/>
+      <c r="J142" s="9" t="n"/>
+      <c r="K142" s="13" t="n"/>
+      <c r="L142" s="9">
+        <f>IF(OR(E142&lt;&gt;"",J142&lt;&gt;""),"Занято",IF(AND(F141="Повторный приём (1 час)",A141=A142),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4879,10 +5026,11 @@
       <c r="F143" s="11" t="n"/>
       <c r="G143" s="12" t="n"/>
       <c r="H143" s="12" t="n"/>
-      <c r="I143" s="9" t="n"/>
-      <c r="J143" s="13" t="n"/>
-      <c r="K143" s="9">
-        <f>IF(OR(E143&lt;&gt;"",I143&lt;&gt;""),"Занято",IF(AND(F142="Повторный приём (1 час)",A142=A143),"Занято","Свободно"))</f>
+      <c r="I143" s="11" t="n"/>
+      <c r="J143" s="9" t="n"/>
+      <c r="K143" s="13" t="n"/>
+      <c r="L143" s="9">
+        <f>IF(OR(E143&lt;&gt;"",J143&lt;&gt;""),"Занято",IF(AND(F142="Повторный приём (1 час)",A142=A143),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4909,10 +5057,11 @@
       <c r="F144" s="17" t="n"/>
       <c r="G144" s="18" t="n"/>
       <c r="H144" s="18" t="n"/>
-      <c r="I144" s="15" t="n"/>
-      <c r="J144" s="19" t="n"/>
-      <c r="K144" s="15">
-        <f>IF(OR(E144&lt;&gt;"",I144&lt;&gt;""),"Занято",IF(AND(F143="Повторный приём (1 час)",A143=A144),"Занято","Свободно"))</f>
+      <c r="I144" s="17" t="n"/>
+      <c r="J144" s="15" t="n"/>
+      <c r="K144" s="19" t="n"/>
+      <c r="L144" s="15">
+        <f>IF(OR(E144&lt;&gt;"",J144&lt;&gt;""),"Занято",IF(AND(F143="Повторный приём (1 час)",A143=A144),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4939,10 +5088,11 @@
       <c r="F145" s="23" t="n"/>
       <c r="G145" s="24" t="n"/>
       <c r="H145" s="24" t="n"/>
-      <c r="I145" s="21" t="n"/>
-      <c r="J145" s="25" t="n"/>
-      <c r="K145" s="21">
-        <f>IF(OR(E145&lt;&gt;"",I145&lt;&gt;""),"Занято",IF(AND(F144="Повторный приём (1 час)",A144=A145),"Занято","Свободно"))</f>
+      <c r="I145" s="23" t="n"/>
+      <c r="J145" s="21" t="n"/>
+      <c r="K145" s="25" t="n"/>
+      <c r="L145" s="21">
+        <f>IF(OR(E145&lt;&gt;"",J145&lt;&gt;""),"Занято",IF(AND(F144="Повторный приём (1 час)",A144=A145),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4969,10 +5119,11 @@
       <c r="F146" s="23" t="n"/>
       <c r="G146" s="24" t="n"/>
       <c r="H146" s="24" t="n"/>
-      <c r="I146" s="21" t="n"/>
-      <c r="J146" s="25" t="n"/>
-      <c r="K146" s="21">
-        <f>IF(OR(E146&lt;&gt;"",I146&lt;&gt;""),"Занято",IF(AND(F145="Повторный приём (1 час)",A145=A146),"Занято","Свободно"))</f>
+      <c r="I146" s="23" t="n"/>
+      <c r="J146" s="21" t="n"/>
+      <c r="K146" s="25" t="n"/>
+      <c r="L146" s="21">
+        <f>IF(OR(E146&lt;&gt;"",J146&lt;&gt;""),"Занято",IF(AND(F145="Повторный приём (1 час)",A145=A146),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -4999,10 +5150,11 @@
       <c r="F147" s="23" t="n"/>
       <c r="G147" s="24" t="n"/>
       <c r="H147" s="24" t="n"/>
-      <c r="I147" s="21" t="n"/>
-      <c r="J147" s="25" t="n"/>
-      <c r="K147" s="21">
-        <f>IF(OR(E147&lt;&gt;"",I147&lt;&gt;""),"Занято",IF(AND(F146="Повторный приём (1 час)",A146=A147),"Занято","Свободно"))</f>
+      <c r="I147" s="23" t="n"/>
+      <c r="J147" s="21" t="n"/>
+      <c r="K147" s="25" t="n"/>
+      <c r="L147" s="21">
+        <f>IF(OR(E147&lt;&gt;"",J147&lt;&gt;""),"Занято",IF(AND(F146="Повторный приём (1 час)",A146=A147),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5029,10 +5181,11 @@
       <c r="F148" s="23" t="n"/>
       <c r="G148" s="24" t="n"/>
       <c r="H148" s="24" t="n"/>
-      <c r="I148" s="21" t="n"/>
-      <c r="J148" s="25" t="n"/>
-      <c r="K148" s="21">
-        <f>IF(OR(E148&lt;&gt;"",I148&lt;&gt;""),"Занято",IF(AND(F147="Повторный приём (1 час)",A147=A148),"Занято","Свободно"))</f>
+      <c r="I148" s="23" t="n"/>
+      <c r="J148" s="21" t="n"/>
+      <c r="K148" s="25" t="n"/>
+      <c r="L148" s="21">
+        <f>IF(OR(E148&lt;&gt;"",J148&lt;&gt;""),"Занято",IF(AND(F147="Повторный приём (1 час)",A147=A148),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5059,10 +5212,11 @@
       <c r="F149" s="23" t="n"/>
       <c r="G149" s="24" t="n"/>
       <c r="H149" s="24" t="n"/>
-      <c r="I149" s="21" t="n"/>
-      <c r="J149" s="25" t="n"/>
-      <c r="K149" s="21">
-        <f>IF(OR(E149&lt;&gt;"",I149&lt;&gt;""),"Занято",IF(AND(F148="Повторный приём (1 час)",A148=A149),"Занято","Свободно"))</f>
+      <c r="I149" s="23" t="n"/>
+      <c r="J149" s="21" t="n"/>
+      <c r="K149" s="25" t="n"/>
+      <c r="L149" s="21">
+        <f>IF(OR(E149&lt;&gt;"",J149&lt;&gt;""),"Занято",IF(AND(F148="Повторный приём (1 час)",A148=A149),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5089,10 +5243,11 @@
       <c r="F150" s="23" t="n"/>
       <c r="G150" s="24" t="n"/>
       <c r="H150" s="24" t="n"/>
-      <c r="I150" s="21" t="n"/>
-      <c r="J150" s="25" t="n"/>
-      <c r="K150" s="21">
-        <f>IF(OR(E150&lt;&gt;"",I150&lt;&gt;""),"Занято",IF(AND(F149="Повторный приём (1 час)",A149=A150),"Занято","Свободно"))</f>
+      <c r="I150" s="23" t="n"/>
+      <c r="J150" s="21" t="n"/>
+      <c r="K150" s="25" t="n"/>
+      <c r="L150" s="21">
+        <f>IF(OR(E150&lt;&gt;"",J150&lt;&gt;""),"Занято",IF(AND(F149="Повторный приём (1 час)",A149=A150),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5119,10 +5274,11 @@
       <c r="F151" s="23" t="n"/>
       <c r="G151" s="24" t="n"/>
       <c r="H151" s="24" t="n"/>
-      <c r="I151" s="21" t="n"/>
-      <c r="J151" s="25" t="n"/>
-      <c r="K151" s="21">
-        <f>IF(OR(E151&lt;&gt;"",I151&lt;&gt;""),"Занято",IF(AND(F150="Повторный приём (1 час)",A150=A151),"Занято","Свободно"))</f>
+      <c r="I151" s="23" t="n"/>
+      <c r="J151" s="21" t="n"/>
+      <c r="K151" s="25" t="n"/>
+      <c r="L151" s="21">
+        <f>IF(OR(E151&lt;&gt;"",J151&lt;&gt;""),"Занято",IF(AND(F150="Повторный приём (1 час)",A150=A151),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5149,10 +5305,11 @@
       <c r="F152" s="23" t="n"/>
       <c r="G152" s="24" t="n"/>
       <c r="H152" s="24" t="n"/>
-      <c r="I152" s="21" t="n"/>
-      <c r="J152" s="25" t="n"/>
-      <c r="K152" s="21">
-        <f>IF(OR(E152&lt;&gt;"",I152&lt;&gt;""),"Занято",IF(AND(F151="Повторный приём (1 час)",A151=A152),"Занято","Свободно"))</f>
+      <c r="I152" s="23" t="n"/>
+      <c r="J152" s="21" t="n"/>
+      <c r="K152" s="25" t="n"/>
+      <c r="L152" s="21">
+        <f>IF(OR(E152&lt;&gt;"",J152&lt;&gt;""),"Занято",IF(AND(F151="Повторный приём (1 час)",A151=A152),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5179,10 +5336,11 @@
       <c r="F153" s="23" t="n"/>
       <c r="G153" s="24" t="n"/>
       <c r="H153" s="24" t="n"/>
-      <c r="I153" s="21" t="n"/>
-      <c r="J153" s="25" t="n"/>
-      <c r="K153" s="21">
-        <f>IF(OR(E153&lt;&gt;"",I153&lt;&gt;""),"Занято",IF(AND(F152="Повторный приём (1 час)",A152=A153),"Занято","Свободно"))</f>
+      <c r="I153" s="23" t="n"/>
+      <c r="J153" s="21" t="n"/>
+      <c r="K153" s="25" t="n"/>
+      <c r="L153" s="21">
+        <f>IF(OR(E153&lt;&gt;"",J153&lt;&gt;""),"Занято",IF(AND(F152="Повторный приём (1 час)",A152=A153),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5209,10 +5367,11 @@
       <c r="F154" s="23" t="n"/>
       <c r="G154" s="24" t="n"/>
       <c r="H154" s="24" t="n"/>
-      <c r="I154" s="21" t="n"/>
-      <c r="J154" s="25" t="n"/>
-      <c r="K154" s="21">
-        <f>IF(OR(E154&lt;&gt;"",I154&lt;&gt;""),"Занято",IF(AND(F153="Повторный приём (1 час)",A153=A154),"Занято","Свободно"))</f>
+      <c r="I154" s="23" t="n"/>
+      <c r="J154" s="21" t="n"/>
+      <c r="K154" s="25" t="n"/>
+      <c r="L154" s="21">
+        <f>IF(OR(E154&lt;&gt;"",J154&lt;&gt;""),"Занято",IF(AND(F153="Повторный приём (1 час)",A153=A154),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5239,10 +5398,11 @@
       <c r="F155" s="23" t="n"/>
       <c r="G155" s="24" t="n"/>
       <c r="H155" s="24" t="n"/>
-      <c r="I155" s="21" t="n"/>
-      <c r="J155" s="25" t="n"/>
-      <c r="K155" s="21">
-        <f>IF(OR(E155&lt;&gt;"",I155&lt;&gt;""),"Занято",IF(AND(F154="Повторный приём (1 час)",A154=A155),"Занято","Свободно"))</f>
+      <c r="I155" s="23" t="n"/>
+      <c r="J155" s="21" t="n"/>
+      <c r="K155" s="25" t="n"/>
+      <c r="L155" s="21">
+        <f>IF(OR(E155&lt;&gt;"",J155&lt;&gt;""),"Занято",IF(AND(F154="Повторный приём (1 час)",A154=A155),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5269,10 +5429,11 @@
       <c r="F156" s="23" t="n"/>
       <c r="G156" s="24" t="n"/>
       <c r="H156" s="24" t="n"/>
-      <c r="I156" s="21" t="n"/>
-      <c r="J156" s="25" t="n"/>
-      <c r="K156" s="21">
-        <f>IF(OR(E156&lt;&gt;"",I156&lt;&gt;""),"Занято",IF(AND(F155="Повторный приём (1 час)",A155=A156),"Занято","Свободно"))</f>
+      <c r="I156" s="23" t="n"/>
+      <c r="J156" s="21" t="n"/>
+      <c r="K156" s="25" t="n"/>
+      <c r="L156" s="21">
+        <f>IF(OR(E156&lt;&gt;"",J156&lt;&gt;""),"Занято",IF(AND(F155="Повторный приём (1 час)",A155=A156),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5299,10 +5460,11 @@
       <c r="F157" s="23" t="n"/>
       <c r="G157" s="24" t="n"/>
       <c r="H157" s="24" t="n"/>
-      <c r="I157" s="21" t="n"/>
-      <c r="J157" s="25" t="n"/>
-      <c r="K157" s="21">
-        <f>IF(OR(E157&lt;&gt;"",I157&lt;&gt;""),"Занято",IF(AND(F156="Повторный приём (1 час)",A156=A157),"Занято","Свободно"))</f>
+      <c r="I157" s="23" t="n"/>
+      <c r="J157" s="21" t="n"/>
+      <c r="K157" s="25" t="n"/>
+      <c r="L157" s="21">
+        <f>IF(OR(E157&lt;&gt;"",J157&lt;&gt;""),"Занято",IF(AND(F156="Повторный приём (1 час)",A156=A157),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5329,10 +5491,11 @@
       <c r="F158" s="23" t="n"/>
       <c r="G158" s="24" t="n"/>
       <c r="H158" s="24" t="n"/>
-      <c r="I158" s="21" t="n"/>
-      <c r="J158" s="25" t="n"/>
-      <c r="K158" s="21">
-        <f>IF(OR(E158&lt;&gt;"",I158&lt;&gt;""),"Занято",IF(AND(F157="Повторный приём (1 час)",A157=A158),"Занято","Свободно"))</f>
+      <c r="I158" s="23" t="n"/>
+      <c r="J158" s="21" t="n"/>
+      <c r="K158" s="25" t="n"/>
+      <c r="L158" s="21">
+        <f>IF(OR(E158&lt;&gt;"",J158&lt;&gt;""),"Занято",IF(AND(F157="Повторный приём (1 час)",A157=A158),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5359,10 +5522,11 @@
       <c r="F159" s="23" t="n"/>
       <c r="G159" s="24" t="n"/>
       <c r="H159" s="24" t="n"/>
-      <c r="I159" s="21" t="n"/>
-      <c r="J159" s="25" t="n"/>
-      <c r="K159" s="21">
-        <f>IF(OR(E159&lt;&gt;"",I159&lt;&gt;""),"Занято",IF(AND(F158="Повторный приём (1 час)",A158=A159),"Занято","Свободно"))</f>
+      <c r="I159" s="23" t="n"/>
+      <c r="J159" s="21" t="n"/>
+      <c r="K159" s="25" t="n"/>
+      <c r="L159" s="21">
+        <f>IF(OR(E159&lt;&gt;"",J159&lt;&gt;""),"Занято",IF(AND(F158="Повторный приём (1 час)",A158=A159),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5389,10 +5553,11 @@
       <c r="F160" s="23" t="n"/>
       <c r="G160" s="24" t="n"/>
       <c r="H160" s="24" t="n"/>
-      <c r="I160" s="21" t="n"/>
-      <c r="J160" s="25" t="n"/>
-      <c r="K160" s="21">
-        <f>IF(OR(E160&lt;&gt;"",I160&lt;&gt;""),"Занято",IF(AND(F159="Повторный приём (1 час)",A159=A160),"Занято","Свободно"))</f>
+      <c r="I160" s="23" t="n"/>
+      <c r="J160" s="21" t="n"/>
+      <c r="K160" s="25" t="n"/>
+      <c r="L160" s="21">
+        <f>IF(OR(E160&lt;&gt;"",J160&lt;&gt;""),"Занято",IF(AND(F159="Повторный приём (1 час)",A159=A160),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5419,10 +5584,11 @@
       <c r="F161" s="23" t="n"/>
       <c r="G161" s="24" t="n"/>
       <c r="H161" s="24" t="n"/>
-      <c r="I161" s="21" t="n"/>
-      <c r="J161" s="25" t="n"/>
-      <c r="K161" s="21">
-        <f>IF(OR(E161&lt;&gt;"",I161&lt;&gt;""),"Занято",IF(AND(F160="Повторный приём (1 час)",A160=A161),"Занято","Свободно"))</f>
+      <c r="I161" s="23" t="n"/>
+      <c r="J161" s="21" t="n"/>
+      <c r="K161" s="25" t="n"/>
+      <c r="L161" s="21">
+        <f>IF(OR(E161&lt;&gt;"",J161&lt;&gt;""),"Занято",IF(AND(F160="Повторный приём (1 час)",A160=A161),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5449,10 +5615,11 @@
       <c r="F162" s="5" t="n"/>
       <c r="G162" s="6" t="n"/>
       <c r="H162" s="6" t="n"/>
-      <c r="I162" s="3" t="n"/>
-      <c r="J162" s="7" t="n"/>
-      <c r="K162" s="3">
-        <f>IF(OR(E162&lt;&gt;"",I162&lt;&gt;""),"Занято",IF(AND(F161="Повторный приём (1 час)",A161=A162),"Занято","Свободно"))</f>
+      <c r="I162" s="5" t="n"/>
+      <c r="J162" s="3" t="n"/>
+      <c r="K162" s="7" t="n"/>
+      <c r="L162" s="3">
+        <f>IF(OR(E162&lt;&gt;"",J162&lt;&gt;""),"Занято",IF(AND(F161="Повторный приём (1 час)",A161=A162),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5479,10 +5646,11 @@
       <c r="F163" s="11" t="n"/>
       <c r="G163" s="12" t="n"/>
       <c r="H163" s="12" t="n"/>
-      <c r="I163" s="9" t="n"/>
-      <c r="J163" s="13" t="n"/>
-      <c r="K163" s="9">
-        <f>IF(OR(E163&lt;&gt;"",I163&lt;&gt;""),"Занято",IF(AND(F162="Повторный приём (1 час)",A162=A163),"Занято","Свободно"))</f>
+      <c r="I163" s="11" t="n"/>
+      <c r="J163" s="9" t="n"/>
+      <c r="K163" s="13" t="n"/>
+      <c r="L163" s="9">
+        <f>IF(OR(E163&lt;&gt;"",J163&lt;&gt;""),"Занято",IF(AND(F162="Повторный приём (1 час)",A162=A163),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5509,10 +5677,11 @@
       <c r="F164" s="11" t="n"/>
       <c r="G164" s="12" t="n"/>
       <c r="H164" s="12" t="n"/>
-      <c r="I164" s="9" t="n"/>
-      <c r="J164" s="13" t="n"/>
-      <c r="K164" s="9">
-        <f>IF(OR(E164&lt;&gt;"",I164&lt;&gt;""),"Занято",IF(AND(F163="Повторный приём (1 час)",A163=A164),"Занято","Свободно"))</f>
+      <c r="I164" s="11" t="n"/>
+      <c r="J164" s="9" t="n"/>
+      <c r="K164" s="13" t="n"/>
+      <c r="L164" s="9">
+        <f>IF(OR(E164&lt;&gt;"",J164&lt;&gt;""),"Занято",IF(AND(F163="Повторный приём (1 час)",A163=A164),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5539,10 +5708,11 @@
       <c r="F165" s="11" t="n"/>
       <c r="G165" s="12" t="n"/>
       <c r="H165" s="12" t="n"/>
-      <c r="I165" s="9" t="n"/>
-      <c r="J165" s="13" t="n"/>
-      <c r="K165" s="9">
-        <f>IF(OR(E165&lt;&gt;"",I165&lt;&gt;""),"Занято",IF(AND(F164="Повторный приём (1 час)",A164=A165),"Занято","Свободно"))</f>
+      <c r="I165" s="11" t="n"/>
+      <c r="J165" s="9" t="n"/>
+      <c r="K165" s="13" t="n"/>
+      <c r="L165" s="9">
+        <f>IF(OR(E165&lt;&gt;"",J165&lt;&gt;""),"Занято",IF(AND(F164="Повторный приём (1 час)",A164=A165),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5569,10 +5739,11 @@
       <c r="F166" s="11" t="n"/>
       <c r="G166" s="12" t="n"/>
       <c r="H166" s="12" t="n"/>
-      <c r="I166" s="9" t="n"/>
-      <c r="J166" s="13" t="n"/>
-      <c r="K166" s="9">
-        <f>IF(OR(E166&lt;&gt;"",I166&lt;&gt;""),"Занято",IF(AND(F165="Повторный приём (1 час)",A165=A166),"Занято","Свободно"))</f>
+      <c r="I166" s="11" t="n"/>
+      <c r="J166" s="9" t="n"/>
+      <c r="K166" s="13" t="n"/>
+      <c r="L166" s="9">
+        <f>IF(OR(E166&lt;&gt;"",J166&lt;&gt;""),"Занято",IF(AND(F165="Повторный приём (1 час)",A165=A166),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5599,10 +5770,11 @@
       <c r="F167" s="11" t="n"/>
       <c r="G167" s="12" t="n"/>
       <c r="H167" s="12" t="n"/>
-      <c r="I167" s="9" t="n"/>
-      <c r="J167" s="13" t="n"/>
-      <c r="K167" s="9">
-        <f>IF(OR(E167&lt;&gt;"",I167&lt;&gt;""),"Занято",IF(AND(F166="Повторный приём (1 час)",A166=A167),"Занято","Свободно"))</f>
+      <c r="I167" s="11" t="n"/>
+      <c r="J167" s="9" t="n"/>
+      <c r="K167" s="13" t="n"/>
+      <c r="L167" s="9">
+        <f>IF(OR(E167&lt;&gt;"",J167&lt;&gt;""),"Занято",IF(AND(F166="Повторный приём (1 час)",A166=A167),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5629,10 +5801,11 @@
       <c r="F168" s="11" t="n"/>
       <c r="G168" s="12" t="n"/>
       <c r="H168" s="12" t="n"/>
-      <c r="I168" s="9" t="n"/>
-      <c r="J168" s="13" t="n"/>
-      <c r="K168" s="9">
-        <f>IF(OR(E168&lt;&gt;"",I168&lt;&gt;""),"Занято",IF(AND(F167="Повторный приём (1 час)",A167=A168),"Занято","Свободно"))</f>
+      <c r="I168" s="11" t="n"/>
+      <c r="J168" s="9" t="n"/>
+      <c r="K168" s="13" t="n"/>
+      <c r="L168" s="9">
+        <f>IF(OR(E168&lt;&gt;"",J168&lt;&gt;""),"Занято",IF(AND(F167="Повторный приём (1 час)",A167=A168),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5659,10 +5832,11 @@
       <c r="F169" s="11" t="n"/>
       <c r="G169" s="12" t="n"/>
       <c r="H169" s="12" t="n"/>
-      <c r="I169" s="9" t="n"/>
-      <c r="J169" s="13" t="n"/>
-      <c r="K169" s="9">
-        <f>IF(OR(E169&lt;&gt;"",I169&lt;&gt;""),"Занято",IF(AND(F168="Повторный приём (1 час)",A168=A169),"Занято","Свободно"))</f>
+      <c r="I169" s="11" t="n"/>
+      <c r="J169" s="9" t="n"/>
+      <c r="K169" s="13" t="n"/>
+      <c r="L169" s="9">
+        <f>IF(OR(E169&lt;&gt;"",J169&lt;&gt;""),"Занято",IF(AND(F168="Повторный приём (1 час)",A168=A169),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5689,10 +5863,11 @@
       <c r="F170" s="11" t="n"/>
       <c r="G170" s="12" t="n"/>
       <c r="H170" s="12" t="n"/>
-      <c r="I170" s="9" t="n"/>
-      <c r="J170" s="13" t="n"/>
-      <c r="K170" s="9">
-        <f>IF(OR(E170&lt;&gt;"",I170&lt;&gt;""),"Занято",IF(AND(F169="Повторный приём (1 час)",A169=A170),"Занято","Свободно"))</f>
+      <c r="I170" s="11" t="n"/>
+      <c r="J170" s="9" t="n"/>
+      <c r="K170" s="13" t="n"/>
+      <c r="L170" s="9">
+        <f>IF(OR(E170&lt;&gt;"",J170&lt;&gt;""),"Занято",IF(AND(F169="Повторный приём (1 час)",A169=A170),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5719,10 +5894,11 @@
       <c r="F171" s="11" t="n"/>
       <c r="G171" s="12" t="n"/>
       <c r="H171" s="12" t="n"/>
-      <c r="I171" s="9" t="n"/>
-      <c r="J171" s="13" t="n"/>
-      <c r="K171" s="9">
-        <f>IF(OR(E171&lt;&gt;"",I171&lt;&gt;""),"Занято",IF(AND(F170="Повторный приём (1 час)",A170=A171),"Занято","Свободно"))</f>
+      <c r="I171" s="11" t="n"/>
+      <c r="J171" s="9" t="n"/>
+      <c r="K171" s="13" t="n"/>
+      <c r="L171" s="9">
+        <f>IF(OR(E171&lt;&gt;"",J171&lt;&gt;""),"Занято",IF(AND(F170="Повторный приём (1 час)",A170=A171),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5749,10 +5925,11 @@
       <c r="F172" s="11" t="n"/>
       <c r="G172" s="12" t="n"/>
       <c r="H172" s="12" t="n"/>
-      <c r="I172" s="9" t="n"/>
-      <c r="J172" s="13" t="n"/>
-      <c r="K172" s="9">
-        <f>IF(OR(E172&lt;&gt;"",I172&lt;&gt;""),"Занято",IF(AND(F171="Повторный приём (1 час)",A171=A172),"Занято","Свободно"))</f>
+      <c r="I172" s="11" t="n"/>
+      <c r="J172" s="9" t="n"/>
+      <c r="K172" s="13" t="n"/>
+      <c r="L172" s="9">
+        <f>IF(OR(E172&lt;&gt;"",J172&lt;&gt;""),"Занято",IF(AND(F171="Повторный приём (1 час)",A171=A172),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5779,10 +5956,11 @@
       <c r="F173" s="11" t="n"/>
       <c r="G173" s="12" t="n"/>
       <c r="H173" s="12" t="n"/>
-      <c r="I173" s="9" t="n"/>
-      <c r="J173" s="13" t="n"/>
-      <c r="K173" s="9">
-        <f>IF(OR(E173&lt;&gt;"",I173&lt;&gt;""),"Занято",IF(AND(F172="Повторный приём (1 час)",A172=A173),"Занято","Свободно"))</f>
+      <c r="I173" s="11" t="n"/>
+      <c r="J173" s="9" t="n"/>
+      <c r="K173" s="13" t="n"/>
+      <c r="L173" s="9">
+        <f>IF(OR(E173&lt;&gt;"",J173&lt;&gt;""),"Занято",IF(AND(F172="Повторный приём (1 час)",A172=A173),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5809,10 +5987,11 @@
       <c r="F174" s="11" t="n"/>
       <c r="G174" s="12" t="n"/>
       <c r="H174" s="12" t="n"/>
-      <c r="I174" s="9" t="n"/>
-      <c r="J174" s="13" t="n"/>
-      <c r="K174" s="9">
-        <f>IF(OR(E174&lt;&gt;"",I174&lt;&gt;""),"Занято",IF(AND(F173="Повторный приём (1 час)",A173=A174),"Занято","Свободно"))</f>
+      <c r="I174" s="11" t="n"/>
+      <c r="J174" s="9" t="n"/>
+      <c r="K174" s="13" t="n"/>
+      <c r="L174" s="9">
+        <f>IF(OR(E174&lt;&gt;"",J174&lt;&gt;""),"Занято",IF(AND(F173="Повторный приём (1 час)",A173=A174),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5839,10 +6018,11 @@
       <c r="F175" s="11" t="n"/>
       <c r="G175" s="12" t="n"/>
       <c r="H175" s="12" t="n"/>
-      <c r="I175" s="9" t="n"/>
-      <c r="J175" s="13" t="n"/>
-      <c r="K175" s="9">
-        <f>IF(OR(E175&lt;&gt;"",I175&lt;&gt;""),"Занято",IF(AND(F174="Повторный приём (1 час)",A174=A175),"Занято","Свободно"))</f>
+      <c r="I175" s="11" t="n"/>
+      <c r="J175" s="9" t="n"/>
+      <c r="K175" s="13" t="n"/>
+      <c r="L175" s="9">
+        <f>IF(OR(E175&lt;&gt;"",J175&lt;&gt;""),"Занято",IF(AND(F174="Повторный приём (1 час)",A174=A175),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5869,10 +6049,11 @@
       <c r="F176" s="11" t="n"/>
       <c r="G176" s="12" t="n"/>
       <c r="H176" s="12" t="n"/>
-      <c r="I176" s="9" t="n"/>
-      <c r="J176" s="13" t="n"/>
-      <c r="K176" s="9">
-        <f>IF(OR(E176&lt;&gt;"",I176&lt;&gt;""),"Занято",IF(AND(F175="Повторный приём (1 час)",A175=A176),"Занято","Свободно"))</f>
+      <c r="I176" s="11" t="n"/>
+      <c r="J176" s="9" t="n"/>
+      <c r="K176" s="13" t="n"/>
+      <c r="L176" s="9">
+        <f>IF(OR(E176&lt;&gt;"",J176&lt;&gt;""),"Занято",IF(AND(F175="Повторный приём (1 час)",A175=A176),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5899,10 +6080,11 @@
       <c r="F177" s="11" t="n"/>
       <c r="G177" s="12" t="n"/>
       <c r="H177" s="12" t="n"/>
-      <c r="I177" s="9" t="n"/>
-      <c r="J177" s="13" t="n"/>
-      <c r="K177" s="9">
-        <f>IF(OR(E177&lt;&gt;"",I177&lt;&gt;""),"Занято",IF(AND(F176="Повторный приём (1 час)",A176=A177),"Занято","Свободно"))</f>
+      <c r="I177" s="11" t="n"/>
+      <c r="J177" s="9" t="n"/>
+      <c r="K177" s="13" t="n"/>
+      <c r="L177" s="9">
+        <f>IF(OR(E177&lt;&gt;"",J177&lt;&gt;""),"Занято",IF(AND(F176="Повторный приём (1 час)",A176=A177),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5929,10 +6111,11 @@
       <c r="F178" s="11" t="n"/>
       <c r="G178" s="12" t="n"/>
       <c r="H178" s="12" t="n"/>
-      <c r="I178" s="9" t="n"/>
-      <c r="J178" s="13" t="n"/>
-      <c r="K178" s="9">
-        <f>IF(OR(E178&lt;&gt;"",I178&lt;&gt;""),"Занято",IF(AND(F177="Повторный приём (1 час)",A177=A178),"Занято","Свободно"))</f>
+      <c r="I178" s="11" t="n"/>
+      <c r="J178" s="9" t="n"/>
+      <c r="K178" s="13" t="n"/>
+      <c r="L178" s="9">
+        <f>IF(OR(E178&lt;&gt;"",J178&lt;&gt;""),"Занято",IF(AND(F177="Повторный приём (1 час)",A177=A178),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5959,10 +6142,11 @@
       <c r="F179" s="11" t="n"/>
       <c r="G179" s="12" t="n"/>
       <c r="H179" s="12" t="n"/>
-      <c r="I179" s="9" t="n"/>
-      <c r="J179" s="13" t="n"/>
-      <c r="K179" s="9">
-        <f>IF(OR(E179&lt;&gt;"",I179&lt;&gt;""),"Занято",IF(AND(F178="Повторный приём (1 час)",A178=A179),"Занято","Свободно"))</f>
+      <c r="I179" s="11" t="n"/>
+      <c r="J179" s="9" t="n"/>
+      <c r="K179" s="13" t="n"/>
+      <c r="L179" s="9">
+        <f>IF(OR(E179&lt;&gt;"",J179&lt;&gt;""),"Занято",IF(AND(F178="Повторный приём (1 час)",A178=A179),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -5989,10 +6173,11 @@
       <c r="F180" s="17" t="n"/>
       <c r="G180" s="18" t="n"/>
       <c r="H180" s="18" t="n"/>
-      <c r="I180" s="15" t="n"/>
-      <c r="J180" s="19" t="n"/>
-      <c r="K180" s="15">
-        <f>IF(OR(E180&lt;&gt;"",I180&lt;&gt;""),"Занято",IF(AND(F179="Повторный приём (1 час)",A179=A180),"Занято","Свободно"))</f>
+      <c r="I180" s="17" t="n"/>
+      <c r="J180" s="15" t="n"/>
+      <c r="K180" s="19" t="n"/>
+      <c r="L180" s="15">
+        <f>IF(OR(E180&lt;&gt;"",J180&lt;&gt;""),"Занято",IF(AND(F179="Повторный приём (1 час)",A179=A180),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6019,10 +6204,11 @@
       <c r="F181" s="23" t="n"/>
       <c r="G181" s="24" t="n"/>
       <c r="H181" s="24" t="n"/>
-      <c r="I181" s="21" t="n"/>
-      <c r="J181" s="25" t="n"/>
-      <c r="K181" s="21">
-        <f>IF(OR(E181&lt;&gt;"",I181&lt;&gt;""),"Занято",IF(AND(F180="Повторный приём (1 час)",A180=A181),"Занято","Свободно"))</f>
+      <c r="I181" s="23" t="n"/>
+      <c r="J181" s="21" t="n"/>
+      <c r="K181" s="25" t="n"/>
+      <c r="L181" s="21">
+        <f>IF(OR(E181&lt;&gt;"",J181&lt;&gt;""),"Занято",IF(AND(F180="Повторный приём (1 час)",A180=A181),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6049,10 +6235,11 @@
       <c r="F182" s="23" t="n"/>
       <c r="G182" s="24" t="n"/>
       <c r="H182" s="24" t="n"/>
-      <c r="I182" s="21" t="n"/>
-      <c r="J182" s="25" t="n"/>
-      <c r="K182" s="21">
-        <f>IF(OR(E182&lt;&gt;"",I182&lt;&gt;""),"Занято",IF(AND(F181="Повторный приём (1 час)",A181=A182),"Занято","Свободно"))</f>
+      <c r="I182" s="23" t="n"/>
+      <c r="J182" s="21" t="n"/>
+      <c r="K182" s="25" t="n"/>
+      <c r="L182" s="21">
+        <f>IF(OR(E182&lt;&gt;"",J182&lt;&gt;""),"Занято",IF(AND(F181="Повторный приём (1 час)",A181=A182),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6079,10 +6266,11 @@
       <c r="F183" s="23" t="n"/>
       <c r="G183" s="24" t="n"/>
       <c r="H183" s="24" t="n"/>
-      <c r="I183" s="21" t="n"/>
-      <c r="J183" s="25" t="n"/>
-      <c r="K183" s="21">
-        <f>IF(OR(E183&lt;&gt;"",I183&lt;&gt;""),"Занято",IF(AND(F182="Повторный приём (1 час)",A182=A183),"Занято","Свободно"))</f>
+      <c r="I183" s="23" t="n"/>
+      <c r="J183" s="21" t="n"/>
+      <c r="K183" s="25" t="n"/>
+      <c r="L183" s="21">
+        <f>IF(OR(E183&lt;&gt;"",J183&lt;&gt;""),"Занято",IF(AND(F182="Повторный приём (1 час)",A182=A183),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6109,10 +6297,11 @@
       <c r="F184" s="23" t="n"/>
       <c r="G184" s="24" t="n"/>
       <c r="H184" s="24" t="n"/>
-      <c r="I184" s="21" t="n"/>
-      <c r="J184" s="25" t="n"/>
-      <c r="K184" s="21">
-        <f>IF(OR(E184&lt;&gt;"",I184&lt;&gt;""),"Занято",IF(AND(F183="Повторный приём (1 час)",A183=A184),"Занято","Свободно"))</f>
+      <c r="I184" s="23" t="n"/>
+      <c r="J184" s="21" t="n"/>
+      <c r="K184" s="25" t="n"/>
+      <c r="L184" s="21">
+        <f>IF(OR(E184&lt;&gt;"",J184&lt;&gt;""),"Занято",IF(AND(F183="Повторный приём (1 час)",A183=A184),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6139,10 +6328,11 @@
       <c r="F185" s="23" t="n"/>
       <c r="G185" s="24" t="n"/>
       <c r="H185" s="24" t="n"/>
-      <c r="I185" s="21" t="n"/>
-      <c r="J185" s="25" t="n"/>
-      <c r="K185" s="21">
-        <f>IF(OR(E185&lt;&gt;"",I185&lt;&gt;""),"Занято",IF(AND(F184="Повторный приём (1 час)",A184=A185),"Занято","Свободно"))</f>
+      <c r="I185" s="23" t="n"/>
+      <c r="J185" s="21" t="n"/>
+      <c r="K185" s="25" t="n"/>
+      <c r="L185" s="21">
+        <f>IF(OR(E185&lt;&gt;"",J185&lt;&gt;""),"Занято",IF(AND(F184="Повторный приём (1 час)",A184=A185),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6169,10 +6359,11 @@
       <c r="F186" s="23" t="n"/>
       <c r="G186" s="24" t="n"/>
       <c r="H186" s="24" t="n"/>
-      <c r="I186" s="21" t="n"/>
-      <c r="J186" s="25" t="n"/>
-      <c r="K186" s="21">
-        <f>IF(OR(E186&lt;&gt;"",I186&lt;&gt;""),"Занято",IF(AND(F185="Повторный приём (1 час)",A185=A186),"Занято","Свободно"))</f>
+      <c r="I186" s="23" t="n"/>
+      <c r="J186" s="21" t="n"/>
+      <c r="K186" s="25" t="n"/>
+      <c r="L186" s="21">
+        <f>IF(OR(E186&lt;&gt;"",J186&lt;&gt;""),"Занято",IF(AND(F185="Повторный приём (1 час)",A185=A186),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6199,10 +6390,11 @@
       <c r="F187" s="23" t="n"/>
       <c r="G187" s="24" t="n"/>
       <c r="H187" s="24" t="n"/>
-      <c r="I187" s="21" t="n"/>
-      <c r="J187" s="25" t="n"/>
-      <c r="K187" s="21">
-        <f>IF(OR(E187&lt;&gt;"",I187&lt;&gt;""),"Занято",IF(AND(F186="Повторный приём (1 час)",A186=A187),"Занято","Свободно"))</f>
+      <c r="I187" s="23" t="n"/>
+      <c r="J187" s="21" t="n"/>
+      <c r="K187" s="25" t="n"/>
+      <c r="L187" s="21">
+        <f>IF(OR(E187&lt;&gt;"",J187&lt;&gt;""),"Занято",IF(AND(F186="Повторный приём (1 час)",A186=A187),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6229,10 +6421,11 @@
       <c r="F188" s="23" t="n"/>
       <c r="G188" s="24" t="n"/>
       <c r="H188" s="24" t="n"/>
-      <c r="I188" s="21" t="n"/>
-      <c r="J188" s="25" t="n"/>
-      <c r="K188" s="21">
-        <f>IF(OR(E188&lt;&gt;"",I188&lt;&gt;""),"Занято",IF(AND(F187="Повторный приём (1 час)",A187=A188),"Занято","Свободно"))</f>
+      <c r="I188" s="23" t="n"/>
+      <c r="J188" s="21" t="n"/>
+      <c r="K188" s="25" t="n"/>
+      <c r="L188" s="21">
+        <f>IF(OR(E188&lt;&gt;"",J188&lt;&gt;""),"Занято",IF(AND(F187="Повторный приём (1 час)",A187=A188),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6259,10 +6452,11 @@
       <c r="F189" s="23" t="n"/>
       <c r="G189" s="24" t="n"/>
       <c r="H189" s="24" t="n"/>
-      <c r="I189" s="21" t="n"/>
-      <c r="J189" s="25" t="n"/>
-      <c r="K189" s="21">
-        <f>IF(OR(E189&lt;&gt;"",I189&lt;&gt;""),"Занято",IF(AND(F188="Повторный приём (1 час)",A188=A189),"Занято","Свободно"))</f>
+      <c r="I189" s="23" t="n"/>
+      <c r="J189" s="21" t="n"/>
+      <c r="K189" s="25" t="n"/>
+      <c r="L189" s="21">
+        <f>IF(OR(E189&lt;&gt;"",J189&lt;&gt;""),"Занято",IF(AND(F188="Повторный приём (1 час)",A188=A189),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6289,10 +6483,11 @@
       <c r="F190" s="23" t="n"/>
       <c r="G190" s="24" t="n"/>
       <c r="H190" s="24" t="n"/>
-      <c r="I190" s="21" t="n"/>
-      <c r="J190" s="25" t="n"/>
-      <c r="K190" s="21">
-        <f>IF(OR(E190&lt;&gt;"",I190&lt;&gt;""),"Занято",IF(AND(F189="Повторный приём (1 час)",A189=A190),"Занято","Свободно"))</f>
+      <c r="I190" s="23" t="n"/>
+      <c r="J190" s="21" t="n"/>
+      <c r="K190" s="25" t="n"/>
+      <c r="L190" s="21">
+        <f>IF(OR(E190&lt;&gt;"",J190&lt;&gt;""),"Занято",IF(AND(F189="Повторный приём (1 час)",A189=A190),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6319,10 +6514,11 @@
       <c r="F191" s="23" t="n"/>
       <c r="G191" s="24" t="n"/>
       <c r="H191" s="24" t="n"/>
-      <c r="I191" s="21" t="n"/>
-      <c r="J191" s="25" t="n"/>
-      <c r="K191" s="21">
-        <f>IF(OR(E191&lt;&gt;"",I191&lt;&gt;""),"Занято",IF(AND(F190="Повторный приём (1 час)",A190=A191),"Занято","Свободно"))</f>
+      <c r="I191" s="23" t="n"/>
+      <c r="J191" s="21" t="n"/>
+      <c r="K191" s="25" t="n"/>
+      <c r="L191" s="21">
+        <f>IF(OR(E191&lt;&gt;"",J191&lt;&gt;""),"Занято",IF(AND(F190="Повторный приём (1 час)",A190=A191),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6349,10 +6545,11 @@
       <c r="F192" s="23" t="n"/>
       <c r="G192" s="24" t="n"/>
       <c r="H192" s="24" t="n"/>
-      <c r="I192" s="21" t="n"/>
-      <c r="J192" s="25" t="n"/>
-      <c r="K192" s="21">
-        <f>IF(OR(E192&lt;&gt;"",I192&lt;&gt;""),"Занято",IF(AND(F191="Повторный приём (1 час)",A191=A192),"Занято","Свободно"))</f>
+      <c r="I192" s="23" t="n"/>
+      <c r="J192" s="21" t="n"/>
+      <c r="K192" s="25" t="n"/>
+      <c r="L192" s="21">
+        <f>IF(OR(E192&lt;&gt;"",J192&lt;&gt;""),"Занято",IF(AND(F191="Повторный приём (1 час)",A191=A192),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6379,10 +6576,11 @@
       <c r="F193" s="23" t="n"/>
       <c r="G193" s="24" t="n"/>
       <c r="H193" s="24" t="n"/>
-      <c r="I193" s="21" t="n"/>
-      <c r="J193" s="25" t="n"/>
-      <c r="K193" s="21">
-        <f>IF(OR(E193&lt;&gt;"",I193&lt;&gt;""),"Занято",IF(AND(F192="Повторный приём (1 час)",A192=A193),"Занято","Свободно"))</f>
+      <c r="I193" s="23" t="n"/>
+      <c r="J193" s="21" t="n"/>
+      <c r="K193" s="25" t="n"/>
+      <c r="L193" s="21">
+        <f>IF(OR(E193&lt;&gt;"",J193&lt;&gt;""),"Занято",IF(AND(F192="Повторный приём (1 час)",A192=A193),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6409,10 +6607,11 @@
       <c r="F194" s="23" t="n"/>
       <c r="G194" s="24" t="n"/>
       <c r="H194" s="24" t="n"/>
-      <c r="I194" s="21" t="n"/>
-      <c r="J194" s="25" t="n"/>
-      <c r="K194" s="21">
-        <f>IF(OR(E194&lt;&gt;"",I194&lt;&gt;""),"Занято",IF(AND(F193="Повторный приём (1 час)",A193=A194),"Занято","Свободно"))</f>
+      <c r="I194" s="23" t="n"/>
+      <c r="J194" s="21" t="n"/>
+      <c r="K194" s="25" t="n"/>
+      <c r="L194" s="21">
+        <f>IF(OR(E194&lt;&gt;"",J194&lt;&gt;""),"Занято",IF(AND(F193="Повторный приём (1 час)",A193=A194),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6439,10 +6638,11 @@
       <c r="F195" s="23" t="n"/>
       <c r="G195" s="24" t="n"/>
       <c r="H195" s="24" t="n"/>
-      <c r="I195" s="21" t="n"/>
-      <c r="J195" s="25" t="n"/>
-      <c r="K195" s="21">
-        <f>IF(OR(E195&lt;&gt;"",I195&lt;&gt;""),"Занято",IF(AND(F194="Повторный приём (1 час)",A194=A195),"Занято","Свободно"))</f>
+      <c r="I195" s="23" t="n"/>
+      <c r="J195" s="21" t="n"/>
+      <c r="K195" s="25" t="n"/>
+      <c r="L195" s="21">
+        <f>IF(OR(E195&lt;&gt;"",J195&lt;&gt;""),"Занято",IF(AND(F194="Повторный приём (1 час)",A194=A195),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6469,10 +6669,11 @@
       <c r="F196" s="23" t="n"/>
       <c r="G196" s="24" t="n"/>
       <c r="H196" s="24" t="n"/>
-      <c r="I196" s="21" t="n"/>
-      <c r="J196" s="25" t="n"/>
-      <c r="K196" s="21">
-        <f>IF(OR(E196&lt;&gt;"",I196&lt;&gt;""),"Занято",IF(AND(F195="Повторный приём (1 час)",A195=A196),"Занято","Свободно"))</f>
+      <c r="I196" s="23" t="n"/>
+      <c r="J196" s="21" t="n"/>
+      <c r="K196" s="25" t="n"/>
+      <c r="L196" s="21">
+        <f>IF(OR(E196&lt;&gt;"",J196&lt;&gt;""),"Занято",IF(AND(F195="Повторный приём (1 час)",A195=A196),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6499,10 +6700,11 @@
       <c r="F197" s="23" t="n"/>
       <c r="G197" s="24" t="n"/>
       <c r="H197" s="24" t="n"/>
-      <c r="I197" s="21" t="n"/>
-      <c r="J197" s="25" t="n"/>
-      <c r="K197" s="21">
-        <f>IF(OR(E197&lt;&gt;"",I197&lt;&gt;""),"Занято",IF(AND(F196="Повторный приём (1 час)",A196=A197),"Занято","Свободно"))</f>
+      <c r="I197" s="23" t="n"/>
+      <c r="J197" s="21" t="n"/>
+      <c r="K197" s="25" t="n"/>
+      <c r="L197" s="21">
+        <f>IF(OR(E197&lt;&gt;"",J197&lt;&gt;""),"Занято",IF(AND(F196="Повторный приём (1 час)",A196=A197),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6529,10 +6731,11 @@
       <c r="F198" s="5" t="n"/>
       <c r="G198" s="6" t="n"/>
       <c r="H198" s="6" t="n"/>
-      <c r="I198" s="3" t="n"/>
-      <c r="J198" s="7" t="n"/>
-      <c r="K198" s="3">
-        <f>IF(OR(E198&lt;&gt;"",I198&lt;&gt;""),"Занято",IF(AND(F197="Повторный приём (1 час)",A197=A198),"Занято","Свободно"))</f>
+      <c r="I198" s="5" t="n"/>
+      <c r="J198" s="3" t="n"/>
+      <c r="K198" s="7" t="n"/>
+      <c r="L198" s="3">
+        <f>IF(OR(E198&lt;&gt;"",J198&lt;&gt;""),"Занято",IF(AND(F197="Повторный приём (1 час)",A197=A198),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6559,10 +6762,11 @@
       <c r="F199" s="11" t="n"/>
       <c r="G199" s="12" t="n"/>
       <c r="H199" s="12" t="n"/>
-      <c r="I199" s="9" t="n"/>
-      <c r="J199" s="13" t="n"/>
-      <c r="K199" s="9">
-        <f>IF(OR(E199&lt;&gt;"",I199&lt;&gt;""),"Занято",IF(AND(F198="Повторный приём (1 час)",A198=A199),"Занято","Свободно"))</f>
+      <c r="I199" s="11" t="n"/>
+      <c r="J199" s="9" t="n"/>
+      <c r="K199" s="13" t="n"/>
+      <c r="L199" s="9">
+        <f>IF(OR(E199&lt;&gt;"",J199&lt;&gt;""),"Занято",IF(AND(F198="Повторный приём (1 час)",A198=A199),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6589,10 +6793,11 @@
       <c r="F200" s="11" t="n"/>
       <c r="G200" s="12" t="n"/>
       <c r="H200" s="12" t="n"/>
-      <c r="I200" s="9" t="n"/>
-      <c r="J200" s="13" t="n"/>
-      <c r="K200" s="9">
-        <f>IF(OR(E200&lt;&gt;"",I200&lt;&gt;""),"Занято",IF(AND(F199="Повторный приём (1 час)",A199=A200),"Занято","Свободно"))</f>
+      <c r="I200" s="11" t="n"/>
+      <c r="J200" s="9" t="n"/>
+      <c r="K200" s="13" t="n"/>
+      <c r="L200" s="9">
+        <f>IF(OR(E200&lt;&gt;"",J200&lt;&gt;""),"Занято",IF(AND(F199="Повторный приём (1 час)",A199=A200),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6619,10 +6824,11 @@
       <c r="F201" s="11" t="n"/>
       <c r="G201" s="12" t="n"/>
       <c r="H201" s="12" t="n"/>
-      <c r="I201" s="9" t="n"/>
-      <c r="J201" s="13" t="n"/>
-      <c r="K201" s="9">
-        <f>IF(OR(E201&lt;&gt;"",I201&lt;&gt;""),"Занято",IF(AND(F200="Повторный приём (1 час)",A200=A201),"Занято","Свободно"))</f>
+      <c r="I201" s="11" t="n"/>
+      <c r="J201" s="9" t="n"/>
+      <c r="K201" s="13" t="n"/>
+      <c r="L201" s="9">
+        <f>IF(OR(E201&lt;&gt;"",J201&lt;&gt;""),"Занято",IF(AND(F200="Повторный приём (1 час)",A200=A201),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6649,10 +6855,11 @@
       <c r="F202" s="11" t="n"/>
       <c r="G202" s="12" t="n"/>
       <c r="H202" s="12" t="n"/>
-      <c r="I202" s="9" t="n"/>
-      <c r="J202" s="13" t="n"/>
-      <c r="K202" s="9">
-        <f>IF(OR(E202&lt;&gt;"",I202&lt;&gt;""),"Занято",IF(AND(F201="Повторный приём (1 час)",A201=A202),"Занято","Свободно"))</f>
+      <c r="I202" s="11" t="n"/>
+      <c r="J202" s="9" t="n"/>
+      <c r="K202" s="13" t="n"/>
+      <c r="L202" s="9">
+        <f>IF(OR(E202&lt;&gt;"",J202&lt;&gt;""),"Занято",IF(AND(F201="Повторный приём (1 час)",A201=A202),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6679,10 +6886,11 @@
       <c r="F203" s="11" t="n"/>
       <c r="G203" s="12" t="n"/>
       <c r="H203" s="12" t="n"/>
-      <c r="I203" s="9" t="n"/>
-      <c r="J203" s="13" t="n"/>
-      <c r="K203" s="9">
-        <f>IF(OR(E203&lt;&gt;"",I203&lt;&gt;""),"Занято",IF(AND(F202="Повторный приём (1 час)",A202=A203),"Занято","Свободно"))</f>
+      <c r="I203" s="11" t="n"/>
+      <c r="J203" s="9" t="n"/>
+      <c r="K203" s="13" t="n"/>
+      <c r="L203" s="9">
+        <f>IF(OR(E203&lt;&gt;"",J203&lt;&gt;""),"Занято",IF(AND(F202="Повторный приём (1 час)",A202=A203),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6709,10 +6917,11 @@
       <c r="F204" s="11" t="n"/>
       <c r="G204" s="12" t="n"/>
       <c r="H204" s="12" t="n"/>
-      <c r="I204" s="9" t="n"/>
-      <c r="J204" s="13" t="n"/>
-      <c r="K204" s="9">
-        <f>IF(OR(E204&lt;&gt;"",I204&lt;&gt;""),"Занято",IF(AND(F203="Повторный приём (1 час)",A203=A204),"Занято","Свободно"))</f>
+      <c r="I204" s="11" t="n"/>
+      <c r="J204" s="9" t="n"/>
+      <c r="K204" s="13" t="n"/>
+      <c r="L204" s="9">
+        <f>IF(OR(E204&lt;&gt;"",J204&lt;&gt;""),"Занято",IF(AND(F203="Повторный приём (1 час)",A203=A204),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6739,10 +6948,11 @@
       <c r="F205" s="11" t="n"/>
       <c r="G205" s="12" t="n"/>
       <c r="H205" s="12" t="n"/>
-      <c r="I205" s="9" t="n"/>
-      <c r="J205" s="13" t="n"/>
-      <c r="K205" s="9">
-        <f>IF(OR(E205&lt;&gt;"",I205&lt;&gt;""),"Занято",IF(AND(F204="Повторный приём (1 час)",A204=A205),"Занято","Свободно"))</f>
+      <c r="I205" s="11" t="n"/>
+      <c r="J205" s="9" t="n"/>
+      <c r="K205" s="13" t="n"/>
+      <c r="L205" s="9">
+        <f>IF(OR(E205&lt;&gt;"",J205&lt;&gt;""),"Занято",IF(AND(F204="Повторный приём (1 час)",A204=A205),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6769,10 +6979,11 @@
       <c r="F206" s="11" t="n"/>
       <c r="G206" s="12" t="n"/>
       <c r="H206" s="12" t="n"/>
-      <c r="I206" s="9" t="n"/>
-      <c r="J206" s="13" t="n"/>
-      <c r="K206" s="9">
-        <f>IF(OR(E206&lt;&gt;"",I206&lt;&gt;""),"Занято",IF(AND(F205="Повторный приём (1 час)",A205=A206),"Занято","Свободно"))</f>
+      <c r="I206" s="11" t="n"/>
+      <c r="J206" s="9" t="n"/>
+      <c r="K206" s="13" t="n"/>
+      <c r="L206" s="9">
+        <f>IF(OR(E206&lt;&gt;"",J206&lt;&gt;""),"Занято",IF(AND(F205="Повторный приём (1 час)",A205=A206),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6799,10 +7010,11 @@
       <c r="F207" s="11" t="n"/>
       <c r="G207" s="12" t="n"/>
       <c r="H207" s="12" t="n"/>
-      <c r="I207" s="9" t="n"/>
-      <c r="J207" s="13" t="n"/>
-      <c r="K207" s="9">
-        <f>IF(OR(E207&lt;&gt;"",I207&lt;&gt;""),"Занято",IF(AND(F206="Повторный приём (1 час)",A206=A207),"Занято","Свободно"))</f>
+      <c r="I207" s="11" t="n"/>
+      <c r="J207" s="9" t="n"/>
+      <c r="K207" s="13" t="n"/>
+      <c r="L207" s="9">
+        <f>IF(OR(E207&lt;&gt;"",J207&lt;&gt;""),"Занято",IF(AND(F206="Повторный приём (1 час)",A206=A207),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6829,10 +7041,11 @@
       <c r="F208" s="11" t="n"/>
       <c r="G208" s="12" t="n"/>
       <c r="H208" s="12" t="n"/>
-      <c r="I208" s="9" t="n"/>
-      <c r="J208" s="13" t="n"/>
-      <c r="K208" s="9">
-        <f>IF(OR(E208&lt;&gt;"",I208&lt;&gt;""),"Занято",IF(AND(F207="Повторный приём (1 час)",A207=A208),"Занято","Свободно"))</f>
+      <c r="I208" s="11" t="n"/>
+      <c r="J208" s="9" t="n"/>
+      <c r="K208" s="13" t="n"/>
+      <c r="L208" s="9">
+        <f>IF(OR(E208&lt;&gt;"",J208&lt;&gt;""),"Занято",IF(AND(F207="Повторный приём (1 час)",A207=A208),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6859,10 +7072,11 @@
       <c r="F209" s="11" t="n"/>
       <c r="G209" s="12" t="n"/>
       <c r="H209" s="12" t="n"/>
-      <c r="I209" s="9" t="n"/>
-      <c r="J209" s="13" t="n"/>
-      <c r="K209" s="9">
-        <f>IF(OR(E209&lt;&gt;"",I209&lt;&gt;""),"Занято",IF(AND(F208="Повторный приём (1 час)",A208=A209),"Занято","Свободно"))</f>
+      <c r="I209" s="11" t="n"/>
+      <c r="J209" s="9" t="n"/>
+      <c r="K209" s="13" t="n"/>
+      <c r="L209" s="9">
+        <f>IF(OR(E209&lt;&gt;"",J209&lt;&gt;""),"Занято",IF(AND(F208="Повторный приём (1 час)",A208=A209),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6889,10 +7103,11 @@
       <c r="F210" s="11" t="n"/>
       <c r="G210" s="12" t="n"/>
       <c r="H210" s="12" t="n"/>
-      <c r="I210" s="9" t="n"/>
-      <c r="J210" s="13" t="n"/>
-      <c r="K210" s="9">
-        <f>IF(OR(E210&lt;&gt;"",I210&lt;&gt;""),"Занято",IF(AND(F209="Повторный приём (1 час)",A209=A210),"Занято","Свободно"))</f>
+      <c r="I210" s="11" t="n"/>
+      <c r="J210" s="9" t="n"/>
+      <c r="K210" s="13" t="n"/>
+      <c r="L210" s="9">
+        <f>IF(OR(E210&lt;&gt;"",J210&lt;&gt;""),"Занято",IF(AND(F209="Повторный приём (1 час)",A209=A210),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6919,10 +7134,11 @@
       <c r="F211" s="11" t="n"/>
       <c r="G211" s="12" t="n"/>
       <c r="H211" s="12" t="n"/>
-      <c r="I211" s="9" t="n"/>
-      <c r="J211" s="13" t="n"/>
-      <c r="K211" s="9">
-        <f>IF(OR(E211&lt;&gt;"",I211&lt;&gt;""),"Занято",IF(AND(F210="Повторный приём (1 час)",A210=A211),"Занято","Свободно"))</f>
+      <c r="I211" s="11" t="n"/>
+      <c r="J211" s="9" t="n"/>
+      <c r="K211" s="13" t="n"/>
+      <c r="L211" s="9">
+        <f>IF(OR(E211&lt;&gt;"",J211&lt;&gt;""),"Занято",IF(AND(F210="Повторный приём (1 час)",A210=A211),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6949,10 +7165,11 @@
       <c r="F212" s="11" t="n"/>
       <c r="G212" s="12" t="n"/>
       <c r="H212" s="12" t="n"/>
-      <c r="I212" s="9" t="n"/>
-      <c r="J212" s="13" t="n"/>
-      <c r="K212" s="9">
-        <f>IF(OR(E212&lt;&gt;"",I212&lt;&gt;""),"Занято",IF(AND(F211="Повторный приём (1 час)",A211=A212),"Занято","Свободно"))</f>
+      <c r="I212" s="11" t="n"/>
+      <c r="J212" s="9" t="n"/>
+      <c r="K212" s="13" t="n"/>
+      <c r="L212" s="9">
+        <f>IF(OR(E212&lt;&gt;"",J212&lt;&gt;""),"Занято",IF(AND(F211="Повторный приём (1 час)",A211=A212),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -6979,10 +7196,11 @@
       <c r="F213" s="11" t="n"/>
       <c r="G213" s="12" t="n"/>
       <c r="H213" s="12" t="n"/>
-      <c r="I213" s="9" t="n"/>
-      <c r="J213" s="13" t="n"/>
-      <c r="K213" s="9">
-        <f>IF(OR(E213&lt;&gt;"",I213&lt;&gt;""),"Занято",IF(AND(F212="Повторный приём (1 час)",A212=A213),"Занято","Свободно"))</f>
+      <c r="I213" s="11" t="n"/>
+      <c r="J213" s="9" t="n"/>
+      <c r="K213" s="13" t="n"/>
+      <c r="L213" s="9">
+        <f>IF(OR(E213&lt;&gt;"",J213&lt;&gt;""),"Занято",IF(AND(F212="Повторный приём (1 час)",A212=A213),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7009,10 +7227,11 @@
       <c r="F214" s="11" t="n"/>
       <c r="G214" s="12" t="n"/>
       <c r="H214" s="12" t="n"/>
-      <c r="I214" s="9" t="n"/>
-      <c r="J214" s="13" t="n"/>
-      <c r="K214" s="9">
-        <f>IF(OR(E214&lt;&gt;"",I214&lt;&gt;""),"Занято",IF(AND(F213="Повторный приём (1 час)",A213=A214),"Занято","Свободно"))</f>
+      <c r="I214" s="11" t="n"/>
+      <c r="J214" s="9" t="n"/>
+      <c r="K214" s="13" t="n"/>
+      <c r="L214" s="9">
+        <f>IF(OR(E214&lt;&gt;"",J214&lt;&gt;""),"Занято",IF(AND(F213="Повторный приём (1 час)",A213=A214),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7039,10 +7258,11 @@
       <c r="F215" s="11" t="n"/>
       <c r="G215" s="12" t="n"/>
       <c r="H215" s="12" t="n"/>
-      <c r="I215" s="9" t="n"/>
-      <c r="J215" s="13" t="n"/>
-      <c r="K215" s="9">
-        <f>IF(OR(E215&lt;&gt;"",I215&lt;&gt;""),"Занято",IF(AND(F214="Повторный приём (1 час)",A214=A215),"Занято","Свободно"))</f>
+      <c r="I215" s="11" t="n"/>
+      <c r="J215" s="9" t="n"/>
+      <c r="K215" s="13" t="n"/>
+      <c r="L215" s="9">
+        <f>IF(OR(E215&lt;&gt;"",J215&lt;&gt;""),"Занято",IF(AND(F214="Повторный приём (1 час)",A214=A215),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7069,10 +7289,11 @@
       <c r="F216" s="17" t="n"/>
       <c r="G216" s="18" t="n"/>
       <c r="H216" s="18" t="n"/>
-      <c r="I216" s="15" t="n"/>
-      <c r="J216" s="19" t="n"/>
-      <c r="K216" s="15">
-        <f>IF(OR(E216&lt;&gt;"",I216&lt;&gt;""),"Занято",IF(AND(F215="Повторный приём (1 час)",A215=A216),"Занято","Свободно"))</f>
+      <c r="I216" s="17" t="n"/>
+      <c r="J216" s="15" t="n"/>
+      <c r="K216" s="19" t="n"/>
+      <c r="L216" s="15">
+        <f>IF(OR(E216&lt;&gt;"",J216&lt;&gt;""),"Занято",IF(AND(F215="Повторный приём (1 час)",A215=A216),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7099,10 +7320,11 @@
       <c r="F217" s="23" t="n"/>
       <c r="G217" s="24" t="n"/>
       <c r="H217" s="24" t="n"/>
-      <c r="I217" s="21" t="n"/>
-      <c r="J217" s="25" t="n"/>
-      <c r="K217" s="21">
-        <f>IF(OR(E217&lt;&gt;"",I217&lt;&gt;""),"Занято",IF(AND(F216="Повторный приём (1 час)",A216=A217),"Занято","Свободно"))</f>
+      <c r="I217" s="23" t="n"/>
+      <c r="J217" s="21" t="n"/>
+      <c r="K217" s="25" t="n"/>
+      <c r="L217" s="21">
+        <f>IF(OR(E217&lt;&gt;"",J217&lt;&gt;""),"Занято",IF(AND(F216="Повторный приём (1 час)",A216=A217),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7129,10 +7351,11 @@
       <c r="F218" s="23" t="n"/>
       <c r="G218" s="24" t="n"/>
       <c r="H218" s="24" t="n"/>
-      <c r="I218" s="21" t="n"/>
-      <c r="J218" s="25" t="n"/>
-      <c r="K218" s="21">
-        <f>IF(OR(E218&lt;&gt;"",I218&lt;&gt;""),"Занято",IF(AND(F217="Повторный приём (1 час)",A217=A218),"Занято","Свободно"))</f>
+      <c r="I218" s="23" t="n"/>
+      <c r="J218" s="21" t="n"/>
+      <c r="K218" s="25" t="n"/>
+      <c r="L218" s="21">
+        <f>IF(OR(E218&lt;&gt;"",J218&lt;&gt;""),"Занято",IF(AND(F217="Повторный приём (1 час)",A217=A218),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7159,10 +7382,11 @@
       <c r="F219" s="23" t="n"/>
       <c r="G219" s="24" t="n"/>
       <c r="H219" s="24" t="n"/>
-      <c r="I219" s="21" t="n"/>
-      <c r="J219" s="25" t="n"/>
-      <c r="K219" s="21">
-        <f>IF(OR(E219&lt;&gt;"",I219&lt;&gt;""),"Занято",IF(AND(F218="Повторный приём (1 час)",A218=A219),"Занято","Свободно"))</f>
+      <c r="I219" s="23" t="n"/>
+      <c r="J219" s="21" t="n"/>
+      <c r="K219" s="25" t="n"/>
+      <c r="L219" s="21">
+        <f>IF(OR(E219&lt;&gt;"",J219&lt;&gt;""),"Занято",IF(AND(F218="Повторный приём (1 час)",A218=A219),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7189,10 +7413,11 @@
       <c r="F220" s="23" t="n"/>
       <c r="G220" s="24" t="n"/>
       <c r="H220" s="24" t="n"/>
-      <c r="I220" s="21" t="n"/>
-      <c r="J220" s="25" t="n"/>
-      <c r="K220" s="21">
-        <f>IF(OR(E220&lt;&gt;"",I220&lt;&gt;""),"Занято",IF(AND(F219="Повторный приём (1 час)",A219=A220),"Занято","Свободно"))</f>
+      <c r="I220" s="23" t="n"/>
+      <c r="J220" s="21" t="n"/>
+      <c r="K220" s="25" t="n"/>
+      <c r="L220" s="21">
+        <f>IF(OR(E220&lt;&gt;"",J220&lt;&gt;""),"Занято",IF(AND(F219="Повторный приём (1 час)",A219=A220),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7219,10 +7444,11 @@
       <c r="F221" s="23" t="n"/>
       <c r="G221" s="24" t="n"/>
       <c r="H221" s="24" t="n"/>
-      <c r="I221" s="21" t="n"/>
-      <c r="J221" s="25" t="n"/>
-      <c r="K221" s="21">
-        <f>IF(OR(E221&lt;&gt;"",I221&lt;&gt;""),"Занято",IF(AND(F220="Повторный приём (1 час)",A220=A221),"Занято","Свободно"))</f>
+      <c r="I221" s="23" t="n"/>
+      <c r="J221" s="21" t="n"/>
+      <c r="K221" s="25" t="n"/>
+      <c r="L221" s="21">
+        <f>IF(OR(E221&lt;&gt;"",J221&lt;&gt;""),"Занято",IF(AND(F220="Повторный приём (1 час)",A220=A221),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7249,10 +7475,11 @@
       <c r="F222" s="23" t="n"/>
       <c r="G222" s="24" t="n"/>
       <c r="H222" s="24" t="n"/>
-      <c r="I222" s="21" t="n"/>
-      <c r="J222" s="25" t="n"/>
-      <c r="K222" s="21">
-        <f>IF(OR(E222&lt;&gt;"",I222&lt;&gt;""),"Занято",IF(AND(F221="Повторный приём (1 час)",A221=A222),"Занято","Свободно"))</f>
+      <c r="I222" s="23" t="n"/>
+      <c r="J222" s="21" t="n"/>
+      <c r="K222" s="25" t="n"/>
+      <c r="L222" s="21">
+        <f>IF(OR(E222&lt;&gt;"",J222&lt;&gt;""),"Занято",IF(AND(F221="Повторный приём (1 час)",A221=A222),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7279,10 +7506,11 @@
       <c r="F223" s="23" t="n"/>
       <c r="G223" s="24" t="n"/>
       <c r="H223" s="24" t="n"/>
-      <c r="I223" s="21" t="n"/>
-      <c r="J223" s="25" t="n"/>
-      <c r="K223" s="21">
-        <f>IF(OR(E223&lt;&gt;"",I223&lt;&gt;""),"Занято",IF(AND(F222="Повторный приём (1 час)",A222=A223),"Занято","Свободно"))</f>
+      <c r="I223" s="23" t="n"/>
+      <c r="J223" s="21" t="n"/>
+      <c r="K223" s="25" t="n"/>
+      <c r="L223" s="21">
+        <f>IF(OR(E223&lt;&gt;"",J223&lt;&gt;""),"Занято",IF(AND(F222="Повторный приём (1 час)",A222=A223),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7309,10 +7537,11 @@
       <c r="F224" s="23" t="n"/>
       <c r="G224" s="24" t="n"/>
       <c r="H224" s="24" t="n"/>
-      <c r="I224" s="21" t="n"/>
-      <c r="J224" s="25" t="n"/>
-      <c r="K224" s="21">
-        <f>IF(OR(E224&lt;&gt;"",I224&lt;&gt;""),"Занято",IF(AND(F223="Повторный приём (1 час)",A223=A224),"Занято","Свободно"))</f>
+      <c r="I224" s="23" t="n"/>
+      <c r="J224" s="21" t="n"/>
+      <c r="K224" s="25" t="n"/>
+      <c r="L224" s="21">
+        <f>IF(OR(E224&lt;&gt;"",J224&lt;&gt;""),"Занято",IF(AND(F223="Повторный приём (1 час)",A223=A224),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7339,10 +7568,11 @@
       <c r="F225" s="23" t="n"/>
       <c r="G225" s="24" t="n"/>
       <c r="H225" s="24" t="n"/>
-      <c r="I225" s="21" t="n"/>
-      <c r="J225" s="25" t="n"/>
-      <c r="K225" s="21">
-        <f>IF(OR(E225&lt;&gt;"",I225&lt;&gt;""),"Занято",IF(AND(F224="Повторный приём (1 час)",A224=A225),"Занято","Свободно"))</f>
+      <c r="I225" s="23" t="n"/>
+      <c r="J225" s="21" t="n"/>
+      <c r="K225" s="25" t="n"/>
+      <c r="L225" s="21">
+        <f>IF(OR(E225&lt;&gt;"",J225&lt;&gt;""),"Занято",IF(AND(F224="Повторный приём (1 час)",A224=A225),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7369,10 +7599,11 @@
       <c r="F226" s="23" t="n"/>
       <c r="G226" s="24" t="n"/>
       <c r="H226" s="24" t="n"/>
-      <c r="I226" s="21" t="n"/>
-      <c r="J226" s="25" t="n"/>
-      <c r="K226" s="21">
-        <f>IF(OR(E226&lt;&gt;"",I226&lt;&gt;""),"Занято",IF(AND(F225="Повторный приём (1 час)",A225=A226),"Занято","Свободно"))</f>
+      <c r="I226" s="23" t="n"/>
+      <c r="J226" s="21" t="n"/>
+      <c r="K226" s="25" t="n"/>
+      <c r="L226" s="21">
+        <f>IF(OR(E226&lt;&gt;"",J226&lt;&gt;""),"Занято",IF(AND(F225="Повторный приём (1 час)",A225=A226),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7399,10 +7630,11 @@
       <c r="F227" s="23" t="n"/>
       <c r="G227" s="24" t="n"/>
       <c r="H227" s="24" t="n"/>
-      <c r="I227" s="21" t="n"/>
-      <c r="J227" s="25" t="n"/>
-      <c r="K227" s="21">
-        <f>IF(OR(E227&lt;&gt;"",I227&lt;&gt;""),"Занято",IF(AND(F226="Повторный приём (1 час)",A226=A227),"Занято","Свободно"))</f>
+      <c r="I227" s="23" t="n"/>
+      <c r="J227" s="21" t="n"/>
+      <c r="K227" s="25" t="n"/>
+      <c r="L227" s="21">
+        <f>IF(OR(E227&lt;&gt;"",J227&lt;&gt;""),"Занято",IF(AND(F226="Повторный приём (1 час)",A226=A227),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7429,10 +7661,11 @@
       <c r="F228" s="23" t="n"/>
       <c r="G228" s="24" t="n"/>
       <c r="H228" s="24" t="n"/>
-      <c r="I228" s="21" t="n"/>
-      <c r="J228" s="25" t="n"/>
-      <c r="K228" s="21">
-        <f>IF(OR(E228&lt;&gt;"",I228&lt;&gt;""),"Занято",IF(AND(F227="Повторный приём (1 час)",A227=A228),"Занято","Свободно"))</f>
+      <c r="I228" s="23" t="n"/>
+      <c r="J228" s="21" t="n"/>
+      <c r="K228" s="25" t="n"/>
+      <c r="L228" s="21">
+        <f>IF(OR(E228&lt;&gt;"",J228&lt;&gt;""),"Занято",IF(AND(F227="Повторный приём (1 час)",A227=A228),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7459,10 +7692,11 @@
       <c r="F229" s="23" t="n"/>
       <c r="G229" s="24" t="n"/>
       <c r="H229" s="24" t="n"/>
-      <c r="I229" s="21" t="n"/>
-      <c r="J229" s="25" t="n"/>
-      <c r="K229" s="21">
-        <f>IF(OR(E229&lt;&gt;"",I229&lt;&gt;""),"Занято",IF(AND(F228="Повторный приём (1 час)",A228=A229),"Занято","Свободно"))</f>
+      <c r="I229" s="23" t="n"/>
+      <c r="J229" s="21" t="n"/>
+      <c r="K229" s="25" t="n"/>
+      <c r="L229" s="21">
+        <f>IF(OR(E229&lt;&gt;"",J229&lt;&gt;""),"Занято",IF(AND(F228="Повторный приём (1 час)",A228=A229),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7489,10 +7723,11 @@
       <c r="F230" s="23" t="n"/>
       <c r="G230" s="24" t="n"/>
       <c r="H230" s="24" t="n"/>
-      <c r="I230" s="21" t="n"/>
-      <c r="J230" s="25" t="n"/>
-      <c r="K230" s="21">
-        <f>IF(OR(E230&lt;&gt;"",I230&lt;&gt;""),"Занято",IF(AND(F229="Повторный приём (1 час)",A229=A230),"Занято","Свободно"))</f>
+      <c r="I230" s="23" t="n"/>
+      <c r="J230" s="21" t="n"/>
+      <c r="K230" s="25" t="n"/>
+      <c r="L230" s="21">
+        <f>IF(OR(E230&lt;&gt;"",J230&lt;&gt;""),"Занято",IF(AND(F229="Повторный приём (1 час)",A229=A230),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7519,10 +7754,11 @@
       <c r="F231" s="23" t="n"/>
       <c r="G231" s="24" t="n"/>
       <c r="H231" s="24" t="n"/>
-      <c r="I231" s="21" t="n"/>
-      <c r="J231" s="25" t="n"/>
-      <c r="K231" s="21">
-        <f>IF(OR(E231&lt;&gt;"",I231&lt;&gt;""),"Занято",IF(AND(F230="Повторный приём (1 час)",A230=A231),"Занято","Свободно"))</f>
+      <c r="I231" s="23" t="n"/>
+      <c r="J231" s="21" t="n"/>
+      <c r="K231" s="25" t="n"/>
+      <c r="L231" s="21">
+        <f>IF(OR(E231&lt;&gt;"",J231&lt;&gt;""),"Занято",IF(AND(F230="Повторный приём (1 час)",A230=A231),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7549,10 +7785,11 @@
       <c r="F232" s="23" t="n"/>
       <c r="G232" s="24" t="n"/>
       <c r="H232" s="24" t="n"/>
-      <c r="I232" s="21" t="n"/>
-      <c r="J232" s="25" t="n"/>
-      <c r="K232" s="21">
-        <f>IF(OR(E232&lt;&gt;"",I232&lt;&gt;""),"Занято",IF(AND(F231="Повторный приём (1 час)",A231=A232),"Занято","Свободно"))</f>
+      <c r="I232" s="23" t="n"/>
+      <c r="J232" s="21" t="n"/>
+      <c r="K232" s="25" t="n"/>
+      <c r="L232" s="21">
+        <f>IF(OR(E232&lt;&gt;"",J232&lt;&gt;""),"Занято",IF(AND(F231="Повторный приём (1 час)",A231=A232),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7579,10 +7816,11 @@
       <c r="F233" s="23" t="n"/>
       <c r="G233" s="24" t="n"/>
       <c r="H233" s="24" t="n"/>
-      <c r="I233" s="21" t="n"/>
-      <c r="J233" s="25" t="n"/>
-      <c r="K233" s="21">
-        <f>IF(OR(E233&lt;&gt;"",I233&lt;&gt;""),"Занято",IF(AND(F232="Повторный приём (1 час)",A232=A233),"Занято","Свободно"))</f>
+      <c r="I233" s="23" t="n"/>
+      <c r="J233" s="21" t="n"/>
+      <c r="K233" s="25" t="n"/>
+      <c r="L233" s="21">
+        <f>IF(OR(E233&lt;&gt;"",J233&lt;&gt;""),"Занято",IF(AND(F232="Повторный приём (1 час)",A232=A233),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7609,10 +7847,11 @@
       <c r="F234" s="5" t="n"/>
       <c r="G234" s="6" t="n"/>
       <c r="H234" s="6" t="n"/>
-      <c r="I234" s="3" t="n"/>
-      <c r="J234" s="7" t="n"/>
-      <c r="K234" s="3">
-        <f>IF(OR(E234&lt;&gt;"",I234&lt;&gt;""),"Занято",IF(AND(F233="Повторный приём (1 час)",A233=A234),"Занято","Свободно"))</f>
+      <c r="I234" s="5" t="n"/>
+      <c r="J234" s="3" t="n"/>
+      <c r="K234" s="7" t="n"/>
+      <c r="L234" s="3">
+        <f>IF(OR(E234&lt;&gt;"",J234&lt;&gt;""),"Занято",IF(AND(F233="Повторный приём (1 час)",A233=A234),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7639,10 +7878,11 @@
       <c r="F235" s="11" t="n"/>
       <c r="G235" s="12" t="n"/>
       <c r="H235" s="12" t="n"/>
-      <c r="I235" s="9" t="n"/>
-      <c r="J235" s="13" t="n"/>
-      <c r="K235" s="9">
-        <f>IF(OR(E235&lt;&gt;"",I235&lt;&gt;""),"Занято",IF(AND(F234="Повторный приём (1 час)",A234=A235),"Занято","Свободно"))</f>
+      <c r="I235" s="11" t="n"/>
+      <c r="J235" s="9" t="n"/>
+      <c r="K235" s="13" t="n"/>
+      <c r="L235" s="9">
+        <f>IF(OR(E235&lt;&gt;"",J235&lt;&gt;""),"Занято",IF(AND(F234="Повторный приём (1 час)",A234=A235),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7669,10 +7909,11 @@
       <c r="F236" s="11" t="n"/>
       <c r="G236" s="12" t="n"/>
       <c r="H236" s="12" t="n"/>
-      <c r="I236" s="9" t="n"/>
-      <c r="J236" s="13" t="n"/>
-      <c r="K236" s="9">
-        <f>IF(OR(E236&lt;&gt;"",I236&lt;&gt;""),"Занято",IF(AND(F235="Повторный приём (1 час)",A235=A236),"Занято","Свободно"))</f>
+      <c r="I236" s="11" t="n"/>
+      <c r="J236" s="9" t="n"/>
+      <c r="K236" s="13" t="n"/>
+      <c r="L236" s="9">
+        <f>IF(OR(E236&lt;&gt;"",J236&lt;&gt;""),"Занято",IF(AND(F235="Повторный приём (1 час)",A235=A236),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7699,10 +7940,11 @@
       <c r="F237" s="11" t="n"/>
       <c r="G237" s="12" t="n"/>
       <c r="H237" s="12" t="n"/>
-      <c r="I237" s="9" t="n"/>
-      <c r="J237" s="13" t="n"/>
-      <c r="K237" s="9">
-        <f>IF(OR(E237&lt;&gt;"",I237&lt;&gt;""),"Занято",IF(AND(F236="Повторный приём (1 час)",A236=A237),"Занято","Свободно"))</f>
+      <c r="I237" s="11" t="n"/>
+      <c r="J237" s="9" t="n"/>
+      <c r="K237" s="13" t="n"/>
+      <c r="L237" s="9">
+        <f>IF(OR(E237&lt;&gt;"",J237&lt;&gt;""),"Занято",IF(AND(F236="Повторный приём (1 час)",A236=A237),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7729,10 +7971,11 @@
       <c r="F238" s="11" t="n"/>
       <c r="G238" s="12" t="n"/>
       <c r="H238" s="12" t="n"/>
-      <c r="I238" s="9" t="n"/>
-      <c r="J238" s="13" t="n"/>
-      <c r="K238" s="9">
-        <f>IF(OR(E238&lt;&gt;"",I238&lt;&gt;""),"Занято",IF(AND(F237="Повторный приём (1 час)",A237=A238),"Занято","Свободно"))</f>
+      <c r="I238" s="11" t="n"/>
+      <c r="J238" s="9" t="n"/>
+      <c r="K238" s="13" t="n"/>
+      <c r="L238" s="9">
+        <f>IF(OR(E238&lt;&gt;"",J238&lt;&gt;""),"Занято",IF(AND(F237="Повторный приём (1 час)",A237=A238),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7759,10 +8002,11 @@
       <c r="F239" s="11" t="n"/>
       <c r="G239" s="12" t="n"/>
       <c r="H239" s="12" t="n"/>
-      <c r="I239" s="9" t="n"/>
-      <c r="J239" s="13" t="n"/>
-      <c r="K239" s="9">
-        <f>IF(OR(E239&lt;&gt;"",I239&lt;&gt;""),"Занято",IF(AND(F238="Повторный приём (1 час)",A238=A239),"Занято","Свободно"))</f>
+      <c r="I239" s="11" t="n"/>
+      <c r="J239" s="9" t="n"/>
+      <c r="K239" s="13" t="n"/>
+      <c r="L239" s="9">
+        <f>IF(OR(E239&lt;&gt;"",J239&lt;&gt;""),"Занято",IF(AND(F238="Повторный приём (1 час)",A238=A239),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7789,10 +8033,11 @@
       <c r="F240" s="11" t="n"/>
       <c r="G240" s="12" t="n"/>
       <c r="H240" s="12" t="n"/>
-      <c r="I240" s="9" t="n"/>
-      <c r="J240" s="13" t="n"/>
-      <c r="K240" s="9">
-        <f>IF(OR(E240&lt;&gt;"",I240&lt;&gt;""),"Занято",IF(AND(F239="Повторный приём (1 час)",A239=A240),"Занято","Свободно"))</f>
+      <c r="I240" s="11" t="n"/>
+      <c r="J240" s="9" t="n"/>
+      <c r="K240" s="13" t="n"/>
+      <c r="L240" s="9">
+        <f>IF(OR(E240&lt;&gt;"",J240&lt;&gt;""),"Занято",IF(AND(F239="Повторный приём (1 час)",A239=A240),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7819,10 +8064,11 @@
       <c r="F241" s="11" t="n"/>
       <c r="G241" s="12" t="n"/>
       <c r="H241" s="12" t="n"/>
-      <c r="I241" s="9" t="n"/>
-      <c r="J241" s="13" t="n"/>
-      <c r="K241" s="9">
-        <f>IF(OR(E241&lt;&gt;"",I241&lt;&gt;""),"Занято",IF(AND(F240="Повторный приём (1 час)",A240=A241),"Занято","Свободно"))</f>
+      <c r="I241" s="11" t="n"/>
+      <c r="J241" s="9" t="n"/>
+      <c r="K241" s="13" t="n"/>
+      <c r="L241" s="9">
+        <f>IF(OR(E241&lt;&gt;"",J241&lt;&gt;""),"Занято",IF(AND(F240="Повторный приём (1 час)",A240=A241),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7849,10 +8095,11 @@
       <c r="F242" s="17" t="n"/>
       <c r="G242" s="18" t="n"/>
       <c r="H242" s="18" t="n"/>
-      <c r="I242" s="15" t="n"/>
-      <c r="J242" s="19" t="n"/>
-      <c r="K242" s="15">
-        <f>IF(OR(E242&lt;&gt;"",I242&lt;&gt;""),"Занято",IF(AND(F241="Повторный приём (1 час)",A241=A242),"Занято","Свободно"))</f>
+      <c r="I242" s="17" t="n"/>
+      <c r="J242" s="15" t="n"/>
+      <c r="K242" s="19" t="n"/>
+      <c r="L242" s="15">
+        <f>IF(OR(E242&lt;&gt;"",J242&lt;&gt;""),"Занято",IF(AND(F241="Повторный приём (1 час)",A241=A242),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7879,10 +8126,11 @@
       <c r="F243" s="23" t="n"/>
       <c r="G243" s="24" t="n"/>
       <c r="H243" s="24" t="n"/>
-      <c r="I243" s="21" t="n"/>
-      <c r="J243" s="25" t="n"/>
-      <c r="K243" s="21">
-        <f>IF(OR(E243&lt;&gt;"",I243&lt;&gt;""),"Занято",IF(AND(F242="Повторный приём (1 час)",A242=A243),"Занято","Свободно"))</f>
+      <c r="I243" s="23" t="n"/>
+      <c r="J243" s="21" t="n"/>
+      <c r="K243" s="25" t="n"/>
+      <c r="L243" s="21">
+        <f>IF(OR(E243&lt;&gt;"",J243&lt;&gt;""),"Занято",IF(AND(F242="Повторный приём (1 час)",A242=A243),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7909,10 +8157,11 @@
       <c r="F244" s="23" t="n"/>
       <c r="G244" s="24" t="n"/>
       <c r="H244" s="24" t="n"/>
-      <c r="I244" s="21" t="n"/>
-      <c r="J244" s="25" t="n"/>
-      <c r="K244" s="21">
-        <f>IF(OR(E244&lt;&gt;"",I244&lt;&gt;""),"Занято",IF(AND(F243="Повторный приём (1 час)",A243=A244),"Занято","Свободно"))</f>
+      <c r="I244" s="23" t="n"/>
+      <c r="J244" s="21" t="n"/>
+      <c r="K244" s="25" t="n"/>
+      <c r="L244" s="21">
+        <f>IF(OR(E244&lt;&gt;"",J244&lt;&gt;""),"Занято",IF(AND(F243="Повторный приём (1 час)",A243=A244),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7939,10 +8188,11 @@
       <c r="F245" s="23" t="n"/>
       <c r="G245" s="24" t="n"/>
       <c r="H245" s="24" t="n"/>
-      <c r="I245" s="21" t="n"/>
-      <c r="J245" s="25" t="n"/>
-      <c r="K245" s="21">
-        <f>IF(OR(E245&lt;&gt;"",I245&lt;&gt;""),"Занято",IF(AND(F244="Повторный приём (1 час)",A244=A245),"Занято","Свободно"))</f>
+      <c r="I245" s="23" t="n"/>
+      <c r="J245" s="21" t="n"/>
+      <c r="K245" s="25" t="n"/>
+      <c r="L245" s="21">
+        <f>IF(OR(E245&lt;&gt;"",J245&lt;&gt;""),"Занято",IF(AND(F244="Повторный приём (1 час)",A244=A245),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7969,10 +8219,11 @@
       <c r="F246" s="23" t="n"/>
       <c r="G246" s="24" t="n"/>
       <c r="H246" s="24" t="n"/>
-      <c r="I246" s="21" t="n"/>
-      <c r="J246" s="25" t="n"/>
-      <c r="K246" s="21">
-        <f>IF(OR(E246&lt;&gt;"",I246&lt;&gt;""),"Занято",IF(AND(F245="Повторный приём (1 час)",A245=A246),"Занято","Свободно"))</f>
+      <c r="I246" s="23" t="n"/>
+      <c r="J246" s="21" t="n"/>
+      <c r="K246" s="25" t="n"/>
+      <c r="L246" s="21">
+        <f>IF(OR(E246&lt;&gt;"",J246&lt;&gt;""),"Занято",IF(AND(F245="Повторный приём (1 час)",A245=A246),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -7999,10 +8250,11 @@
       <c r="F247" s="23" t="n"/>
       <c r="G247" s="24" t="n"/>
       <c r="H247" s="24" t="n"/>
-      <c r="I247" s="21" t="n"/>
-      <c r="J247" s="25" t="n"/>
-      <c r="K247" s="21">
-        <f>IF(OR(E247&lt;&gt;"",I247&lt;&gt;""),"Занято",IF(AND(F246="Повторный приём (1 час)",A246=A247),"Занято","Свободно"))</f>
+      <c r="I247" s="23" t="n"/>
+      <c r="J247" s="21" t="n"/>
+      <c r="K247" s="25" t="n"/>
+      <c r="L247" s="21">
+        <f>IF(OR(E247&lt;&gt;"",J247&lt;&gt;""),"Занято",IF(AND(F246="Повторный приём (1 час)",A246=A247),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8029,10 +8281,11 @@
       <c r="F248" s="23" t="n"/>
       <c r="G248" s="24" t="n"/>
       <c r="H248" s="24" t="n"/>
-      <c r="I248" s="21" t="n"/>
-      <c r="J248" s="25" t="n"/>
-      <c r="K248" s="21">
-        <f>IF(OR(E248&lt;&gt;"",I248&lt;&gt;""),"Занято",IF(AND(F247="Повторный приём (1 час)",A247=A248),"Занято","Свободно"))</f>
+      <c r="I248" s="23" t="n"/>
+      <c r="J248" s="21" t="n"/>
+      <c r="K248" s="25" t="n"/>
+      <c r="L248" s="21">
+        <f>IF(OR(E248&lt;&gt;"",J248&lt;&gt;""),"Занято",IF(AND(F247="Повторный приём (1 час)",A247=A248),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8059,10 +8312,11 @@
       <c r="F249" s="23" t="n"/>
       <c r="G249" s="24" t="n"/>
       <c r="H249" s="24" t="n"/>
-      <c r="I249" s="21" t="n"/>
-      <c r="J249" s="25" t="n"/>
-      <c r="K249" s="21">
-        <f>IF(OR(E249&lt;&gt;"",I249&lt;&gt;""),"Занято",IF(AND(F248="Повторный приём (1 час)",A248=A249),"Занято","Свободно"))</f>
+      <c r="I249" s="23" t="n"/>
+      <c r="J249" s="21" t="n"/>
+      <c r="K249" s="25" t="n"/>
+      <c r="L249" s="21">
+        <f>IF(OR(E249&lt;&gt;"",J249&lt;&gt;""),"Занято",IF(AND(F248="Повторный приём (1 час)",A248=A249),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8089,10 +8343,11 @@
       <c r="F250" s="23" t="n"/>
       <c r="G250" s="24" t="n"/>
       <c r="H250" s="24" t="n"/>
-      <c r="I250" s="21" t="n"/>
-      <c r="J250" s="25" t="n"/>
-      <c r="K250" s="21">
-        <f>IF(OR(E250&lt;&gt;"",I250&lt;&gt;""),"Занято",IF(AND(F249="Повторный приём (1 час)",A249=A250),"Занято","Свободно"))</f>
+      <c r="I250" s="23" t="n"/>
+      <c r="J250" s="21" t="n"/>
+      <c r="K250" s="25" t="n"/>
+      <c r="L250" s="21">
+        <f>IF(OR(E250&lt;&gt;"",J250&lt;&gt;""),"Занято",IF(AND(F249="Повторный приём (1 час)",A249=A250),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8119,10 +8374,11 @@
       <c r="F251" s="23" t="n"/>
       <c r="G251" s="24" t="n"/>
       <c r="H251" s="24" t="n"/>
-      <c r="I251" s="21" t="n"/>
-      <c r="J251" s="25" t="n"/>
-      <c r="K251" s="21">
-        <f>IF(OR(E251&lt;&gt;"",I251&lt;&gt;""),"Занято",IF(AND(F250="Повторный приём (1 час)",A250=A251),"Занято","Свободно"))</f>
+      <c r="I251" s="23" t="n"/>
+      <c r="J251" s="21" t="n"/>
+      <c r="K251" s="25" t="n"/>
+      <c r="L251" s="21">
+        <f>IF(OR(E251&lt;&gt;"",J251&lt;&gt;""),"Занято",IF(AND(F250="Повторный приём (1 час)",A250=A251),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8149,10 +8405,11 @@
       <c r="F252" s="23" t="n"/>
       <c r="G252" s="24" t="n"/>
       <c r="H252" s="24" t="n"/>
-      <c r="I252" s="21" t="n"/>
-      <c r="J252" s="25" t="n"/>
-      <c r="K252" s="21">
-        <f>IF(OR(E252&lt;&gt;"",I252&lt;&gt;""),"Занято",IF(AND(F251="Повторный приём (1 час)",A251=A252),"Занято","Свободно"))</f>
+      <c r="I252" s="23" t="n"/>
+      <c r="J252" s="21" t="n"/>
+      <c r="K252" s="25" t="n"/>
+      <c r="L252" s="21">
+        <f>IF(OR(E252&lt;&gt;"",J252&lt;&gt;""),"Занято",IF(AND(F251="Повторный приём (1 час)",A251=A252),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8179,10 +8436,11 @@
       <c r="F253" s="23" t="n"/>
       <c r="G253" s="24" t="n"/>
       <c r="H253" s="24" t="n"/>
-      <c r="I253" s="21" t="n"/>
-      <c r="J253" s="25" t="n"/>
-      <c r="K253" s="21">
-        <f>IF(OR(E253&lt;&gt;"",I253&lt;&gt;""),"Занято",IF(AND(F252="Повторный приём (1 час)",A252=A253),"Занято","Свободно"))</f>
+      <c r="I253" s="23" t="n"/>
+      <c r="J253" s="21" t="n"/>
+      <c r="K253" s="25" t="n"/>
+      <c r="L253" s="21">
+        <f>IF(OR(E253&lt;&gt;"",J253&lt;&gt;""),"Занято",IF(AND(F252="Повторный приём (1 час)",A252=A253),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8209,10 +8467,11 @@
       <c r="F254" s="23" t="n"/>
       <c r="G254" s="24" t="n"/>
       <c r="H254" s="24" t="n"/>
-      <c r="I254" s="21" t="n"/>
-      <c r="J254" s="25" t="n"/>
-      <c r="K254" s="21">
-        <f>IF(OR(E254&lt;&gt;"",I254&lt;&gt;""),"Занято",IF(AND(F253="Повторный приём (1 час)",A253=A254),"Занято","Свободно"))</f>
+      <c r="I254" s="23" t="n"/>
+      <c r="J254" s="21" t="n"/>
+      <c r="K254" s="25" t="n"/>
+      <c r="L254" s="21">
+        <f>IF(OR(E254&lt;&gt;"",J254&lt;&gt;""),"Занято",IF(AND(F253="Повторный приём (1 час)",A253=A254),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8239,10 +8498,11 @@
       <c r="F255" s="23" t="n"/>
       <c r="G255" s="24" t="n"/>
       <c r="H255" s="24" t="n"/>
-      <c r="I255" s="21" t="n"/>
-      <c r="J255" s="25" t="n"/>
-      <c r="K255" s="21">
-        <f>IF(OR(E255&lt;&gt;"",I255&lt;&gt;""),"Занято",IF(AND(F254="Повторный приём (1 час)",A254=A255),"Занято","Свободно"))</f>
+      <c r="I255" s="23" t="n"/>
+      <c r="J255" s="21" t="n"/>
+      <c r="K255" s="25" t="n"/>
+      <c r="L255" s="21">
+        <f>IF(OR(E255&lt;&gt;"",J255&lt;&gt;""),"Занято",IF(AND(F254="Повторный приём (1 час)",A254=A255),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8269,10 +8529,11 @@
       <c r="F256" s="23" t="n"/>
       <c r="G256" s="24" t="n"/>
       <c r="H256" s="24" t="n"/>
-      <c r="I256" s="21" t="n"/>
-      <c r="J256" s="25" t="n"/>
-      <c r="K256" s="21">
-        <f>IF(OR(E256&lt;&gt;"",I256&lt;&gt;""),"Занято",IF(AND(F255="Повторный приём (1 час)",A255=A256),"Занято","Свободно"))</f>
+      <c r="I256" s="23" t="n"/>
+      <c r="J256" s="21" t="n"/>
+      <c r="K256" s="25" t="n"/>
+      <c r="L256" s="21">
+        <f>IF(OR(E256&lt;&gt;"",J256&lt;&gt;""),"Занято",IF(AND(F255="Повторный приём (1 час)",A255=A256),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8299,10 +8560,11 @@
       <c r="F257" s="23" t="n"/>
       <c r="G257" s="24" t="n"/>
       <c r="H257" s="24" t="n"/>
-      <c r="I257" s="21" t="n"/>
-      <c r="J257" s="25" t="n"/>
-      <c r="K257" s="21">
-        <f>IF(OR(E257&lt;&gt;"",I257&lt;&gt;""),"Занято",IF(AND(F256="Повторный приём (1 час)",A256=A257),"Занято","Свободно"))</f>
+      <c r="I257" s="23" t="n"/>
+      <c r="J257" s="21" t="n"/>
+      <c r="K257" s="25" t="n"/>
+      <c r="L257" s="21">
+        <f>IF(OR(E257&lt;&gt;"",J257&lt;&gt;""),"Занято",IF(AND(F256="Повторный приём (1 час)",A256=A257),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8329,10 +8591,11 @@
       <c r="F258" s="23" t="n"/>
       <c r="G258" s="24" t="n"/>
       <c r="H258" s="24" t="n"/>
-      <c r="I258" s="21" t="n"/>
-      <c r="J258" s="25" t="n"/>
-      <c r="K258" s="21">
-        <f>IF(OR(E258&lt;&gt;"",I258&lt;&gt;""),"Занято",IF(AND(F257="Повторный приём (1 час)",A257=A258),"Занято","Свободно"))</f>
+      <c r="I258" s="23" t="n"/>
+      <c r="J258" s="21" t="n"/>
+      <c r="K258" s="25" t="n"/>
+      <c r="L258" s="21">
+        <f>IF(OR(E258&lt;&gt;"",J258&lt;&gt;""),"Занято",IF(AND(F257="Повторный приём (1 час)",A257=A258),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8359,10 +8622,11 @@
       <c r="F259" s="23" t="n"/>
       <c r="G259" s="24" t="n"/>
       <c r="H259" s="24" t="n"/>
-      <c r="I259" s="21" t="n"/>
-      <c r="J259" s="25" t="n"/>
-      <c r="K259" s="21">
-        <f>IF(OR(E259&lt;&gt;"",I259&lt;&gt;""),"Занято",IF(AND(F258="Повторный приём (1 час)",A258=A259),"Занято","Свободно"))</f>
+      <c r="I259" s="23" t="n"/>
+      <c r="J259" s="21" t="n"/>
+      <c r="K259" s="25" t="n"/>
+      <c r="L259" s="21">
+        <f>IF(OR(E259&lt;&gt;"",J259&lt;&gt;""),"Занято",IF(AND(F258="Повторный приём (1 час)",A258=A259),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8389,10 +8653,11 @@
       <c r="F260" s="5" t="n"/>
       <c r="G260" s="6" t="n"/>
       <c r="H260" s="6" t="n"/>
-      <c r="I260" s="3" t="n"/>
-      <c r="J260" s="7" t="n"/>
-      <c r="K260" s="3">
-        <f>IF(OR(E260&lt;&gt;"",I260&lt;&gt;""),"Занято",IF(AND(F259="Повторный приём (1 час)",A259=A260),"Занято","Свободно"))</f>
+      <c r="I260" s="5" t="n"/>
+      <c r="J260" s="3" t="n"/>
+      <c r="K260" s="7" t="n"/>
+      <c r="L260" s="3">
+        <f>IF(OR(E260&lt;&gt;"",J260&lt;&gt;""),"Занято",IF(AND(F259="Повторный приём (1 час)",A259=A260),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8419,10 +8684,11 @@
       <c r="F261" s="11" t="n"/>
       <c r="G261" s="12" t="n"/>
       <c r="H261" s="12" t="n"/>
-      <c r="I261" s="9" t="n"/>
-      <c r="J261" s="13" t="n"/>
-      <c r="K261" s="9">
-        <f>IF(OR(E261&lt;&gt;"",I261&lt;&gt;""),"Занято",IF(AND(F260="Повторный приём (1 час)",A260=A261),"Занято","Свободно"))</f>
+      <c r="I261" s="11" t="n"/>
+      <c r="J261" s="9" t="n"/>
+      <c r="K261" s="13" t="n"/>
+      <c r="L261" s="9">
+        <f>IF(OR(E261&lt;&gt;"",J261&lt;&gt;""),"Занято",IF(AND(F260="Повторный приём (1 час)",A260=A261),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8449,10 +8715,11 @@
       <c r="F262" s="11" t="n"/>
       <c r="G262" s="12" t="n"/>
       <c r="H262" s="12" t="n"/>
-      <c r="I262" s="9" t="n"/>
-      <c r="J262" s="13" t="n"/>
-      <c r="K262" s="9">
-        <f>IF(OR(E262&lt;&gt;"",I262&lt;&gt;""),"Занято",IF(AND(F261="Повторный приём (1 час)",A261=A262),"Занято","Свободно"))</f>
+      <c r="I262" s="11" t="n"/>
+      <c r="J262" s="9" t="n"/>
+      <c r="K262" s="13" t="n"/>
+      <c r="L262" s="9">
+        <f>IF(OR(E262&lt;&gt;"",J262&lt;&gt;""),"Занято",IF(AND(F261="Повторный приём (1 час)",A261=A262),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8479,10 +8746,11 @@
       <c r="F263" s="11" t="n"/>
       <c r="G263" s="12" t="n"/>
       <c r="H263" s="12" t="n"/>
-      <c r="I263" s="9" t="n"/>
-      <c r="J263" s="13" t="n"/>
-      <c r="K263" s="9">
-        <f>IF(OR(E263&lt;&gt;"",I263&lt;&gt;""),"Занято",IF(AND(F262="Повторный приём (1 час)",A262=A263),"Занято","Свободно"))</f>
+      <c r="I263" s="11" t="n"/>
+      <c r="J263" s="9" t="n"/>
+      <c r="K263" s="13" t="n"/>
+      <c r="L263" s="9">
+        <f>IF(OR(E263&lt;&gt;"",J263&lt;&gt;""),"Занято",IF(AND(F262="Повторный приём (1 час)",A262=A263),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8509,10 +8777,11 @@
       <c r="F264" s="11" t="n"/>
       <c r="G264" s="12" t="n"/>
       <c r="H264" s="12" t="n"/>
-      <c r="I264" s="9" t="n"/>
-      <c r="J264" s="13" t="n"/>
-      <c r="K264" s="9">
-        <f>IF(OR(E264&lt;&gt;"",I264&lt;&gt;""),"Занято",IF(AND(F263="Повторный приём (1 час)",A263=A264),"Занято","Свободно"))</f>
+      <c r="I264" s="11" t="n"/>
+      <c r="J264" s="9" t="n"/>
+      <c r="K264" s="13" t="n"/>
+      <c r="L264" s="9">
+        <f>IF(OR(E264&lt;&gt;"",J264&lt;&gt;""),"Занято",IF(AND(F263="Повторный приём (1 час)",A263=A264),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8539,10 +8808,11 @@
       <c r="F265" s="11" t="n"/>
       <c r="G265" s="12" t="n"/>
       <c r="H265" s="12" t="n"/>
-      <c r="I265" s="9" t="n"/>
-      <c r="J265" s="13" t="n"/>
-      <c r="K265" s="9">
-        <f>IF(OR(E265&lt;&gt;"",I265&lt;&gt;""),"Занято",IF(AND(F264="Повторный приём (1 час)",A264=A265),"Занято","Свободно"))</f>
+      <c r="I265" s="11" t="n"/>
+      <c r="J265" s="9" t="n"/>
+      <c r="K265" s="13" t="n"/>
+      <c r="L265" s="9">
+        <f>IF(OR(E265&lt;&gt;"",J265&lt;&gt;""),"Занято",IF(AND(F264="Повторный приём (1 час)",A264=A265),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8569,10 +8839,11 @@
       <c r="F266" s="11" t="n"/>
       <c r="G266" s="12" t="n"/>
       <c r="H266" s="12" t="n"/>
-      <c r="I266" s="9" t="n"/>
-      <c r="J266" s="13" t="n"/>
-      <c r="K266" s="9">
-        <f>IF(OR(E266&lt;&gt;"",I266&lt;&gt;""),"Занято",IF(AND(F265="Повторный приём (1 час)",A265=A266),"Занято","Свободно"))</f>
+      <c r="I266" s="11" t="n"/>
+      <c r="J266" s="9" t="n"/>
+      <c r="K266" s="13" t="n"/>
+      <c r="L266" s="9">
+        <f>IF(OR(E266&lt;&gt;"",J266&lt;&gt;""),"Занято",IF(AND(F265="Повторный приём (1 час)",A265=A266),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8599,10 +8870,11 @@
       <c r="F267" s="11" t="n"/>
       <c r="G267" s="12" t="n"/>
       <c r="H267" s="12" t="n"/>
-      <c r="I267" s="9" t="n"/>
-      <c r="J267" s="13" t="n"/>
-      <c r="K267" s="9">
-        <f>IF(OR(E267&lt;&gt;"",I267&lt;&gt;""),"Занято",IF(AND(F266="Повторный приём (1 час)",A266=A267),"Занято","Свободно"))</f>
+      <c r="I267" s="11" t="n"/>
+      <c r="J267" s="9" t="n"/>
+      <c r="K267" s="13" t="n"/>
+      <c r="L267" s="9">
+        <f>IF(OR(E267&lt;&gt;"",J267&lt;&gt;""),"Занято",IF(AND(F266="Повторный приём (1 час)",A266=A267),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8629,10 +8901,11 @@
       <c r="F268" s="11" t="n"/>
       <c r="G268" s="12" t="n"/>
       <c r="H268" s="12" t="n"/>
-      <c r="I268" s="9" t="n"/>
-      <c r="J268" s="13" t="n"/>
-      <c r="K268" s="9">
-        <f>IF(OR(E268&lt;&gt;"",I268&lt;&gt;""),"Занято",IF(AND(F267="Повторный приём (1 час)",A267=A268),"Занято","Свободно"))</f>
+      <c r="I268" s="11" t="n"/>
+      <c r="J268" s="9" t="n"/>
+      <c r="K268" s="13" t="n"/>
+      <c r="L268" s="9">
+        <f>IF(OR(E268&lt;&gt;"",J268&lt;&gt;""),"Занято",IF(AND(F267="Повторный приём (1 час)",A267=A268),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8659,10 +8932,11 @@
       <c r="F269" s="11" t="n"/>
       <c r="G269" s="12" t="n"/>
       <c r="H269" s="12" t="n"/>
-      <c r="I269" s="9" t="n"/>
-      <c r="J269" s="13" t="n"/>
-      <c r="K269" s="9">
-        <f>IF(OR(E269&lt;&gt;"",I269&lt;&gt;""),"Занято",IF(AND(F268="Повторный приём (1 час)",A268=A269),"Занято","Свободно"))</f>
+      <c r="I269" s="11" t="n"/>
+      <c r="J269" s="9" t="n"/>
+      <c r="K269" s="13" t="n"/>
+      <c r="L269" s="9">
+        <f>IF(OR(E269&lt;&gt;"",J269&lt;&gt;""),"Занято",IF(AND(F268="Повторный приём (1 час)",A268=A269),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8689,10 +8963,11 @@
       <c r="F270" s="11" t="n"/>
       <c r="G270" s="12" t="n"/>
       <c r="H270" s="12" t="n"/>
-      <c r="I270" s="9" t="n"/>
-      <c r="J270" s="13" t="n"/>
-      <c r="K270" s="9">
-        <f>IF(OR(E270&lt;&gt;"",I270&lt;&gt;""),"Занято",IF(AND(F269="Повторный приём (1 час)",A269=A270),"Занято","Свободно"))</f>
+      <c r="I270" s="11" t="n"/>
+      <c r="J270" s="9" t="n"/>
+      <c r="K270" s="13" t="n"/>
+      <c r="L270" s="9">
+        <f>IF(OR(E270&lt;&gt;"",J270&lt;&gt;""),"Занято",IF(AND(F269="Повторный приём (1 час)",A269=A270),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8719,10 +8994,11 @@
       <c r="F271" s="11" t="n"/>
       <c r="G271" s="12" t="n"/>
       <c r="H271" s="12" t="n"/>
-      <c r="I271" s="9" t="n"/>
-      <c r="J271" s="13" t="n"/>
-      <c r="K271" s="9">
-        <f>IF(OR(E271&lt;&gt;"",I271&lt;&gt;""),"Занято",IF(AND(F270="Повторный приём (1 час)",A270=A271),"Занято","Свободно"))</f>
+      <c r="I271" s="11" t="n"/>
+      <c r="J271" s="9" t="n"/>
+      <c r="K271" s="13" t="n"/>
+      <c r="L271" s="9">
+        <f>IF(OR(E271&lt;&gt;"",J271&lt;&gt;""),"Занято",IF(AND(F270="Повторный приём (1 час)",A270=A271),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8749,10 +9025,11 @@
       <c r="F272" s="11" t="n"/>
       <c r="G272" s="12" t="n"/>
       <c r="H272" s="12" t="n"/>
-      <c r="I272" s="9" t="n"/>
-      <c r="J272" s="13" t="n"/>
-      <c r="K272" s="9">
-        <f>IF(OR(E272&lt;&gt;"",I272&lt;&gt;""),"Занято",IF(AND(F271="Повторный приём (1 час)",A271=A272),"Занято","Свободно"))</f>
+      <c r="I272" s="11" t="n"/>
+      <c r="J272" s="9" t="n"/>
+      <c r="K272" s="13" t="n"/>
+      <c r="L272" s="9">
+        <f>IF(OR(E272&lt;&gt;"",J272&lt;&gt;""),"Занято",IF(AND(F271="Повторный приём (1 час)",A271=A272),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8779,10 +9056,11 @@
       <c r="F273" s="11" t="n"/>
       <c r="G273" s="12" t="n"/>
       <c r="H273" s="12" t="n"/>
-      <c r="I273" s="9" t="n"/>
-      <c r="J273" s="13" t="n"/>
-      <c r="K273" s="9">
-        <f>IF(OR(E273&lt;&gt;"",I273&lt;&gt;""),"Занято",IF(AND(F272="Повторный приём (1 час)",A272=A273),"Занято","Свободно"))</f>
+      <c r="I273" s="11" t="n"/>
+      <c r="J273" s="9" t="n"/>
+      <c r="K273" s="13" t="n"/>
+      <c r="L273" s="9">
+        <f>IF(OR(E273&lt;&gt;"",J273&lt;&gt;""),"Занято",IF(AND(F272="Повторный приём (1 час)",A272=A273),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8809,10 +9087,11 @@
       <c r="F274" s="11" t="n"/>
       <c r="G274" s="12" t="n"/>
       <c r="H274" s="12" t="n"/>
-      <c r="I274" s="9" t="n"/>
-      <c r="J274" s="13" t="n"/>
-      <c r="K274" s="9">
-        <f>IF(OR(E274&lt;&gt;"",I274&lt;&gt;""),"Занято",IF(AND(F273="Повторный приём (1 час)",A273=A274),"Занято","Свободно"))</f>
+      <c r="I274" s="11" t="n"/>
+      <c r="J274" s="9" t="n"/>
+      <c r="K274" s="13" t="n"/>
+      <c r="L274" s="9">
+        <f>IF(OR(E274&lt;&gt;"",J274&lt;&gt;""),"Занято",IF(AND(F273="Повторный приём (1 час)",A273=A274),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8839,10 +9118,11 @@
       <c r="F275" s="11" t="n"/>
       <c r="G275" s="12" t="n"/>
       <c r="H275" s="12" t="n"/>
-      <c r="I275" s="9" t="n"/>
-      <c r="J275" s="13" t="n"/>
-      <c r="K275" s="9">
-        <f>IF(OR(E275&lt;&gt;"",I275&lt;&gt;""),"Занято",IF(AND(F274="Повторный приём (1 час)",A274=A275),"Занято","Свободно"))</f>
+      <c r="I275" s="11" t="n"/>
+      <c r="J275" s="9" t="n"/>
+      <c r="K275" s="13" t="n"/>
+      <c r="L275" s="9">
+        <f>IF(OR(E275&lt;&gt;"",J275&lt;&gt;""),"Занято",IF(AND(F274="Повторный приём (1 час)",A274=A275),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8869,10 +9149,11 @@
       <c r="F276" s="11" t="n"/>
       <c r="G276" s="12" t="n"/>
       <c r="H276" s="12" t="n"/>
-      <c r="I276" s="9" t="n"/>
-      <c r="J276" s="13" t="n"/>
-      <c r="K276" s="9">
-        <f>IF(OR(E276&lt;&gt;"",I276&lt;&gt;""),"Занято",IF(AND(F275="Повторный приём (1 час)",A275=A276),"Занято","Свободно"))</f>
+      <c r="I276" s="11" t="n"/>
+      <c r="J276" s="9" t="n"/>
+      <c r="K276" s="13" t="n"/>
+      <c r="L276" s="9">
+        <f>IF(OR(E276&lt;&gt;"",J276&lt;&gt;""),"Занято",IF(AND(F275="Повторный приём (1 час)",A275=A276),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8899,10 +9180,11 @@
       <c r="F277" s="11" t="n"/>
       <c r="G277" s="12" t="n"/>
       <c r="H277" s="12" t="n"/>
-      <c r="I277" s="9" t="n"/>
-      <c r="J277" s="13" t="n"/>
-      <c r="K277" s="9">
-        <f>IF(OR(E277&lt;&gt;"",I277&lt;&gt;""),"Занято",IF(AND(F276="Повторный приём (1 час)",A276=A277),"Занято","Свободно"))</f>
+      <c r="I277" s="11" t="n"/>
+      <c r="J277" s="9" t="n"/>
+      <c r="K277" s="13" t="n"/>
+      <c r="L277" s="9">
+        <f>IF(OR(E277&lt;&gt;"",J277&lt;&gt;""),"Занято",IF(AND(F276="Повторный приём (1 час)",A276=A277),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8929,10 +9211,11 @@
       <c r="F278" s="17" t="n"/>
       <c r="G278" s="18" t="n"/>
       <c r="H278" s="18" t="n"/>
-      <c r="I278" s="15" t="n"/>
-      <c r="J278" s="19" t="n"/>
-      <c r="K278" s="15">
-        <f>IF(OR(E278&lt;&gt;"",I278&lt;&gt;""),"Занято",IF(AND(F277="Повторный приём (1 час)",A277=A278),"Занято","Свободно"))</f>
+      <c r="I278" s="17" t="n"/>
+      <c r="J278" s="15" t="n"/>
+      <c r="K278" s="19" t="n"/>
+      <c r="L278" s="15">
+        <f>IF(OR(E278&lt;&gt;"",J278&lt;&gt;""),"Занято",IF(AND(F277="Повторный приём (1 час)",A277=A278),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8959,10 +9242,11 @@
       <c r="F279" s="23" t="n"/>
       <c r="G279" s="24" t="n"/>
       <c r="H279" s="24" t="n"/>
-      <c r="I279" s="21" t="n"/>
-      <c r="J279" s="25" t="n"/>
-      <c r="K279" s="21">
-        <f>IF(OR(E279&lt;&gt;"",I279&lt;&gt;""),"Занято",IF(AND(F278="Повторный приём (1 час)",A278=A279),"Занято","Свободно"))</f>
+      <c r="I279" s="23" t="n"/>
+      <c r="J279" s="21" t="n"/>
+      <c r="K279" s="25" t="n"/>
+      <c r="L279" s="21">
+        <f>IF(OR(E279&lt;&gt;"",J279&lt;&gt;""),"Занято",IF(AND(F278="Повторный приём (1 час)",A278=A279),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -8989,10 +9273,11 @@
       <c r="F280" s="23" t="n"/>
       <c r="G280" s="24" t="n"/>
       <c r="H280" s="24" t="n"/>
-      <c r="I280" s="21" t="n"/>
-      <c r="J280" s="25" t="n"/>
-      <c r="K280" s="21">
-        <f>IF(OR(E280&lt;&gt;"",I280&lt;&gt;""),"Занято",IF(AND(F279="Повторный приём (1 час)",A279=A280),"Занято","Свободно"))</f>
+      <c r="I280" s="23" t="n"/>
+      <c r="J280" s="21" t="n"/>
+      <c r="K280" s="25" t="n"/>
+      <c r="L280" s="21">
+        <f>IF(OR(E280&lt;&gt;"",J280&lt;&gt;""),"Занято",IF(AND(F279="Повторный приём (1 час)",A279=A280),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9019,10 +9304,11 @@
       <c r="F281" s="23" t="n"/>
       <c r="G281" s="24" t="n"/>
       <c r="H281" s="24" t="n"/>
-      <c r="I281" s="21" t="n"/>
-      <c r="J281" s="25" t="n"/>
-      <c r="K281" s="21">
-        <f>IF(OR(E281&lt;&gt;"",I281&lt;&gt;""),"Занято",IF(AND(F280="Повторный приём (1 час)",A280=A281),"Занято","Свободно"))</f>
+      <c r="I281" s="23" t="n"/>
+      <c r="J281" s="21" t="n"/>
+      <c r="K281" s="25" t="n"/>
+      <c r="L281" s="21">
+        <f>IF(OR(E281&lt;&gt;"",J281&lt;&gt;""),"Занято",IF(AND(F280="Повторный приём (1 час)",A280=A281),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9049,10 +9335,11 @@
       <c r="F282" s="23" t="n"/>
       <c r="G282" s="24" t="n"/>
       <c r="H282" s="24" t="n"/>
-      <c r="I282" s="21" t="n"/>
-      <c r="J282" s="25" t="n"/>
-      <c r="K282" s="21">
-        <f>IF(OR(E282&lt;&gt;"",I282&lt;&gt;""),"Занято",IF(AND(F281="Повторный приём (1 час)",A281=A282),"Занято","Свободно"))</f>
+      <c r="I282" s="23" t="n"/>
+      <c r="J282" s="21" t="n"/>
+      <c r="K282" s="25" t="n"/>
+      <c r="L282" s="21">
+        <f>IF(OR(E282&lt;&gt;"",J282&lt;&gt;""),"Занято",IF(AND(F281="Повторный приём (1 час)",A281=A282),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9079,10 +9366,11 @@
       <c r="F283" s="23" t="n"/>
       <c r="G283" s="24" t="n"/>
       <c r="H283" s="24" t="n"/>
-      <c r="I283" s="21" t="n"/>
-      <c r="J283" s="25" t="n"/>
-      <c r="K283" s="21">
-        <f>IF(OR(E283&lt;&gt;"",I283&lt;&gt;""),"Занято",IF(AND(F282="Повторный приём (1 час)",A282=A283),"Занято","Свободно"))</f>
+      <c r="I283" s="23" t="n"/>
+      <c r="J283" s="21" t="n"/>
+      <c r="K283" s="25" t="n"/>
+      <c r="L283" s="21">
+        <f>IF(OR(E283&lt;&gt;"",J283&lt;&gt;""),"Занято",IF(AND(F282="Повторный приём (1 час)",A282=A283),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9109,10 +9397,11 @@
       <c r="F284" s="23" t="n"/>
       <c r="G284" s="24" t="n"/>
       <c r="H284" s="24" t="n"/>
-      <c r="I284" s="21" t="n"/>
-      <c r="J284" s="25" t="n"/>
-      <c r="K284" s="21">
-        <f>IF(OR(E284&lt;&gt;"",I284&lt;&gt;""),"Занято",IF(AND(F283="Повторный приём (1 час)",A283=A284),"Занято","Свободно"))</f>
+      <c r="I284" s="23" t="n"/>
+      <c r="J284" s="21" t="n"/>
+      <c r="K284" s="25" t="n"/>
+      <c r="L284" s="21">
+        <f>IF(OR(E284&lt;&gt;"",J284&lt;&gt;""),"Занято",IF(AND(F283="Повторный приём (1 час)",A283=A284),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9139,10 +9428,11 @@
       <c r="F285" s="23" t="n"/>
       <c r="G285" s="24" t="n"/>
       <c r="H285" s="24" t="n"/>
-      <c r="I285" s="21" t="n"/>
-      <c r="J285" s="25" t="n"/>
-      <c r="K285" s="21">
-        <f>IF(OR(E285&lt;&gt;"",I285&lt;&gt;""),"Занято",IF(AND(F284="Повторный приём (1 час)",A284=A285),"Занято","Свободно"))</f>
+      <c r="I285" s="23" t="n"/>
+      <c r="J285" s="21" t="n"/>
+      <c r="K285" s="25" t="n"/>
+      <c r="L285" s="21">
+        <f>IF(OR(E285&lt;&gt;"",J285&lt;&gt;""),"Занято",IF(AND(F284="Повторный приём (1 час)",A284=A285),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9169,10 +9459,11 @@
       <c r="F286" s="23" t="n"/>
       <c r="G286" s="24" t="n"/>
       <c r="H286" s="24" t="n"/>
-      <c r="I286" s="21" t="n"/>
-      <c r="J286" s="25" t="n"/>
-      <c r="K286" s="21">
-        <f>IF(OR(E286&lt;&gt;"",I286&lt;&gt;""),"Занято",IF(AND(F285="Повторный приём (1 час)",A285=A286),"Занято","Свободно"))</f>
+      <c r="I286" s="23" t="n"/>
+      <c r="J286" s="21" t="n"/>
+      <c r="K286" s="25" t="n"/>
+      <c r="L286" s="21">
+        <f>IF(OR(E286&lt;&gt;"",J286&lt;&gt;""),"Занято",IF(AND(F285="Повторный приём (1 час)",A285=A286),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9199,10 +9490,11 @@
       <c r="F287" s="23" t="n"/>
       <c r="G287" s="24" t="n"/>
       <c r="H287" s="24" t="n"/>
-      <c r="I287" s="21" t="n"/>
-      <c r="J287" s="25" t="n"/>
-      <c r="K287" s="21">
-        <f>IF(OR(E287&lt;&gt;"",I287&lt;&gt;""),"Занято",IF(AND(F286="Повторный приём (1 час)",A286=A287),"Занято","Свободно"))</f>
+      <c r="I287" s="23" t="n"/>
+      <c r="J287" s="21" t="n"/>
+      <c r="K287" s="25" t="n"/>
+      <c r="L287" s="21">
+        <f>IF(OR(E287&lt;&gt;"",J287&lt;&gt;""),"Занято",IF(AND(F286="Повторный приём (1 час)",A286=A287),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9229,10 +9521,11 @@
       <c r="F288" s="23" t="n"/>
       <c r="G288" s="24" t="n"/>
       <c r="H288" s="24" t="n"/>
-      <c r="I288" s="21" t="n"/>
-      <c r="J288" s="25" t="n"/>
-      <c r="K288" s="21">
-        <f>IF(OR(E288&lt;&gt;"",I288&lt;&gt;""),"Занято",IF(AND(F287="Повторный приём (1 час)",A287=A288),"Занято","Свободно"))</f>
+      <c r="I288" s="23" t="n"/>
+      <c r="J288" s="21" t="n"/>
+      <c r="K288" s="25" t="n"/>
+      <c r="L288" s="21">
+        <f>IF(OR(E288&lt;&gt;"",J288&lt;&gt;""),"Занято",IF(AND(F287="Повторный приём (1 час)",A287=A288),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9259,10 +9552,11 @@
       <c r="F289" s="23" t="n"/>
       <c r="G289" s="24" t="n"/>
       <c r="H289" s="24" t="n"/>
-      <c r="I289" s="21" t="n"/>
-      <c r="J289" s="25" t="n"/>
-      <c r="K289" s="21">
-        <f>IF(OR(E289&lt;&gt;"",I289&lt;&gt;""),"Занято",IF(AND(F288="Повторный приём (1 час)",A288=A289),"Занято","Свободно"))</f>
+      <c r="I289" s="23" t="n"/>
+      <c r="J289" s="21" t="n"/>
+      <c r="K289" s="25" t="n"/>
+      <c r="L289" s="21">
+        <f>IF(OR(E289&lt;&gt;"",J289&lt;&gt;""),"Занято",IF(AND(F288="Повторный приём (1 час)",A288=A289),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9289,10 +9583,11 @@
       <c r="F290" s="23" t="n"/>
       <c r="G290" s="24" t="n"/>
       <c r="H290" s="24" t="n"/>
-      <c r="I290" s="21" t="n"/>
-      <c r="J290" s="25" t="n"/>
-      <c r="K290" s="21">
-        <f>IF(OR(E290&lt;&gt;"",I290&lt;&gt;""),"Занято",IF(AND(F289="Повторный приём (1 час)",A289=A290),"Занято","Свободно"))</f>
+      <c r="I290" s="23" t="n"/>
+      <c r="J290" s="21" t="n"/>
+      <c r="K290" s="25" t="n"/>
+      <c r="L290" s="21">
+        <f>IF(OR(E290&lt;&gt;"",J290&lt;&gt;""),"Занято",IF(AND(F289="Повторный приём (1 час)",A289=A290),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9319,10 +9614,11 @@
       <c r="F291" s="23" t="n"/>
       <c r="G291" s="24" t="n"/>
       <c r="H291" s="24" t="n"/>
-      <c r="I291" s="21" t="n"/>
-      <c r="J291" s="25" t="n"/>
-      <c r="K291" s="21">
-        <f>IF(OR(E291&lt;&gt;"",I291&lt;&gt;""),"Занято",IF(AND(F290="Повторный приём (1 час)",A290=A291),"Занято","Свободно"))</f>
+      <c r="I291" s="23" t="n"/>
+      <c r="J291" s="21" t="n"/>
+      <c r="K291" s="25" t="n"/>
+      <c r="L291" s="21">
+        <f>IF(OR(E291&lt;&gt;"",J291&lt;&gt;""),"Занято",IF(AND(F290="Повторный приём (1 час)",A290=A291),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9349,10 +9645,11 @@
       <c r="F292" s="23" t="n"/>
       <c r="G292" s="24" t="n"/>
       <c r="H292" s="24" t="n"/>
-      <c r="I292" s="21" t="n"/>
-      <c r="J292" s="25" t="n"/>
-      <c r="K292" s="21">
-        <f>IF(OR(E292&lt;&gt;"",I292&lt;&gt;""),"Занято",IF(AND(F291="Повторный приём (1 час)",A291=A292),"Занято","Свободно"))</f>
+      <c r="I292" s="23" t="n"/>
+      <c r="J292" s="21" t="n"/>
+      <c r="K292" s="25" t="n"/>
+      <c r="L292" s="21">
+        <f>IF(OR(E292&lt;&gt;"",J292&lt;&gt;""),"Занято",IF(AND(F291="Повторный приём (1 час)",A291=A292),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9379,10 +9676,11 @@
       <c r="F293" s="23" t="n"/>
       <c r="G293" s="24" t="n"/>
       <c r="H293" s="24" t="n"/>
-      <c r="I293" s="21" t="n"/>
-      <c r="J293" s="25" t="n"/>
-      <c r="K293" s="21">
-        <f>IF(OR(E293&lt;&gt;"",I293&lt;&gt;""),"Занято",IF(AND(F292="Повторный приём (1 час)",A292=A293),"Занято","Свободно"))</f>
+      <c r="I293" s="23" t="n"/>
+      <c r="J293" s="21" t="n"/>
+      <c r="K293" s="25" t="n"/>
+      <c r="L293" s="21">
+        <f>IF(OR(E293&lt;&gt;"",J293&lt;&gt;""),"Занято",IF(AND(F292="Повторный приём (1 час)",A292=A293),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9409,10 +9707,11 @@
       <c r="F294" s="23" t="n"/>
       <c r="G294" s="24" t="n"/>
       <c r="H294" s="24" t="n"/>
-      <c r="I294" s="21" t="n"/>
-      <c r="J294" s="25" t="n"/>
-      <c r="K294" s="21">
-        <f>IF(OR(E294&lt;&gt;"",I294&lt;&gt;""),"Занято",IF(AND(F293="Повторный приём (1 час)",A293=A294),"Занято","Свободно"))</f>
+      <c r="I294" s="23" t="n"/>
+      <c r="J294" s="21" t="n"/>
+      <c r="K294" s="25" t="n"/>
+      <c r="L294" s="21">
+        <f>IF(OR(E294&lt;&gt;"",J294&lt;&gt;""),"Занято",IF(AND(F293="Повторный приём (1 час)",A293=A294),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9439,10 +9738,11 @@
       <c r="F295" s="23" t="n"/>
       <c r="G295" s="24" t="n"/>
       <c r="H295" s="24" t="n"/>
-      <c r="I295" s="21" t="n"/>
-      <c r="J295" s="25" t="n"/>
-      <c r="K295" s="21">
-        <f>IF(OR(E295&lt;&gt;"",I295&lt;&gt;""),"Занято",IF(AND(F294="Повторный приём (1 час)",A294=A295),"Занято","Свободно"))</f>
+      <c r="I295" s="23" t="n"/>
+      <c r="J295" s="21" t="n"/>
+      <c r="K295" s="25" t="n"/>
+      <c r="L295" s="21">
+        <f>IF(OR(E295&lt;&gt;"",J295&lt;&gt;""),"Занято",IF(AND(F294="Повторный приём (1 час)",A294=A295),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9469,10 +9769,11 @@
       <c r="F296" s="5" t="n"/>
       <c r="G296" s="6" t="n"/>
       <c r="H296" s="6" t="n"/>
-      <c r="I296" s="3" t="n"/>
-      <c r="J296" s="7" t="n"/>
-      <c r="K296" s="3">
-        <f>IF(OR(E296&lt;&gt;"",I296&lt;&gt;""),"Занято",IF(AND(F295="Повторный приём (1 час)",A295=A296),"Занято","Свободно"))</f>
+      <c r="I296" s="5" t="n"/>
+      <c r="J296" s="3" t="n"/>
+      <c r="K296" s="7" t="n"/>
+      <c r="L296" s="3">
+        <f>IF(OR(E296&lt;&gt;"",J296&lt;&gt;""),"Занято",IF(AND(F295="Повторный приём (1 час)",A295=A296),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9499,10 +9800,11 @@
       <c r="F297" s="11" t="n"/>
       <c r="G297" s="12" t="n"/>
       <c r="H297" s="12" t="n"/>
-      <c r="I297" s="9" t="n"/>
-      <c r="J297" s="13" t="n"/>
-      <c r="K297" s="9">
-        <f>IF(OR(E297&lt;&gt;"",I297&lt;&gt;""),"Занято",IF(AND(F296="Повторный приём (1 час)",A296=A297),"Занято","Свободно"))</f>
+      <c r="I297" s="11" t="n"/>
+      <c r="J297" s="9" t="n"/>
+      <c r="K297" s="13" t="n"/>
+      <c r="L297" s="9">
+        <f>IF(OR(E297&lt;&gt;"",J297&lt;&gt;""),"Занято",IF(AND(F296="Повторный приём (1 час)",A296=A297),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9529,10 +9831,11 @@
       <c r="F298" s="11" t="n"/>
       <c r="G298" s="12" t="n"/>
       <c r="H298" s="12" t="n"/>
-      <c r="I298" s="9" t="n"/>
-      <c r="J298" s="13" t="n"/>
-      <c r="K298" s="9">
-        <f>IF(OR(E298&lt;&gt;"",I298&lt;&gt;""),"Занято",IF(AND(F297="Повторный приём (1 час)",A297=A298),"Занято","Свободно"))</f>
+      <c r="I298" s="11" t="n"/>
+      <c r="J298" s="9" t="n"/>
+      <c r="K298" s="13" t="n"/>
+      <c r="L298" s="9">
+        <f>IF(OR(E298&lt;&gt;"",J298&lt;&gt;""),"Занято",IF(AND(F297="Повторный приём (1 час)",A297=A298),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9559,10 +9862,11 @@
       <c r="F299" s="11" t="n"/>
       <c r="G299" s="12" t="n"/>
       <c r="H299" s="12" t="n"/>
-      <c r="I299" s="9" t="n"/>
-      <c r="J299" s="13" t="n"/>
-      <c r="K299" s="9">
-        <f>IF(OR(E299&lt;&gt;"",I299&lt;&gt;""),"Занято",IF(AND(F298="Повторный приём (1 час)",A298=A299),"Занято","Свободно"))</f>
+      <c r="I299" s="11" t="n"/>
+      <c r="J299" s="9" t="n"/>
+      <c r="K299" s="13" t="n"/>
+      <c r="L299" s="9">
+        <f>IF(OR(E299&lt;&gt;"",J299&lt;&gt;""),"Занято",IF(AND(F298="Повторный приём (1 час)",A298=A299),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9589,10 +9893,11 @@
       <c r="F300" s="11" t="n"/>
       <c r="G300" s="12" t="n"/>
       <c r="H300" s="12" t="n"/>
-      <c r="I300" s="9" t="n"/>
-      <c r="J300" s="13" t="n"/>
-      <c r="K300" s="9">
-        <f>IF(OR(E300&lt;&gt;"",I300&lt;&gt;""),"Занято",IF(AND(F299="Повторный приём (1 час)",A299=A300),"Занято","Свободно"))</f>
+      <c r="I300" s="11" t="n"/>
+      <c r="J300" s="9" t="n"/>
+      <c r="K300" s="13" t="n"/>
+      <c r="L300" s="9">
+        <f>IF(OR(E300&lt;&gt;"",J300&lt;&gt;""),"Занято",IF(AND(F299="Повторный приём (1 час)",A299=A300),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9619,10 +9924,11 @@
       <c r="F301" s="11" t="n"/>
       <c r="G301" s="12" t="n"/>
       <c r="H301" s="12" t="n"/>
-      <c r="I301" s="9" t="n"/>
-      <c r="J301" s="13" t="n"/>
-      <c r="K301" s="9">
-        <f>IF(OR(E301&lt;&gt;"",I301&lt;&gt;""),"Занято",IF(AND(F300="Повторный приём (1 час)",A300=A301),"Занято","Свободно"))</f>
+      <c r="I301" s="11" t="n"/>
+      <c r="J301" s="9" t="n"/>
+      <c r="K301" s="13" t="n"/>
+      <c r="L301" s="9">
+        <f>IF(OR(E301&lt;&gt;"",J301&lt;&gt;""),"Занято",IF(AND(F300="Повторный приём (1 час)",A300=A301),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9649,10 +9955,11 @@
       <c r="F302" s="11" t="n"/>
       <c r="G302" s="12" t="n"/>
       <c r="H302" s="12" t="n"/>
-      <c r="I302" s="9" t="n"/>
-      <c r="J302" s="13" t="n"/>
-      <c r="K302" s="9">
-        <f>IF(OR(E302&lt;&gt;"",I302&lt;&gt;""),"Занято",IF(AND(F301="Повторный приём (1 час)",A301=A302),"Занято","Свободно"))</f>
+      <c r="I302" s="11" t="n"/>
+      <c r="J302" s="9" t="n"/>
+      <c r="K302" s="13" t="n"/>
+      <c r="L302" s="9">
+        <f>IF(OR(E302&lt;&gt;"",J302&lt;&gt;""),"Занято",IF(AND(F301="Повторный приём (1 час)",A301=A302),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9679,10 +9986,11 @@
       <c r="F303" s="11" t="n"/>
       <c r="G303" s="12" t="n"/>
       <c r="H303" s="12" t="n"/>
-      <c r="I303" s="9" t="n"/>
-      <c r="J303" s="13" t="n"/>
-      <c r="K303" s="9">
-        <f>IF(OR(E303&lt;&gt;"",I303&lt;&gt;""),"Занято",IF(AND(F302="Повторный приём (1 час)",A302=A303),"Занято","Свободно"))</f>
+      <c r="I303" s="11" t="n"/>
+      <c r="J303" s="9" t="n"/>
+      <c r="K303" s="13" t="n"/>
+      <c r="L303" s="9">
+        <f>IF(OR(E303&lt;&gt;"",J303&lt;&gt;""),"Занято",IF(AND(F302="Повторный приём (1 час)",A302=A303),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9709,10 +10017,11 @@
       <c r="F304" s="11" t="n"/>
       <c r="G304" s="12" t="n"/>
       <c r="H304" s="12" t="n"/>
-      <c r="I304" s="9" t="n"/>
-      <c r="J304" s="13" t="n"/>
-      <c r="K304" s="9">
-        <f>IF(OR(E304&lt;&gt;"",I304&lt;&gt;""),"Занято",IF(AND(F303="Повторный приём (1 час)",A303=A304),"Занято","Свободно"))</f>
+      <c r="I304" s="11" t="n"/>
+      <c r="J304" s="9" t="n"/>
+      <c r="K304" s="13" t="n"/>
+      <c r="L304" s="9">
+        <f>IF(OR(E304&lt;&gt;"",J304&lt;&gt;""),"Занято",IF(AND(F303="Повторный приём (1 час)",A303=A304),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9739,10 +10048,11 @@
       <c r="F305" s="11" t="n"/>
       <c r="G305" s="12" t="n"/>
       <c r="H305" s="12" t="n"/>
-      <c r="I305" s="9" t="n"/>
-      <c r="J305" s="13" t="n"/>
-      <c r="K305" s="9">
-        <f>IF(OR(E305&lt;&gt;"",I305&lt;&gt;""),"Занято",IF(AND(F304="Повторный приём (1 час)",A304=A305),"Занято","Свободно"))</f>
+      <c r="I305" s="11" t="n"/>
+      <c r="J305" s="9" t="n"/>
+      <c r="K305" s="13" t="n"/>
+      <c r="L305" s="9">
+        <f>IF(OR(E305&lt;&gt;"",J305&lt;&gt;""),"Занято",IF(AND(F304="Повторный приём (1 час)",A304=A305),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9769,10 +10079,11 @@
       <c r="F306" s="11" t="n"/>
       <c r="G306" s="12" t="n"/>
       <c r="H306" s="12" t="n"/>
-      <c r="I306" s="9" t="n"/>
-      <c r="J306" s="13" t="n"/>
-      <c r="K306" s="9">
-        <f>IF(OR(E306&lt;&gt;"",I306&lt;&gt;""),"Занято",IF(AND(F305="Повторный приём (1 час)",A305=A306),"Занято","Свободно"))</f>
+      <c r="I306" s="11" t="n"/>
+      <c r="J306" s="9" t="n"/>
+      <c r="K306" s="13" t="n"/>
+      <c r="L306" s="9">
+        <f>IF(OR(E306&lt;&gt;"",J306&lt;&gt;""),"Занято",IF(AND(F305="Повторный приём (1 час)",A305=A306),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9799,10 +10110,11 @@
       <c r="F307" s="11" t="n"/>
       <c r="G307" s="12" t="n"/>
       <c r="H307" s="12" t="n"/>
-      <c r="I307" s="9" t="n"/>
-      <c r="J307" s="13" t="n"/>
-      <c r="K307" s="9">
-        <f>IF(OR(E307&lt;&gt;"",I307&lt;&gt;""),"Занято",IF(AND(F306="Повторный приём (1 час)",A306=A307),"Занято","Свободно"))</f>
+      <c r="I307" s="11" t="n"/>
+      <c r="J307" s="9" t="n"/>
+      <c r="K307" s="13" t="n"/>
+      <c r="L307" s="9">
+        <f>IF(OR(E307&lt;&gt;"",J307&lt;&gt;""),"Занято",IF(AND(F306="Повторный приём (1 час)",A306=A307),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9829,10 +10141,11 @@
       <c r="F308" s="11" t="n"/>
       <c r="G308" s="12" t="n"/>
       <c r="H308" s="12" t="n"/>
-      <c r="I308" s="9" t="n"/>
-      <c r="J308" s="13" t="n"/>
-      <c r="K308" s="9">
-        <f>IF(OR(E308&lt;&gt;"",I308&lt;&gt;""),"Занято",IF(AND(F307="Повторный приём (1 час)",A307=A308),"Занято","Свободно"))</f>
+      <c r="I308" s="11" t="n"/>
+      <c r="J308" s="9" t="n"/>
+      <c r="K308" s="13" t="n"/>
+      <c r="L308" s="9">
+        <f>IF(OR(E308&lt;&gt;"",J308&lt;&gt;""),"Занято",IF(AND(F307="Повторный приём (1 час)",A307=A308),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9859,10 +10172,11 @@
       <c r="F309" s="11" t="n"/>
       <c r="G309" s="12" t="n"/>
       <c r="H309" s="12" t="n"/>
-      <c r="I309" s="9" t="n"/>
-      <c r="J309" s="13" t="n"/>
-      <c r="K309" s="9">
-        <f>IF(OR(E309&lt;&gt;"",I309&lt;&gt;""),"Занято",IF(AND(F308="Повторный приём (1 час)",A308=A309),"Занято","Свободно"))</f>
+      <c r="I309" s="11" t="n"/>
+      <c r="J309" s="9" t="n"/>
+      <c r="K309" s="13" t="n"/>
+      <c r="L309" s="9">
+        <f>IF(OR(E309&lt;&gt;"",J309&lt;&gt;""),"Занято",IF(AND(F308="Повторный приём (1 час)",A308=A309),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9889,10 +10203,11 @@
       <c r="F310" s="11" t="n"/>
       <c r="G310" s="12" t="n"/>
       <c r="H310" s="12" t="n"/>
-      <c r="I310" s="9" t="n"/>
-      <c r="J310" s="13" t="n"/>
-      <c r="K310" s="9">
-        <f>IF(OR(E310&lt;&gt;"",I310&lt;&gt;""),"Занято",IF(AND(F309="Повторный приём (1 час)",A309=A310),"Занято","Свободно"))</f>
+      <c r="I310" s="11" t="n"/>
+      <c r="J310" s="9" t="n"/>
+      <c r="K310" s="13" t="n"/>
+      <c r="L310" s="9">
+        <f>IF(OR(E310&lt;&gt;"",J310&lt;&gt;""),"Занято",IF(AND(F309="Повторный приём (1 час)",A309=A310),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9919,10 +10234,11 @@
       <c r="F311" s="11" t="n"/>
       <c r="G311" s="12" t="n"/>
       <c r="H311" s="12" t="n"/>
-      <c r="I311" s="9" t="n"/>
-      <c r="J311" s="13" t="n"/>
-      <c r="K311" s="9">
-        <f>IF(OR(E311&lt;&gt;"",I311&lt;&gt;""),"Занято",IF(AND(F310="Повторный приём (1 час)",A310=A311),"Занято","Свободно"))</f>
+      <c r="I311" s="11" t="n"/>
+      <c r="J311" s="9" t="n"/>
+      <c r="K311" s="13" t="n"/>
+      <c r="L311" s="9">
+        <f>IF(OR(E311&lt;&gt;"",J311&lt;&gt;""),"Занято",IF(AND(F310="Повторный приём (1 час)",A310=A311),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9949,10 +10265,11 @@
       <c r="F312" s="11" t="n"/>
       <c r="G312" s="12" t="n"/>
       <c r="H312" s="12" t="n"/>
-      <c r="I312" s="9" t="n"/>
-      <c r="J312" s="13" t="n"/>
-      <c r="K312" s="9">
-        <f>IF(OR(E312&lt;&gt;"",I312&lt;&gt;""),"Занято",IF(AND(F311="Повторный приём (1 час)",A311=A312),"Занято","Свободно"))</f>
+      <c r="I312" s="11" t="n"/>
+      <c r="J312" s="9" t="n"/>
+      <c r="K312" s="13" t="n"/>
+      <c r="L312" s="9">
+        <f>IF(OR(E312&lt;&gt;"",J312&lt;&gt;""),"Занято",IF(AND(F311="Повторный приём (1 час)",A311=A312),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -9979,10 +10296,11 @@
       <c r="F313" s="11" t="n"/>
       <c r="G313" s="12" t="n"/>
       <c r="H313" s="12" t="n"/>
-      <c r="I313" s="9" t="n"/>
-      <c r="J313" s="13" t="n"/>
-      <c r="K313" s="9">
-        <f>IF(OR(E313&lt;&gt;"",I313&lt;&gt;""),"Занято",IF(AND(F312="Повторный приём (1 час)",A312=A313),"Занято","Свободно"))</f>
+      <c r="I313" s="11" t="n"/>
+      <c r="J313" s="9" t="n"/>
+      <c r="K313" s="13" t="n"/>
+      <c r="L313" s="9">
+        <f>IF(OR(E313&lt;&gt;"",J313&lt;&gt;""),"Занято",IF(AND(F312="Повторный приём (1 час)",A312=A313),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10009,10 +10327,11 @@
       <c r="F314" s="17" t="n"/>
       <c r="G314" s="18" t="n"/>
       <c r="H314" s="18" t="n"/>
-      <c r="I314" s="15" t="n"/>
-      <c r="J314" s="19" t="n"/>
-      <c r="K314" s="15">
-        <f>IF(OR(E314&lt;&gt;"",I314&lt;&gt;""),"Занято",IF(AND(F313="Повторный приём (1 час)",A313=A314),"Занято","Свободно"))</f>
+      <c r="I314" s="17" t="n"/>
+      <c r="J314" s="15" t="n"/>
+      <c r="K314" s="19" t="n"/>
+      <c r="L314" s="15">
+        <f>IF(OR(E314&lt;&gt;"",J314&lt;&gt;""),"Занято",IF(AND(F313="Повторный приём (1 час)",A313=A314),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10039,10 +10358,11 @@
       <c r="F315" s="23" t="n"/>
       <c r="G315" s="24" t="n"/>
       <c r="H315" s="24" t="n"/>
-      <c r="I315" s="21" t="n"/>
-      <c r="J315" s="25" t="n"/>
-      <c r="K315" s="21">
-        <f>IF(OR(E315&lt;&gt;"",I315&lt;&gt;""),"Занято",IF(AND(F314="Повторный приём (1 час)",A314=A315),"Занято","Свободно"))</f>
+      <c r="I315" s="23" t="n"/>
+      <c r="J315" s="21" t="n"/>
+      <c r="K315" s="25" t="n"/>
+      <c r="L315" s="21">
+        <f>IF(OR(E315&lt;&gt;"",J315&lt;&gt;""),"Занято",IF(AND(F314="Повторный приём (1 час)",A314=A315),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10069,10 +10389,11 @@
       <c r="F316" s="23" t="n"/>
       <c r="G316" s="24" t="n"/>
       <c r="H316" s="24" t="n"/>
-      <c r="I316" s="21" t="n"/>
-      <c r="J316" s="25" t="n"/>
-      <c r="K316" s="21">
-        <f>IF(OR(E316&lt;&gt;"",I316&lt;&gt;""),"Занято",IF(AND(F315="Повторный приём (1 час)",A315=A316),"Занято","Свободно"))</f>
+      <c r="I316" s="23" t="n"/>
+      <c r="J316" s="21" t="n"/>
+      <c r="K316" s="25" t="n"/>
+      <c r="L316" s="21">
+        <f>IF(OR(E316&lt;&gt;"",J316&lt;&gt;""),"Занято",IF(AND(F315="Повторный приём (1 час)",A315=A316),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10099,10 +10420,11 @@
       <c r="F317" s="23" t="n"/>
       <c r="G317" s="24" t="n"/>
       <c r="H317" s="24" t="n"/>
-      <c r="I317" s="21" t="n"/>
-      <c r="J317" s="25" t="n"/>
-      <c r="K317" s="21">
-        <f>IF(OR(E317&lt;&gt;"",I317&lt;&gt;""),"Занято",IF(AND(F316="Повторный приём (1 час)",A316=A317),"Занято","Свободно"))</f>
+      <c r="I317" s="23" t="n"/>
+      <c r="J317" s="21" t="n"/>
+      <c r="K317" s="25" t="n"/>
+      <c r="L317" s="21">
+        <f>IF(OR(E317&lt;&gt;"",J317&lt;&gt;""),"Занято",IF(AND(F316="Повторный приём (1 час)",A316=A317),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10129,10 +10451,11 @@
       <c r="F318" s="23" t="n"/>
       <c r="G318" s="24" t="n"/>
       <c r="H318" s="24" t="n"/>
-      <c r="I318" s="21" t="n"/>
-      <c r="J318" s="25" t="n"/>
-      <c r="K318" s="21">
-        <f>IF(OR(E318&lt;&gt;"",I318&lt;&gt;""),"Занято",IF(AND(F317="Повторный приём (1 час)",A317=A318),"Занято","Свободно"))</f>
+      <c r="I318" s="23" t="n"/>
+      <c r="J318" s="21" t="n"/>
+      <c r="K318" s="25" t="n"/>
+      <c r="L318" s="21">
+        <f>IF(OR(E318&lt;&gt;"",J318&lt;&gt;""),"Занято",IF(AND(F317="Повторный приём (1 час)",A317=A318),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10159,10 +10482,11 @@
       <c r="F319" s="23" t="n"/>
       <c r="G319" s="24" t="n"/>
       <c r="H319" s="24" t="n"/>
-      <c r="I319" s="21" t="n"/>
-      <c r="J319" s="25" t="n"/>
-      <c r="K319" s="21">
-        <f>IF(OR(E319&lt;&gt;"",I319&lt;&gt;""),"Занято",IF(AND(F318="Повторный приём (1 час)",A318=A319),"Занято","Свободно"))</f>
+      <c r="I319" s="23" t="n"/>
+      <c r="J319" s="21" t="n"/>
+      <c r="K319" s="25" t="n"/>
+      <c r="L319" s="21">
+        <f>IF(OR(E319&lt;&gt;"",J319&lt;&gt;""),"Занято",IF(AND(F318="Повторный приём (1 час)",A318=A319),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10189,10 +10513,11 @@
       <c r="F320" s="23" t="n"/>
       <c r="G320" s="24" t="n"/>
       <c r="H320" s="24" t="n"/>
-      <c r="I320" s="21" t="n"/>
-      <c r="J320" s="25" t="n"/>
-      <c r="K320" s="21">
-        <f>IF(OR(E320&lt;&gt;"",I320&lt;&gt;""),"Занято",IF(AND(F319="Повторный приём (1 час)",A319=A320),"Занято","Свободно"))</f>
+      <c r="I320" s="23" t="n"/>
+      <c r="J320" s="21" t="n"/>
+      <c r="K320" s="25" t="n"/>
+      <c r="L320" s="21">
+        <f>IF(OR(E320&lt;&gt;"",J320&lt;&gt;""),"Занято",IF(AND(F319="Повторный приём (1 час)",A319=A320),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10219,10 +10544,11 @@
       <c r="F321" s="23" t="n"/>
       <c r="G321" s="24" t="n"/>
       <c r="H321" s="24" t="n"/>
-      <c r="I321" s="21" t="n"/>
-      <c r="J321" s="25" t="n"/>
-      <c r="K321" s="21">
-        <f>IF(OR(E321&lt;&gt;"",I321&lt;&gt;""),"Занято",IF(AND(F320="Повторный приём (1 час)",A320=A321),"Занято","Свободно"))</f>
+      <c r="I321" s="23" t="n"/>
+      <c r="J321" s="21" t="n"/>
+      <c r="K321" s="25" t="n"/>
+      <c r="L321" s="21">
+        <f>IF(OR(E321&lt;&gt;"",J321&lt;&gt;""),"Занято",IF(AND(F320="Повторный приём (1 час)",A320=A321),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10249,10 +10575,11 @@
       <c r="F322" s="23" t="n"/>
       <c r="G322" s="24" t="n"/>
       <c r="H322" s="24" t="n"/>
-      <c r="I322" s="21" t="n"/>
-      <c r="J322" s="25" t="n"/>
-      <c r="K322" s="21">
-        <f>IF(OR(E322&lt;&gt;"",I322&lt;&gt;""),"Занято",IF(AND(F321="Повторный приём (1 час)",A321=A322),"Занято","Свободно"))</f>
+      <c r="I322" s="23" t="n"/>
+      <c r="J322" s="21" t="n"/>
+      <c r="K322" s="25" t="n"/>
+      <c r="L322" s="21">
+        <f>IF(OR(E322&lt;&gt;"",J322&lt;&gt;""),"Занято",IF(AND(F321="Повторный приём (1 час)",A321=A322),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10279,10 +10606,11 @@
       <c r="F323" s="23" t="n"/>
       <c r="G323" s="24" t="n"/>
       <c r="H323" s="24" t="n"/>
-      <c r="I323" s="21" t="n"/>
-      <c r="J323" s="25" t="n"/>
-      <c r="K323" s="21">
-        <f>IF(OR(E323&lt;&gt;"",I323&lt;&gt;""),"Занято",IF(AND(F322="Повторный приём (1 час)",A322=A323),"Занято","Свободно"))</f>
+      <c r="I323" s="23" t="n"/>
+      <c r="J323" s="21" t="n"/>
+      <c r="K323" s="25" t="n"/>
+      <c r="L323" s="21">
+        <f>IF(OR(E323&lt;&gt;"",J323&lt;&gt;""),"Занято",IF(AND(F322="Повторный приём (1 час)",A322=A323),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10309,10 +10637,11 @@
       <c r="F324" s="23" t="n"/>
       <c r="G324" s="24" t="n"/>
       <c r="H324" s="24" t="n"/>
-      <c r="I324" s="21" t="n"/>
-      <c r="J324" s="25" t="n"/>
-      <c r="K324" s="21">
-        <f>IF(OR(E324&lt;&gt;"",I324&lt;&gt;""),"Занято",IF(AND(F323="Повторный приём (1 час)",A323=A324),"Занято","Свободно"))</f>
+      <c r="I324" s="23" t="n"/>
+      <c r="J324" s="21" t="n"/>
+      <c r="K324" s="25" t="n"/>
+      <c r="L324" s="21">
+        <f>IF(OR(E324&lt;&gt;"",J324&lt;&gt;""),"Занято",IF(AND(F323="Повторный приём (1 час)",A323=A324),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10339,10 +10668,11 @@
       <c r="F325" s="23" t="n"/>
       <c r="G325" s="24" t="n"/>
       <c r="H325" s="24" t="n"/>
-      <c r="I325" s="21" t="n"/>
-      <c r="J325" s="25" t="n"/>
-      <c r="K325" s="21">
-        <f>IF(OR(E325&lt;&gt;"",I325&lt;&gt;""),"Занято",IF(AND(F324="Повторный приём (1 час)",A324=A325),"Занято","Свободно"))</f>
+      <c r="I325" s="23" t="n"/>
+      <c r="J325" s="21" t="n"/>
+      <c r="K325" s="25" t="n"/>
+      <c r="L325" s="21">
+        <f>IF(OR(E325&lt;&gt;"",J325&lt;&gt;""),"Занято",IF(AND(F324="Повторный приём (1 час)",A324=A325),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10369,10 +10699,11 @@
       <c r="F326" s="23" t="n"/>
       <c r="G326" s="24" t="n"/>
       <c r="H326" s="24" t="n"/>
-      <c r="I326" s="21" t="n"/>
-      <c r="J326" s="25" t="n"/>
-      <c r="K326" s="21">
-        <f>IF(OR(E326&lt;&gt;"",I326&lt;&gt;""),"Занято",IF(AND(F325="Повторный приём (1 час)",A325=A326),"Занято","Свободно"))</f>
+      <c r="I326" s="23" t="n"/>
+      <c r="J326" s="21" t="n"/>
+      <c r="K326" s="25" t="n"/>
+      <c r="L326" s="21">
+        <f>IF(OR(E326&lt;&gt;"",J326&lt;&gt;""),"Занято",IF(AND(F325="Повторный приём (1 час)",A325=A326),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10399,10 +10730,11 @@
       <c r="F327" s="23" t="n"/>
       <c r="G327" s="24" t="n"/>
       <c r="H327" s="24" t="n"/>
-      <c r="I327" s="21" t="n"/>
-      <c r="J327" s="25" t="n"/>
-      <c r="K327" s="21">
-        <f>IF(OR(E327&lt;&gt;"",I327&lt;&gt;""),"Занято",IF(AND(F326="Повторный приём (1 час)",A326=A327),"Занято","Свободно"))</f>
+      <c r="I327" s="23" t="n"/>
+      <c r="J327" s="21" t="n"/>
+      <c r="K327" s="25" t="n"/>
+      <c r="L327" s="21">
+        <f>IF(OR(E327&lt;&gt;"",J327&lt;&gt;""),"Занято",IF(AND(F326="Повторный приём (1 час)",A326=A327),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10429,10 +10761,11 @@
       <c r="F328" s="23" t="n"/>
       <c r="G328" s="24" t="n"/>
       <c r="H328" s="24" t="n"/>
-      <c r="I328" s="21" t="n"/>
-      <c r="J328" s="25" t="n"/>
-      <c r="K328" s="21">
-        <f>IF(OR(E328&lt;&gt;"",I328&lt;&gt;""),"Занято",IF(AND(F327="Повторный приём (1 час)",A327=A328),"Занято","Свободно"))</f>
+      <c r="I328" s="23" t="n"/>
+      <c r="J328" s="21" t="n"/>
+      <c r="K328" s="25" t="n"/>
+      <c r="L328" s="21">
+        <f>IF(OR(E328&lt;&gt;"",J328&lt;&gt;""),"Занято",IF(AND(F327="Повторный приём (1 час)",A327=A328),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10459,10 +10792,11 @@
       <c r="F329" s="23" t="n"/>
       <c r="G329" s="24" t="n"/>
       <c r="H329" s="24" t="n"/>
-      <c r="I329" s="21" t="n"/>
-      <c r="J329" s="25" t="n"/>
-      <c r="K329" s="21">
-        <f>IF(OR(E329&lt;&gt;"",I329&lt;&gt;""),"Занято",IF(AND(F328="Повторный приём (1 час)",A328=A329),"Занято","Свободно"))</f>
+      <c r="I329" s="23" t="n"/>
+      <c r="J329" s="21" t="n"/>
+      <c r="K329" s="25" t="n"/>
+      <c r="L329" s="21">
+        <f>IF(OR(E329&lt;&gt;"",J329&lt;&gt;""),"Занято",IF(AND(F328="Повторный приём (1 час)",A328=A329),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10489,10 +10823,11 @@
       <c r="F330" s="23" t="n"/>
       <c r="G330" s="24" t="n"/>
       <c r="H330" s="24" t="n"/>
-      <c r="I330" s="21" t="n"/>
-      <c r="J330" s="25" t="n"/>
-      <c r="K330" s="21">
-        <f>IF(OR(E330&lt;&gt;"",I330&lt;&gt;""),"Занято",IF(AND(F329="Повторный приём (1 час)",A329=A330),"Занято","Свободно"))</f>
+      <c r="I330" s="23" t="n"/>
+      <c r="J330" s="21" t="n"/>
+      <c r="K330" s="25" t="n"/>
+      <c r="L330" s="21">
+        <f>IF(OR(E330&lt;&gt;"",J330&lt;&gt;""),"Занято",IF(AND(F329="Повторный приём (1 час)",A329=A330),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10519,10 +10854,11 @@
       <c r="F331" s="23" t="n"/>
       <c r="G331" s="24" t="n"/>
       <c r="H331" s="24" t="n"/>
-      <c r="I331" s="21" t="n"/>
-      <c r="J331" s="25" t="n"/>
-      <c r="K331" s="21">
-        <f>IF(OR(E331&lt;&gt;"",I331&lt;&gt;""),"Занято",IF(AND(F330="Повторный приём (1 час)",A330=A331),"Занято","Свободно"))</f>
+      <c r="I331" s="23" t="n"/>
+      <c r="J331" s="21" t="n"/>
+      <c r="K331" s="25" t="n"/>
+      <c r="L331" s="21">
+        <f>IF(OR(E331&lt;&gt;"",J331&lt;&gt;""),"Занято",IF(AND(F330="Повторный приём (1 час)",A330=A331),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10549,10 +10885,11 @@
       <c r="F332" s="5" t="n"/>
       <c r="G332" s="6" t="n"/>
       <c r="H332" s="6" t="n"/>
-      <c r="I332" s="3" t="n"/>
-      <c r="J332" s="7" t="n"/>
-      <c r="K332" s="3">
-        <f>IF(OR(E332&lt;&gt;"",I332&lt;&gt;""),"Занято",IF(AND(F331="Повторный приём (1 час)",A331=A332),"Занято","Свободно"))</f>
+      <c r="I332" s="5" t="n"/>
+      <c r="J332" s="3" t="n"/>
+      <c r="K332" s="7" t="n"/>
+      <c r="L332" s="3">
+        <f>IF(OR(E332&lt;&gt;"",J332&lt;&gt;""),"Занято",IF(AND(F331="Повторный приём (1 час)",A331=A332),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10579,10 +10916,11 @@
       <c r="F333" s="11" t="n"/>
       <c r="G333" s="12" t="n"/>
       <c r="H333" s="12" t="n"/>
-      <c r="I333" s="9" t="n"/>
-      <c r="J333" s="13" t="n"/>
-      <c r="K333" s="9">
-        <f>IF(OR(E333&lt;&gt;"",I333&lt;&gt;""),"Занято",IF(AND(F332="Повторный приём (1 час)",A332=A333),"Занято","Свободно"))</f>
+      <c r="I333" s="11" t="n"/>
+      <c r="J333" s="9" t="n"/>
+      <c r="K333" s="13" t="n"/>
+      <c r="L333" s="9">
+        <f>IF(OR(E333&lt;&gt;"",J333&lt;&gt;""),"Занято",IF(AND(F332="Повторный приём (1 час)",A332=A333),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10609,10 +10947,11 @@
       <c r="F334" s="11" t="n"/>
       <c r="G334" s="12" t="n"/>
       <c r="H334" s="12" t="n"/>
-      <c r="I334" s="9" t="n"/>
-      <c r="J334" s="13" t="n"/>
-      <c r="K334" s="9">
-        <f>IF(OR(E334&lt;&gt;"",I334&lt;&gt;""),"Занято",IF(AND(F333="Повторный приём (1 час)",A333=A334),"Занято","Свободно"))</f>
+      <c r="I334" s="11" t="n"/>
+      <c r="J334" s="9" t="n"/>
+      <c r="K334" s="13" t="n"/>
+      <c r="L334" s="9">
+        <f>IF(OR(E334&lt;&gt;"",J334&lt;&gt;""),"Занято",IF(AND(F333="Повторный приём (1 час)",A333=A334),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10639,10 +10978,11 @@
       <c r="F335" s="11" t="n"/>
       <c r="G335" s="12" t="n"/>
       <c r="H335" s="12" t="n"/>
-      <c r="I335" s="9" t="n"/>
-      <c r="J335" s="13" t="n"/>
-      <c r="K335" s="9">
-        <f>IF(OR(E335&lt;&gt;"",I335&lt;&gt;""),"Занято",IF(AND(F334="Повторный приём (1 час)",A334=A335),"Занято","Свободно"))</f>
+      <c r="I335" s="11" t="n"/>
+      <c r="J335" s="9" t="n"/>
+      <c r="K335" s="13" t="n"/>
+      <c r="L335" s="9">
+        <f>IF(OR(E335&lt;&gt;"",J335&lt;&gt;""),"Занято",IF(AND(F334="Повторный приём (1 час)",A334=A335),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10669,10 +11009,11 @@
       <c r="F336" s="11" t="n"/>
       <c r="G336" s="12" t="n"/>
       <c r="H336" s="12" t="n"/>
-      <c r="I336" s="9" t="n"/>
-      <c r="J336" s="13" t="n"/>
-      <c r="K336" s="9">
-        <f>IF(OR(E336&lt;&gt;"",I336&lt;&gt;""),"Занято",IF(AND(F335="Повторный приём (1 час)",A335=A336),"Занято","Свободно"))</f>
+      <c r="I336" s="11" t="n"/>
+      <c r="J336" s="9" t="n"/>
+      <c r="K336" s="13" t="n"/>
+      <c r="L336" s="9">
+        <f>IF(OR(E336&lt;&gt;"",J336&lt;&gt;""),"Занято",IF(AND(F335="Повторный приём (1 час)",A335=A336),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10699,10 +11040,11 @@
       <c r="F337" s="11" t="n"/>
       <c r="G337" s="12" t="n"/>
       <c r="H337" s="12" t="n"/>
-      <c r="I337" s="9" t="n"/>
-      <c r="J337" s="13" t="n"/>
-      <c r="K337" s="9">
-        <f>IF(OR(E337&lt;&gt;"",I337&lt;&gt;""),"Занято",IF(AND(F336="Повторный приём (1 час)",A336=A337),"Занято","Свободно"))</f>
+      <c r="I337" s="11" t="n"/>
+      <c r="J337" s="9" t="n"/>
+      <c r="K337" s="13" t="n"/>
+      <c r="L337" s="9">
+        <f>IF(OR(E337&lt;&gt;"",J337&lt;&gt;""),"Занято",IF(AND(F336="Повторный приём (1 час)",A336=A337),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10729,10 +11071,11 @@
       <c r="F338" s="11" t="n"/>
       <c r="G338" s="12" t="n"/>
       <c r="H338" s="12" t="n"/>
-      <c r="I338" s="9" t="n"/>
-      <c r="J338" s="13" t="n"/>
-      <c r="K338" s="9">
-        <f>IF(OR(E338&lt;&gt;"",I338&lt;&gt;""),"Занято",IF(AND(F337="Повторный приём (1 час)",A337=A338),"Занято","Свободно"))</f>
+      <c r="I338" s="11" t="n"/>
+      <c r="J338" s="9" t="n"/>
+      <c r="K338" s="13" t="n"/>
+      <c r="L338" s="9">
+        <f>IF(OR(E338&lt;&gt;"",J338&lt;&gt;""),"Занято",IF(AND(F337="Повторный приём (1 час)",A337=A338),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10759,10 +11102,11 @@
       <c r="F339" s="11" t="n"/>
       <c r="G339" s="12" t="n"/>
       <c r="H339" s="12" t="n"/>
-      <c r="I339" s="9" t="n"/>
-      <c r="J339" s="13" t="n"/>
-      <c r="K339" s="9">
-        <f>IF(OR(E339&lt;&gt;"",I339&lt;&gt;""),"Занято",IF(AND(F338="Повторный приём (1 час)",A338=A339),"Занято","Свободно"))</f>
+      <c r="I339" s="11" t="n"/>
+      <c r="J339" s="9" t="n"/>
+      <c r="K339" s="13" t="n"/>
+      <c r="L339" s="9">
+        <f>IF(OR(E339&lt;&gt;"",J339&lt;&gt;""),"Занято",IF(AND(F338="Повторный приём (1 час)",A338=A339),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10789,10 +11133,11 @@
       <c r="F340" s="17" t="n"/>
       <c r="G340" s="18" t="n"/>
       <c r="H340" s="18" t="n"/>
-      <c r="I340" s="15" t="n"/>
-      <c r="J340" s="19" t="n"/>
-      <c r="K340" s="15">
-        <f>IF(OR(E340&lt;&gt;"",I340&lt;&gt;""),"Занято",IF(AND(F339="Повторный приём (1 час)",A339=A340),"Занято","Свободно"))</f>
+      <c r="I340" s="17" t="n"/>
+      <c r="J340" s="15" t="n"/>
+      <c r="K340" s="19" t="n"/>
+      <c r="L340" s="15">
+        <f>IF(OR(E340&lt;&gt;"",J340&lt;&gt;""),"Занято",IF(AND(F339="Повторный приём (1 час)",A339=A340),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10819,10 +11164,11 @@
       <c r="F341" s="23" t="n"/>
       <c r="G341" s="24" t="n"/>
       <c r="H341" s="24" t="n"/>
-      <c r="I341" s="21" t="n"/>
-      <c r="J341" s="25" t="n"/>
-      <c r="K341" s="21">
-        <f>IF(OR(E341&lt;&gt;"",I341&lt;&gt;""),"Занято",IF(AND(F340="Повторный приём (1 час)",A340=A341),"Занято","Свободно"))</f>
+      <c r="I341" s="23" t="n"/>
+      <c r="J341" s="21" t="n"/>
+      <c r="K341" s="25" t="n"/>
+      <c r="L341" s="21">
+        <f>IF(OR(E341&lt;&gt;"",J341&lt;&gt;""),"Занято",IF(AND(F340="Повторный приём (1 час)",A340=A341),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10849,10 +11195,11 @@
       <c r="F342" s="23" t="n"/>
       <c r="G342" s="24" t="n"/>
       <c r="H342" s="24" t="n"/>
-      <c r="I342" s="21" t="n"/>
-      <c r="J342" s="25" t="n"/>
-      <c r="K342" s="21">
-        <f>IF(OR(E342&lt;&gt;"",I342&lt;&gt;""),"Занято",IF(AND(F341="Повторный приём (1 час)",A341=A342),"Занято","Свободно"))</f>
+      <c r="I342" s="23" t="n"/>
+      <c r="J342" s="21" t="n"/>
+      <c r="K342" s="25" t="n"/>
+      <c r="L342" s="21">
+        <f>IF(OR(E342&lt;&gt;"",J342&lt;&gt;""),"Занято",IF(AND(F341="Повторный приём (1 час)",A341=A342),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10879,10 +11226,11 @@
       <c r="F343" s="23" t="n"/>
       <c r="G343" s="24" t="n"/>
       <c r="H343" s="24" t="n"/>
-      <c r="I343" s="21" t="n"/>
-      <c r="J343" s="25" t="n"/>
-      <c r="K343" s="21">
-        <f>IF(OR(E343&lt;&gt;"",I343&lt;&gt;""),"Занято",IF(AND(F342="Повторный приём (1 час)",A342=A343),"Занято","Свободно"))</f>
+      <c r="I343" s="23" t="n"/>
+      <c r="J343" s="21" t="n"/>
+      <c r="K343" s="25" t="n"/>
+      <c r="L343" s="21">
+        <f>IF(OR(E343&lt;&gt;"",J343&lt;&gt;""),"Занято",IF(AND(F342="Повторный приём (1 час)",A342=A343),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10909,10 +11257,11 @@
       <c r="F344" s="23" t="n"/>
       <c r="G344" s="24" t="n"/>
       <c r="H344" s="24" t="n"/>
-      <c r="I344" s="21" t="n"/>
-      <c r="J344" s="25" t="n"/>
-      <c r="K344" s="21">
-        <f>IF(OR(E344&lt;&gt;"",I344&lt;&gt;""),"Занято",IF(AND(F343="Повторный приём (1 час)",A343=A344),"Занято","Свободно"))</f>
+      <c r="I344" s="23" t="n"/>
+      <c r="J344" s="21" t="n"/>
+      <c r="K344" s="25" t="n"/>
+      <c r="L344" s="21">
+        <f>IF(OR(E344&lt;&gt;"",J344&lt;&gt;""),"Занято",IF(AND(F343="Повторный приём (1 час)",A343=A344),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10939,10 +11288,11 @@
       <c r="F345" s="23" t="n"/>
       <c r="G345" s="24" t="n"/>
       <c r="H345" s="24" t="n"/>
-      <c r="I345" s="21" t="n"/>
-      <c r="J345" s="25" t="n"/>
-      <c r="K345" s="21">
-        <f>IF(OR(E345&lt;&gt;"",I345&lt;&gt;""),"Занято",IF(AND(F344="Повторный приём (1 час)",A344=A345),"Занято","Свободно"))</f>
+      <c r="I345" s="23" t="n"/>
+      <c r="J345" s="21" t="n"/>
+      <c r="K345" s="25" t="n"/>
+      <c r="L345" s="21">
+        <f>IF(OR(E345&lt;&gt;"",J345&lt;&gt;""),"Занято",IF(AND(F344="Повторный приём (1 час)",A344=A345),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10969,10 +11319,11 @@
       <c r="F346" s="23" t="n"/>
       <c r="G346" s="24" t="n"/>
       <c r="H346" s="24" t="n"/>
-      <c r="I346" s="21" t="n"/>
-      <c r="J346" s="25" t="n"/>
-      <c r="K346" s="21">
-        <f>IF(OR(E346&lt;&gt;"",I346&lt;&gt;""),"Занято",IF(AND(F345="Повторный приём (1 час)",A345=A346),"Занято","Свободно"))</f>
+      <c r="I346" s="23" t="n"/>
+      <c r="J346" s="21" t="n"/>
+      <c r="K346" s="25" t="n"/>
+      <c r="L346" s="21">
+        <f>IF(OR(E346&lt;&gt;"",J346&lt;&gt;""),"Занято",IF(AND(F345="Повторный приём (1 час)",A345=A346),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -10999,10 +11350,11 @@
       <c r="F347" s="23" t="n"/>
       <c r="G347" s="24" t="n"/>
       <c r="H347" s="24" t="n"/>
-      <c r="I347" s="21" t="n"/>
-      <c r="J347" s="25" t="n"/>
-      <c r="K347" s="21">
-        <f>IF(OR(E347&lt;&gt;"",I347&lt;&gt;""),"Занято",IF(AND(F346="Повторный приём (1 час)",A346=A347),"Занято","Свободно"))</f>
+      <c r="I347" s="23" t="n"/>
+      <c r="J347" s="21" t="n"/>
+      <c r="K347" s="25" t="n"/>
+      <c r="L347" s="21">
+        <f>IF(OR(E347&lt;&gt;"",J347&lt;&gt;""),"Занято",IF(AND(F346="Повторный приём (1 час)",A346=A347),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11029,10 +11381,11 @@
       <c r="F348" s="23" t="n"/>
       <c r="G348" s="24" t="n"/>
       <c r="H348" s="24" t="n"/>
-      <c r="I348" s="21" t="n"/>
-      <c r="J348" s="25" t="n"/>
-      <c r="K348" s="21">
-        <f>IF(OR(E348&lt;&gt;"",I348&lt;&gt;""),"Занято",IF(AND(F347="Повторный приём (1 час)",A347=A348),"Занято","Свободно"))</f>
+      <c r="I348" s="23" t="n"/>
+      <c r="J348" s="21" t="n"/>
+      <c r="K348" s="25" t="n"/>
+      <c r="L348" s="21">
+        <f>IF(OR(E348&lt;&gt;"",J348&lt;&gt;""),"Занято",IF(AND(F347="Повторный приём (1 час)",A347=A348),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11059,10 +11412,11 @@
       <c r="F349" s="23" t="n"/>
       <c r="G349" s="24" t="n"/>
       <c r="H349" s="24" t="n"/>
-      <c r="I349" s="21" t="n"/>
-      <c r="J349" s="25" t="n"/>
-      <c r="K349" s="21">
-        <f>IF(OR(E349&lt;&gt;"",I349&lt;&gt;""),"Занято",IF(AND(F348="Повторный приём (1 час)",A348=A349),"Занято","Свободно"))</f>
+      <c r="I349" s="23" t="n"/>
+      <c r="J349" s="21" t="n"/>
+      <c r="K349" s="25" t="n"/>
+      <c r="L349" s="21">
+        <f>IF(OR(E349&lt;&gt;"",J349&lt;&gt;""),"Занято",IF(AND(F348="Повторный приём (1 час)",A348=A349),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11089,10 +11443,11 @@
       <c r="F350" s="23" t="n"/>
       <c r="G350" s="24" t="n"/>
       <c r="H350" s="24" t="n"/>
-      <c r="I350" s="21" t="n"/>
-      <c r="J350" s="25" t="n"/>
-      <c r="K350" s="21">
-        <f>IF(OR(E350&lt;&gt;"",I350&lt;&gt;""),"Занято",IF(AND(F349="Повторный приём (1 час)",A349=A350),"Занято","Свободно"))</f>
+      <c r="I350" s="23" t="n"/>
+      <c r="J350" s="21" t="n"/>
+      <c r="K350" s="25" t="n"/>
+      <c r="L350" s="21">
+        <f>IF(OR(E350&lt;&gt;"",J350&lt;&gt;""),"Занято",IF(AND(F349="Повторный приём (1 час)",A349=A350),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11119,10 +11474,11 @@
       <c r="F351" s="23" t="n"/>
       <c r="G351" s="24" t="n"/>
       <c r="H351" s="24" t="n"/>
-      <c r="I351" s="21" t="n"/>
-      <c r="J351" s="25" t="n"/>
-      <c r="K351" s="21">
-        <f>IF(OR(E351&lt;&gt;"",I351&lt;&gt;""),"Занято",IF(AND(F350="Повторный приём (1 час)",A350=A351),"Занято","Свободно"))</f>
+      <c r="I351" s="23" t="n"/>
+      <c r="J351" s="21" t="n"/>
+      <c r="K351" s="25" t="n"/>
+      <c r="L351" s="21">
+        <f>IF(OR(E351&lt;&gt;"",J351&lt;&gt;""),"Занято",IF(AND(F350="Повторный приём (1 час)",A350=A351),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11149,10 +11505,11 @@
       <c r="F352" s="23" t="n"/>
       <c r="G352" s="24" t="n"/>
       <c r="H352" s="24" t="n"/>
-      <c r="I352" s="21" t="n"/>
-      <c r="J352" s="25" t="n"/>
-      <c r="K352" s="21">
-        <f>IF(OR(E352&lt;&gt;"",I352&lt;&gt;""),"Занято",IF(AND(F351="Повторный приём (1 час)",A351=A352),"Занято","Свободно"))</f>
+      <c r="I352" s="23" t="n"/>
+      <c r="J352" s="21" t="n"/>
+      <c r="K352" s="25" t="n"/>
+      <c r="L352" s="21">
+        <f>IF(OR(E352&lt;&gt;"",J352&lt;&gt;""),"Занято",IF(AND(F351="Повторный приём (1 час)",A351=A352),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11179,10 +11536,11 @@
       <c r="F353" s="23" t="n"/>
       <c r="G353" s="24" t="n"/>
       <c r="H353" s="24" t="n"/>
-      <c r="I353" s="21" t="n"/>
-      <c r="J353" s="25" t="n"/>
-      <c r="K353" s="21">
-        <f>IF(OR(E353&lt;&gt;"",I353&lt;&gt;""),"Занято",IF(AND(F352="Повторный приём (1 час)",A352=A353),"Занято","Свободно"))</f>
+      <c r="I353" s="23" t="n"/>
+      <c r="J353" s="21" t="n"/>
+      <c r="K353" s="25" t="n"/>
+      <c r="L353" s="21">
+        <f>IF(OR(E353&lt;&gt;"",J353&lt;&gt;""),"Занято",IF(AND(F352="Повторный приём (1 час)",A352=A353),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11209,10 +11567,11 @@
       <c r="F354" s="23" t="n"/>
       <c r="G354" s="24" t="n"/>
       <c r="H354" s="24" t="n"/>
-      <c r="I354" s="21" t="n"/>
-      <c r="J354" s="25" t="n"/>
-      <c r="K354" s="21">
-        <f>IF(OR(E354&lt;&gt;"",I354&lt;&gt;""),"Занято",IF(AND(F353="Повторный приём (1 час)",A353=A354),"Занято","Свободно"))</f>
+      <c r="I354" s="23" t="n"/>
+      <c r="J354" s="21" t="n"/>
+      <c r="K354" s="25" t="n"/>
+      <c r="L354" s="21">
+        <f>IF(OR(E354&lt;&gt;"",J354&lt;&gt;""),"Занято",IF(AND(F353="Повторный приём (1 час)",A353=A354),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11239,10 +11598,11 @@
       <c r="F355" s="23" t="n"/>
       <c r="G355" s="24" t="n"/>
       <c r="H355" s="24" t="n"/>
-      <c r="I355" s="21" t="n"/>
-      <c r="J355" s="25" t="n"/>
-      <c r="K355" s="21">
-        <f>IF(OR(E355&lt;&gt;"",I355&lt;&gt;""),"Занято",IF(AND(F354="Повторный приём (1 час)",A354=A355),"Занято","Свободно"))</f>
+      <c r="I355" s="23" t="n"/>
+      <c r="J355" s="21" t="n"/>
+      <c r="K355" s="25" t="n"/>
+      <c r="L355" s="21">
+        <f>IF(OR(E355&lt;&gt;"",J355&lt;&gt;""),"Занято",IF(AND(F354="Повторный приём (1 час)",A354=A355),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11269,10 +11629,11 @@
       <c r="F356" s="23" t="n"/>
       <c r="G356" s="24" t="n"/>
       <c r="H356" s="24" t="n"/>
-      <c r="I356" s="21" t="n"/>
-      <c r="J356" s="25" t="n"/>
-      <c r="K356" s="21">
-        <f>IF(OR(E356&lt;&gt;"",I356&lt;&gt;""),"Занято",IF(AND(F355="Повторный приём (1 час)",A355=A356),"Занято","Свободно"))</f>
+      <c r="I356" s="23" t="n"/>
+      <c r="J356" s="21" t="n"/>
+      <c r="K356" s="25" t="n"/>
+      <c r="L356" s="21">
+        <f>IF(OR(E356&lt;&gt;"",J356&lt;&gt;""),"Занято",IF(AND(F355="Повторный приём (1 час)",A355=A356),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11299,10 +11660,11 @@
       <c r="F357" s="23" t="n"/>
       <c r="G357" s="24" t="n"/>
       <c r="H357" s="24" t="n"/>
-      <c r="I357" s="21" t="n"/>
-      <c r="J357" s="25" t="n"/>
-      <c r="K357" s="21">
-        <f>IF(OR(E357&lt;&gt;"",I357&lt;&gt;""),"Занято",IF(AND(F356="Повторный приём (1 час)",A356=A357),"Занято","Свободно"))</f>
+      <c r="I357" s="23" t="n"/>
+      <c r="J357" s="21" t="n"/>
+      <c r="K357" s="25" t="n"/>
+      <c r="L357" s="21">
+        <f>IF(OR(E357&lt;&gt;"",J357&lt;&gt;""),"Занято",IF(AND(F356="Повторный приём (1 час)",A356=A357),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11329,10 +11691,11 @@
       <c r="F358" s="5" t="n"/>
       <c r="G358" s="6" t="n"/>
       <c r="H358" s="6" t="n"/>
-      <c r="I358" s="3" t="n"/>
-      <c r="J358" s="7" t="n"/>
-      <c r="K358" s="3">
-        <f>IF(OR(E358&lt;&gt;"",I358&lt;&gt;""),"Занято",IF(AND(F357="Повторный приём (1 час)",A357=A358),"Занято","Свободно"))</f>
+      <c r="I358" s="5" t="n"/>
+      <c r="J358" s="3" t="n"/>
+      <c r="K358" s="7" t="n"/>
+      <c r="L358" s="3">
+        <f>IF(OR(E358&lt;&gt;"",J358&lt;&gt;""),"Занято",IF(AND(F357="Повторный приём (1 час)",A357=A358),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11359,10 +11722,11 @@
       <c r="F359" s="11" t="n"/>
       <c r="G359" s="12" t="n"/>
       <c r="H359" s="12" t="n"/>
-      <c r="I359" s="9" t="n"/>
-      <c r="J359" s="13" t="n"/>
-      <c r="K359" s="9">
-        <f>IF(OR(E359&lt;&gt;"",I359&lt;&gt;""),"Занято",IF(AND(F358="Повторный приём (1 час)",A358=A359),"Занято","Свободно"))</f>
+      <c r="I359" s="11" t="n"/>
+      <c r="J359" s="9" t="n"/>
+      <c r="K359" s="13" t="n"/>
+      <c r="L359" s="9">
+        <f>IF(OR(E359&lt;&gt;"",J359&lt;&gt;""),"Занято",IF(AND(F358="Повторный приём (1 час)",A358=A359),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11389,10 +11753,11 @@
       <c r="F360" s="11" t="n"/>
       <c r="G360" s="12" t="n"/>
       <c r="H360" s="12" t="n"/>
-      <c r="I360" s="9" t="n"/>
-      <c r="J360" s="13" t="n"/>
-      <c r="K360" s="9">
-        <f>IF(OR(E360&lt;&gt;"",I360&lt;&gt;""),"Занято",IF(AND(F359="Повторный приём (1 час)",A359=A360),"Занято","Свободно"))</f>
+      <c r="I360" s="11" t="n"/>
+      <c r="J360" s="9" t="n"/>
+      <c r="K360" s="13" t="n"/>
+      <c r="L360" s="9">
+        <f>IF(OR(E360&lt;&gt;"",J360&lt;&gt;""),"Занято",IF(AND(F359="Повторный приём (1 час)",A359=A360),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11419,10 +11784,11 @@
       <c r="F361" s="11" t="n"/>
       <c r="G361" s="12" t="n"/>
       <c r="H361" s="12" t="n"/>
-      <c r="I361" s="9" t="n"/>
-      <c r="J361" s="13" t="n"/>
-      <c r="K361" s="9">
-        <f>IF(OR(E361&lt;&gt;"",I361&lt;&gt;""),"Занято",IF(AND(F360="Повторный приём (1 час)",A360=A361),"Занято","Свободно"))</f>
+      <c r="I361" s="11" t="n"/>
+      <c r="J361" s="9" t="n"/>
+      <c r="K361" s="13" t="n"/>
+      <c r="L361" s="9">
+        <f>IF(OR(E361&lt;&gt;"",J361&lt;&gt;""),"Занято",IF(AND(F360="Повторный приём (1 час)",A360=A361),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11449,10 +11815,11 @@
       <c r="F362" s="11" t="n"/>
       <c r="G362" s="12" t="n"/>
       <c r="H362" s="12" t="n"/>
-      <c r="I362" s="9" t="n"/>
-      <c r="J362" s="13" t="n"/>
-      <c r="K362" s="9">
-        <f>IF(OR(E362&lt;&gt;"",I362&lt;&gt;""),"Занято",IF(AND(F361="Повторный приём (1 час)",A361=A362),"Занято","Свободно"))</f>
+      <c r="I362" s="11" t="n"/>
+      <c r="J362" s="9" t="n"/>
+      <c r="K362" s="13" t="n"/>
+      <c r="L362" s="9">
+        <f>IF(OR(E362&lt;&gt;"",J362&lt;&gt;""),"Занято",IF(AND(F361="Повторный приём (1 час)",A361=A362),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11479,10 +11846,11 @@
       <c r="F363" s="11" t="n"/>
       <c r="G363" s="12" t="n"/>
       <c r="H363" s="12" t="n"/>
-      <c r="I363" s="9" t="n"/>
-      <c r="J363" s="13" t="n"/>
-      <c r="K363" s="9">
-        <f>IF(OR(E363&lt;&gt;"",I363&lt;&gt;""),"Занято",IF(AND(F362="Повторный приём (1 час)",A362=A363),"Занято","Свободно"))</f>
+      <c r="I363" s="11" t="n"/>
+      <c r="J363" s="9" t="n"/>
+      <c r="K363" s="13" t="n"/>
+      <c r="L363" s="9">
+        <f>IF(OR(E363&lt;&gt;"",J363&lt;&gt;""),"Занято",IF(AND(F362="Повторный приём (1 час)",A362=A363),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11509,10 +11877,11 @@
       <c r="F364" s="11" t="n"/>
       <c r="G364" s="12" t="n"/>
       <c r="H364" s="12" t="n"/>
-      <c r="I364" s="9" t="n"/>
-      <c r="J364" s="13" t="n"/>
-      <c r="K364" s="9">
-        <f>IF(OR(E364&lt;&gt;"",I364&lt;&gt;""),"Занято",IF(AND(F363="Повторный приём (1 час)",A363=A364),"Занято","Свободно"))</f>
+      <c r="I364" s="11" t="n"/>
+      <c r="J364" s="9" t="n"/>
+      <c r="K364" s="13" t="n"/>
+      <c r="L364" s="9">
+        <f>IF(OR(E364&lt;&gt;"",J364&lt;&gt;""),"Занято",IF(AND(F363="Повторный приём (1 час)",A363=A364),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11539,10 +11908,11 @@
       <c r="F365" s="11" t="n"/>
       <c r="G365" s="12" t="n"/>
       <c r="H365" s="12" t="n"/>
-      <c r="I365" s="9" t="n"/>
-      <c r="J365" s="13" t="n"/>
-      <c r="K365" s="9">
-        <f>IF(OR(E365&lt;&gt;"",I365&lt;&gt;""),"Занято",IF(AND(F364="Повторный приём (1 час)",A364=A365),"Занято","Свободно"))</f>
+      <c r="I365" s="11" t="n"/>
+      <c r="J365" s="9" t="n"/>
+      <c r="K365" s="13" t="n"/>
+      <c r="L365" s="9">
+        <f>IF(OR(E365&lt;&gt;"",J365&lt;&gt;""),"Занято",IF(AND(F364="Повторный приём (1 час)",A364=A365),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11569,10 +11939,11 @@
       <c r="F366" s="11" t="n"/>
       <c r="G366" s="12" t="n"/>
       <c r="H366" s="12" t="n"/>
-      <c r="I366" s="9" t="n"/>
-      <c r="J366" s="13" t="n"/>
-      <c r="K366" s="9">
-        <f>IF(OR(E366&lt;&gt;"",I366&lt;&gt;""),"Занято",IF(AND(F365="Повторный приём (1 час)",A365=A366),"Занято","Свободно"))</f>
+      <c r="I366" s="11" t="n"/>
+      <c r="J366" s="9" t="n"/>
+      <c r="K366" s="13" t="n"/>
+      <c r="L366" s="9">
+        <f>IF(OR(E366&lt;&gt;"",J366&lt;&gt;""),"Занято",IF(AND(F365="Повторный приём (1 час)",A365=A366),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11599,10 +11970,11 @@
       <c r="F367" s="11" t="n"/>
       <c r="G367" s="12" t="n"/>
       <c r="H367" s="12" t="n"/>
-      <c r="I367" s="9" t="n"/>
-      <c r="J367" s="13" t="n"/>
-      <c r="K367" s="9">
-        <f>IF(OR(E367&lt;&gt;"",I367&lt;&gt;""),"Занято",IF(AND(F366="Повторный приём (1 час)",A366=A367),"Занято","Свободно"))</f>
+      <c r="I367" s="11" t="n"/>
+      <c r="J367" s="9" t="n"/>
+      <c r="K367" s="13" t="n"/>
+      <c r="L367" s="9">
+        <f>IF(OR(E367&lt;&gt;"",J367&lt;&gt;""),"Занято",IF(AND(F366="Повторный приём (1 час)",A366=A367),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11629,10 +12001,11 @@
       <c r="F368" s="11" t="n"/>
       <c r="G368" s="12" t="n"/>
       <c r="H368" s="12" t="n"/>
-      <c r="I368" s="9" t="n"/>
-      <c r="J368" s="13" t="n"/>
-      <c r="K368" s="9">
-        <f>IF(OR(E368&lt;&gt;"",I368&lt;&gt;""),"Занято",IF(AND(F367="Повторный приём (1 час)",A367=A368),"Занято","Свободно"))</f>
+      <c r="I368" s="11" t="n"/>
+      <c r="J368" s="9" t="n"/>
+      <c r="K368" s="13" t="n"/>
+      <c r="L368" s="9">
+        <f>IF(OR(E368&lt;&gt;"",J368&lt;&gt;""),"Занято",IF(AND(F367="Повторный приём (1 час)",A367=A368),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11659,10 +12032,11 @@
       <c r="F369" s="11" t="n"/>
       <c r="G369" s="12" t="n"/>
       <c r="H369" s="12" t="n"/>
-      <c r="I369" s="9" t="n"/>
-      <c r="J369" s="13" t="n"/>
-      <c r="K369" s="9">
-        <f>IF(OR(E369&lt;&gt;"",I369&lt;&gt;""),"Занято",IF(AND(F368="Повторный приём (1 час)",A368=A369),"Занято","Свободно"))</f>
+      <c r="I369" s="11" t="n"/>
+      <c r="J369" s="9" t="n"/>
+      <c r="K369" s="13" t="n"/>
+      <c r="L369" s="9">
+        <f>IF(OR(E369&lt;&gt;"",J369&lt;&gt;""),"Занято",IF(AND(F368="Повторный приём (1 час)",A368=A369),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11689,10 +12063,11 @@
       <c r="F370" s="11" t="n"/>
       <c r="G370" s="12" t="n"/>
       <c r="H370" s="12" t="n"/>
-      <c r="I370" s="9" t="n"/>
-      <c r="J370" s="13" t="n"/>
-      <c r="K370" s="9">
-        <f>IF(OR(E370&lt;&gt;"",I370&lt;&gt;""),"Занято",IF(AND(F369="Повторный приём (1 час)",A369=A370),"Занято","Свободно"))</f>
+      <c r="I370" s="11" t="n"/>
+      <c r="J370" s="9" t="n"/>
+      <c r="K370" s="13" t="n"/>
+      <c r="L370" s="9">
+        <f>IF(OR(E370&lt;&gt;"",J370&lt;&gt;""),"Занято",IF(AND(F369="Повторный приём (1 час)",A369=A370),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11719,10 +12094,11 @@
       <c r="F371" s="11" t="n"/>
       <c r="G371" s="12" t="n"/>
       <c r="H371" s="12" t="n"/>
-      <c r="I371" s="9" t="n"/>
-      <c r="J371" s="13" t="n"/>
-      <c r="K371" s="9">
-        <f>IF(OR(E371&lt;&gt;"",I371&lt;&gt;""),"Занято",IF(AND(F370="Повторный приём (1 час)",A370=A371),"Занято","Свободно"))</f>
+      <c r="I371" s="11" t="n"/>
+      <c r="J371" s="9" t="n"/>
+      <c r="K371" s="13" t="n"/>
+      <c r="L371" s="9">
+        <f>IF(OR(E371&lt;&gt;"",J371&lt;&gt;""),"Занято",IF(AND(F370="Повторный приём (1 час)",A370=A371),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11749,10 +12125,11 @@
       <c r="F372" s="11" t="n"/>
       <c r="G372" s="12" t="n"/>
       <c r="H372" s="12" t="n"/>
-      <c r="I372" s="9" t="n"/>
-      <c r="J372" s="13" t="n"/>
-      <c r="K372" s="9">
-        <f>IF(OR(E372&lt;&gt;"",I372&lt;&gt;""),"Занято",IF(AND(F371="Повторный приём (1 час)",A371=A372),"Занято","Свободно"))</f>
+      <c r="I372" s="11" t="n"/>
+      <c r="J372" s="9" t="n"/>
+      <c r="K372" s="13" t="n"/>
+      <c r="L372" s="9">
+        <f>IF(OR(E372&lt;&gt;"",J372&lt;&gt;""),"Занято",IF(AND(F371="Повторный приём (1 час)",A371=A372),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11779,10 +12156,11 @@
       <c r="F373" s="11" t="n"/>
       <c r="G373" s="12" t="n"/>
       <c r="H373" s="12" t="n"/>
-      <c r="I373" s="9" t="n"/>
-      <c r="J373" s="13" t="n"/>
-      <c r="K373" s="9">
-        <f>IF(OR(E373&lt;&gt;"",I373&lt;&gt;""),"Занято",IF(AND(F372="Повторный приём (1 час)",A372=A373),"Занято","Свободно"))</f>
+      <c r="I373" s="11" t="n"/>
+      <c r="J373" s="9" t="n"/>
+      <c r="K373" s="13" t="n"/>
+      <c r="L373" s="9">
+        <f>IF(OR(E373&lt;&gt;"",J373&lt;&gt;""),"Занято",IF(AND(F372="Повторный приём (1 час)",A372=A373),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11809,10 +12187,11 @@
       <c r="F374" s="11" t="n"/>
       <c r="G374" s="12" t="n"/>
       <c r="H374" s="12" t="n"/>
-      <c r="I374" s="9" t="n"/>
-      <c r="J374" s="13" t="n"/>
-      <c r="K374" s="9">
-        <f>IF(OR(E374&lt;&gt;"",I374&lt;&gt;""),"Занято",IF(AND(F373="Повторный приём (1 час)",A373=A374),"Занято","Свободно"))</f>
+      <c r="I374" s="11" t="n"/>
+      <c r="J374" s="9" t="n"/>
+      <c r="K374" s="13" t="n"/>
+      <c r="L374" s="9">
+        <f>IF(OR(E374&lt;&gt;"",J374&lt;&gt;""),"Занято",IF(AND(F373="Повторный приём (1 час)",A373=A374),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11839,10 +12218,11 @@
       <c r="F375" s="11" t="n"/>
       <c r="G375" s="12" t="n"/>
       <c r="H375" s="12" t="n"/>
-      <c r="I375" s="9" t="n"/>
-      <c r="J375" s="13" t="n"/>
-      <c r="K375" s="9">
-        <f>IF(OR(E375&lt;&gt;"",I375&lt;&gt;""),"Занято",IF(AND(F374="Повторный приём (1 час)",A374=A375),"Занято","Свободно"))</f>
+      <c r="I375" s="11" t="n"/>
+      <c r="J375" s="9" t="n"/>
+      <c r="K375" s="13" t="n"/>
+      <c r="L375" s="9">
+        <f>IF(OR(E375&lt;&gt;"",J375&lt;&gt;""),"Занято",IF(AND(F374="Повторный приём (1 час)",A374=A375),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11869,10 +12249,11 @@
       <c r="F376" s="17" t="n"/>
       <c r="G376" s="18" t="n"/>
       <c r="H376" s="18" t="n"/>
-      <c r="I376" s="15" t="n"/>
-      <c r="J376" s="19" t="n"/>
-      <c r="K376" s="15">
-        <f>IF(OR(E376&lt;&gt;"",I376&lt;&gt;""),"Занято",IF(AND(F375="Повторный приём (1 час)",A375=A376),"Занято","Свободно"))</f>
+      <c r="I376" s="17" t="n"/>
+      <c r="J376" s="15" t="n"/>
+      <c r="K376" s="19" t="n"/>
+      <c r="L376" s="15">
+        <f>IF(OR(E376&lt;&gt;"",J376&lt;&gt;""),"Занято",IF(AND(F375="Повторный приём (1 час)",A375=A376),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11899,10 +12280,11 @@
       <c r="F377" s="23" t="n"/>
       <c r="G377" s="24" t="n"/>
       <c r="H377" s="24" t="n"/>
-      <c r="I377" s="21" t="n"/>
-      <c r="J377" s="25" t="n"/>
-      <c r="K377" s="21">
-        <f>IF(OR(E377&lt;&gt;"",I377&lt;&gt;""),"Занято",IF(AND(F376="Повторный приём (1 час)",A376=A377),"Занято","Свободно"))</f>
+      <c r="I377" s="23" t="n"/>
+      <c r="J377" s="21" t="n"/>
+      <c r="K377" s="25" t="n"/>
+      <c r="L377" s="21">
+        <f>IF(OR(E377&lt;&gt;"",J377&lt;&gt;""),"Занято",IF(AND(F376="Повторный приём (1 час)",A376=A377),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11929,10 +12311,11 @@
       <c r="F378" s="23" t="n"/>
       <c r="G378" s="24" t="n"/>
       <c r="H378" s="24" t="n"/>
-      <c r="I378" s="21" t="n"/>
-      <c r="J378" s="25" t="n"/>
-      <c r="K378" s="21">
-        <f>IF(OR(E378&lt;&gt;"",I378&lt;&gt;""),"Занято",IF(AND(F377="Повторный приём (1 час)",A377=A378),"Занято","Свободно"))</f>
+      <c r="I378" s="23" t="n"/>
+      <c r="J378" s="21" t="n"/>
+      <c r="K378" s="25" t="n"/>
+      <c r="L378" s="21">
+        <f>IF(OR(E378&lt;&gt;"",J378&lt;&gt;""),"Занято",IF(AND(F377="Повторный приём (1 час)",A377=A378),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11959,10 +12342,11 @@
       <c r="F379" s="23" t="n"/>
       <c r="G379" s="24" t="n"/>
       <c r="H379" s="24" t="n"/>
-      <c r="I379" s="21" t="n"/>
-      <c r="J379" s="25" t="n"/>
-      <c r="K379" s="21">
-        <f>IF(OR(E379&lt;&gt;"",I379&lt;&gt;""),"Занято",IF(AND(F378="Повторный приём (1 час)",A378=A379),"Занято","Свободно"))</f>
+      <c r="I379" s="23" t="n"/>
+      <c r="J379" s="21" t="n"/>
+      <c r="K379" s="25" t="n"/>
+      <c r="L379" s="21">
+        <f>IF(OR(E379&lt;&gt;"",J379&lt;&gt;""),"Занято",IF(AND(F378="Повторный приём (1 час)",A378=A379),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -11989,10 +12373,11 @@
       <c r="F380" s="23" t="n"/>
       <c r="G380" s="24" t="n"/>
       <c r="H380" s="24" t="n"/>
-      <c r="I380" s="21" t="n"/>
-      <c r="J380" s="25" t="n"/>
-      <c r="K380" s="21">
-        <f>IF(OR(E380&lt;&gt;"",I380&lt;&gt;""),"Занято",IF(AND(F379="Повторный приём (1 час)",A379=A380),"Занято","Свободно"))</f>
+      <c r="I380" s="23" t="n"/>
+      <c r="J380" s="21" t="n"/>
+      <c r="K380" s="25" t="n"/>
+      <c r="L380" s="21">
+        <f>IF(OR(E380&lt;&gt;"",J380&lt;&gt;""),"Занято",IF(AND(F379="Повторный приём (1 час)",A379=A380),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12019,10 +12404,11 @@
       <c r="F381" s="23" t="n"/>
       <c r="G381" s="24" t="n"/>
       <c r="H381" s="24" t="n"/>
-      <c r="I381" s="21" t="n"/>
-      <c r="J381" s="25" t="n"/>
-      <c r="K381" s="21">
-        <f>IF(OR(E381&lt;&gt;"",I381&lt;&gt;""),"Занято",IF(AND(F380="Повторный приём (1 час)",A380=A381),"Занято","Свободно"))</f>
+      <c r="I381" s="23" t="n"/>
+      <c r="J381" s="21" t="n"/>
+      <c r="K381" s="25" t="n"/>
+      <c r="L381" s="21">
+        <f>IF(OR(E381&lt;&gt;"",J381&lt;&gt;""),"Занято",IF(AND(F380="Повторный приём (1 час)",A380=A381),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12049,10 +12435,11 @@
       <c r="F382" s="23" t="n"/>
       <c r="G382" s="24" t="n"/>
       <c r="H382" s="24" t="n"/>
-      <c r="I382" s="21" t="n"/>
-      <c r="J382" s="25" t="n"/>
-      <c r="K382" s="21">
-        <f>IF(OR(E382&lt;&gt;"",I382&lt;&gt;""),"Занято",IF(AND(F381="Повторный приём (1 час)",A381=A382),"Занято","Свободно"))</f>
+      <c r="I382" s="23" t="n"/>
+      <c r="J382" s="21" t="n"/>
+      <c r="K382" s="25" t="n"/>
+      <c r="L382" s="21">
+        <f>IF(OR(E382&lt;&gt;"",J382&lt;&gt;""),"Занято",IF(AND(F381="Повторный приём (1 час)",A381=A382),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12079,10 +12466,11 @@
       <c r="F383" s="23" t="n"/>
       <c r="G383" s="24" t="n"/>
       <c r="H383" s="24" t="n"/>
-      <c r="I383" s="21" t="n"/>
-      <c r="J383" s="25" t="n"/>
-      <c r="K383" s="21">
-        <f>IF(OR(E383&lt;&gt;"",I383&lt;&gt;""),"Занято",IF(AND(F382="Повторный приём (1 час)",A382=A383),"Занято","Свободно"))</f>
+      <c r="I383" s="23" t="n"/>
+      <c r="J383" s="21" t="n"/>
+      <c r="K383" s="25" t="n"/>
+      <c r="L383" s="21">
+        <f>IF(OR(E383&lt;&gt;"",J383&lt;&gt;""),"Занято",IF(AND(F382="Повторный приём (1 час)",A382=A383),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12109,10 +12497,11 @@
       <c r="F384" s="23" t="n"/>
       <c r="G384" s="24" t="n"/>
       <c r="H384" s="24" t="n"/>
-      <c r="I384" s="21" t="n"/>
-      <c r="J384" s="25" t="n"/>
-      <c r="K384" s="21">
-        <f>IF(OR(E384&lt;&gt;"",I384&lt;&gt;""),"Занято",IF(AND(F383="Повторный приём (1 час)",A383=A384),"Занято","Свободно"))</f>
+      <c r="I384" s="23" t="n"/>
+      <c r="J384" s="21" t="n"/>
+      <c r="K384" s="25" t="n"/>
+      <c r="L384" s="21">
+        <f>IF(OR(E384&lt;&gt;"",J384&lt;&gt;""),"Занято",IF(AND(F383="Повторный приём (1 час)",A383=A384),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12139,10 +12528,11 @@
       <c r="F385" s="23" t="n"/>
       <c r="G385" s="24" t="n"/>
       <c r="H385" s="24" t="n"/>
-      <c r="I385" s="21" t="n"/>
-      <c r="J385" s="25" t="n"/>
-      <c r="K385" s="21">
-        <f>IF(OR(E385&lt;&gt;"",I385&lt;&gt;""),"Занято",IF(AND(F384="Повторный приём (1 час)",A384=A385),"Занято","Свободно"))</f>
+      <c r="I385" s="23" t="n"/>
+      <c r="J385" s="21" t="n"/>
+      <c r="K385" s="25" t="n"/>
+      <c r="L385" s="21">
+        <f>IF(OR(E385&lt;&gt;"",J385&lt;&gt;""),"Занято",IF(AND(F384="Повторный приём (1 час)",A384=A385),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12169,10 +12559,11 @@
       <c r="F386" s="23" t="n"/>
       <c r="G386" s="24" t="n"/>
       <c r="H386" s="24" t="n"/>
-      <c r="I386" s="21" t="n"/>
-      <c r="J386" s="25" t="n"/>
-      <c r="K386" s="21">
-        <f>IF(OR(E386&lt;&gt;"",I386&lt;&gt;""),"Занято",IF(AND(F385="Повторный приём (1 час)",A385=A386),"Занято","Свободно"))</f>
+      <c r="I386" s="23" t="n"/>
+      <c r="J386" s="21" t="n"/>
+      <c r="K386" s="25" t="n"/>
+      <c r="L386" s="21">
+        <f>IF(OR(E386&lt;&gt;"",J386&lt;&gt;""),"Занято",IF(AND(F385="Повторный приём (1 час)",A385=A386),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12199,10 +12590,11 @@
       <c r="F387" s="23" t="n"/>
       <c r="G387" s="24" t="n"/>
       <c r="H387" s="24" t="n"/>
-      <c r="I387" s="21" t="n"/>
-      <c r="J387" s="25" t="n"/>
-      <c r="K387" s="21">
-        <f>IF(OR(E387&lt;&gt;"",I387&lt;&gt;""),"Занято",IF(AND(F386="Повторный приём (1 час)",A386=A387),"Занято","Свободно"))</f>
+      <c r="I387" s="23" t="n"/>
+      <c r="J387" s="21" t="n"/>
+      <c r="K387" s="25" t="n"/>
+      <c r="L387" s="21">
+        <f>IF(OR(E387&lt;&gt;"",J387&lt;&gt;""),"Занято",IF(AND(F386="Повторный приём (1 час)",A386=A387),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12229,10 +12621,11 @@
       <c r="F388" s="23" t="n"/>
       <c r="G388" s="24" t="n"/>
       <c r="H388" s="24" t="n"/>
-      <c r="I388" s="21" t="n"/>
-      <c r="J388" s="25" t="n"/>
-      <c r="K388" s="21">
-        <f>IF(OR(E388&lt;&gt;"",I388&lt;&gt;""),"Занято",IF(AND(F387="Повторный приём (1 час)",A387=A388),"Занято","Свободно"))</f>
+      <c r="I388" s="23" t="n"/>
+      <c r="J388" s="21" t="n"/>
+      <c r="K388" s="25" t="n"/>
+      <c r="L388" s="21">
+        <f>IF(OR(E388&lt;&gt;"",J388&lt;&gt;""),"Занято",IF(AND(F387="Повторный приём (1 час)",A387=A388),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12259,10 +12652,11 @@
       <c r="F389" s="23" t="n"/>
       <c r="G389" s="24" t="n"/>
       <c r="H389" s="24" t="n"/>
-      <c r="I389" s="21" t="n"/>
-      <c r="J389" s="25" t="n"/>
-      <c r="K389" s="21">
-        <f>IF(OR(E389&lt;&gt;"",I389&lt;&gt;""),"Занято",IF(AND(F388="Повторный приём (1 час)",A388=A389),"Занято","Свободно"))</f>
+      <c r="I389" s="23" t="n"/>
+      <c r="J389" s="21" t="n"/>
+      <c r="K389" s="25" t="n"/>
+      <c r="L389" s="21">
+        <f>IF(OR(E389&lt;&gt;"",J389&lt;&gt;""),"Занято",IF(AND(F388="Повторный приём (1 час)",A388=A389),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12289,10 +12683,11 @@
       <c r="F390" s="23" t="n"/>
       <c r="G390" s="24" t="n"/>
       <c r="H390" s="24" t="n"/>
-      <c r="I390" s="21" t="n"/>
-      <c r="J390" s="25" t="n"/>
-      <c r="K390" s="21">
-        <f>IF(OR(E390&lt;&gt;"",I390&lt;&gt;""),"Занято",IF(AND(F389="Повторный приём (1 час)",A389=A390),"Занято","Свободно"))</f>
+      <c r="I390" s="23" t="n"/>
+      <c r="J390" s="21" t="n"/>
+      <c r="K390" s="25" t="n"/>
+      <c r="L390" s="21">
+        <f>IF(OR(E390&lt;&gt;"",J390&lt;&gt;""),"Занято",IF(AND(F389="Повторный приём (1 час)",A389=A390),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12319,10 +12714,11 @@
       <c r="F391" s="23" t="n"/>
       <c r="G391" s="24" t="n"/>
       <c r="H391" s="24" t="n"/>
-      <c r="I391" s="21" t="n"/>
-      <c r="J391" s="25" t="n"/>
-      <c r="K391" s="21">
-        <f>IF(OR(E391&lt;&gt;"",I391&lt;&gt;""),"Занято",IF(AND(F390="Повторный приём (1 час)",A390=A391),"Занято","Свободно"))</f>
+      <c r="I391" s="23" t="n"/>
+      <c r="J391" s="21" t="n"/>
+      <c r="K391" s="25" t="n"/>
+      <c r="L391" s="21">
+        <f>IF(OR(E391&lt;&gt;"",J391&lt;&gt;""),"Занято",IF(AND(F390="Повторный приём (1 час)",A390=A391),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12349,10 +12745,11 @@
       <c r="F392" s="23" t="n"/>
       <c r="G392" s="24" t="n"/>
       <c r="H392" s="24" t="n"/>
-      <c r="I392" s="21" t="n"/>
-      <c r="J392" s="25" t="n"/>
-      <c r="K392" s="21">
-        <f>IF(OR(E392&lt;&gt;"",I392&lt;&gt;""),"Занято",IF(AND(F391="Повторный приём (1 час)",A391=A392),"Занято","Свободно"))</f>
+      <c r="I392" s="23" t="n"/>
+      <c r="J392" s="21" t="n"/>
+      <c r="K392" s="25" t="n"/>
+      <c r="L392" s="21">
+        <f>IF(OR(E392&lt;&gt;"",J392&lt;&gt;""),"Занято",IF(AND(F391="Повторный приём (1 час)",A391=A392),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12379,10 +12776,11 @@
       <c r="F393" s="23" t="n"/>
       <c r="G393" s="24" t="n"/>
       <c r="H393" s="24" t="n"/>
-      <c r="I393" s="21" t="n"/>
-      <c r="J393" s="25" t="n"/>
-      <c r="K393" s="21">
-        <f>IF(OR(E393&lt;&gt;"",I393&lt;&gt;""),"Занято",IF(AND(F392="Повторный приём (1 час)",A392=A393),"Занято","Свободно"))</f>
+      <c r="I393" s="23" t="n"/>
+      <c r="J393" s="21" t="n"/>
+      <c r="K393" s="25" t="n"/>
+      <c r="L393" s="21">
+        <f>IF(OR(E393&lt;&gt;"",J393&lt;&gt;""),"Занято",IF(AND(F392="Повторный приём (1 час)",A392=A393),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12409,10 +12807,11 @@
       <c r="F394" s="5" t="n"/>
       <c r="G394" s="6" t="n"/>
       <c r="H394" s="6" t="n"/>
-      <c r="I394" s="3" t="n"/>
-      <c r="J394" s="7" t="n"/>
-      <c r="K394" s="3">
-        <f>IF(OR(E394&lt;&gt;"",I394&lt;&gt;""),"Занято",IF(AND(F393="Повторный приём (1 час)",A393=A394),"Занято","Свободно"))</f>
+      <c r="I394" s="5" t="n"/>
+      <c r="J394" s="3" t="n"/>
+      <c r="K394" s="7" t="n"/>
+      <c r="L394" s="3">
+        <f>IF(OR(E394&lt;&gt;"",J394&lt;&gt;""),"Занято",IF(AND(F393="Повторный приём (1 час)",A393=A394),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12439,10 +12838,11 @@
       <c r="F395" s="11" t="n"/>
       <c r="G395" s="12" t="n"/>
       <c r="H395" s="12" t="n"/>
-      <c r="I395" s="9" t="n"/>
-      <c r="J395" s="13" t="n"/>
-      <c r="K395" s="9">
-        <f>IF(OR(E395&lt;&gt;"",I395&lt;&gt;""),"Занято",IF(AND(F394="Повторный приём (1 час)",A394=A395),"Занято","Свободно"))</f>
+      <c r="I395" s="11" t="n"/>
+      <c r="J395" s="9" t="n"/>
+      <c r="K395" s="13" t="n"/>
+      <c r="L395" s="9">
+        <f>IF(OR(E395&lt;&gt;"",J395&lt;&gt;""),"Занято",IF(AND(F394="Повторный приём (1 час)",A394=A395),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12469,10 +12869,11 @@
       <c r="F396" s="11" t="n"/>
       <c r="G396" s="12" t="n"/>
       <c r="H396" s="12" t="n"/>
-      <c r="I396" s="9" t="n"/>
-      <c r="J396" s="13" t="n"/>
-      <c r="K396" s="9">
-        <f>IF(OR(E396&lt;&gt;"",I396&lt;&gt;""),"Занято",IF(AND(F395="Повторный приём (1 час)",A395=A396),"Занято","Свободно"))</f>
+      <c r="I396" s="11" t="n"/>
+      <c r="J396" s="9" t="n"/>
+      <c r="K396" s="13" t="n"/>
+      <c r="L396" s="9">
+        <f>IF(OR(E396&lt;&gt;"",J396&lt;&gt;""),"Занято",IF(AND(F395="Повторный приём (1 час)",A395=A396),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12499,10 +12900,11 @@
       <c r="F397" s="11" t="n"/>
       <c r="G397" s="12" t="n"/>
       <c r="H397" s="12" t="n"/>
-      <c r="I397" s="9" t="n"/>
-      <c r="J397" s="13" t="n"/>
-      <c r="K397" s="9">
-        <f>IF(OR(E397&lt;&gt;"",I397&lt;&gt;""),"Занято",IF(AND(F396="Повторный приём (1 час)",A396=A397),"Занято","Свободно"))</f>
+      <c r="I397" s="11" t="n"/>
+      <c r="J397" s="9" t="n"/>
+      <c r="K397" s="13" t="n"/>
+      <c r="L397" s="9">
+        <f>IF(OR(E397&lt;&gt;"",J397&lt;&gt;""),"Занято",IF(AND(F396="Повторный приём (1 час)",A396=A397),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12529,10 +12931,11 @@
       <c r="F398" s="11" t="n"/>
       <c r="G398" s="12" t="n"/>
       <c r="H398" s="12" t="n"/>
-      <c r="I398" s="9" t="n"/>
-      <c r="J398" s="13" t="n"/>
-      <c r="K398" s="9">
-        <f>IF(OR(E398&lt;&gt;"",I398&lt;&gt;""),"Занято",IF(AND(F397="Повторный приём (1 час)",A397=A398),"Занято","Свободно"))</f>
+      <c r="I398" s="11" t="n"/>
+      <c r="J398" s="9" t="n"/>
+      <c r="K398" s="13" t="n"/>
+      <c r="L398" s="9">
+        <f>IF(OR(E398&lt;&gt;"",J398&lt;&gt;""),"Занято",IF(AND(F397="Повторный приём (1 час)",A397=A398),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12559,10 +12962,11 @@
       <c r="F399" s="11" t="n"/>
       <c r="G399" s="12" t="n"/>
       <c r="H399" s="12" t="n"/>
-      <c r="I399" s="9" t="n"/>
-      <c r="J399" s="13" t="n"/>
-      <c r="K399" s="9">
-        <f>IF(OR(E399&lt;&gt;"",I399&lt;&gt;""),"Занято",IF(AND(F398="Повторный приём (1 час)",A398=A399),"Занято","Свободно"))</f>
+      <c r="I399" s="11" t="n"/>
+      <c r="J399" s="9" t="n"/>
+      <c r="K399" s="13" t="n"/>
+      <c r="L399" s="9">
+        <f>IF(OR(E399&lt;&gt;"",J399&lt;&gt;""),"Занято",IF(AND(F398="Повторный приём (1 час)",A398=A399),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12589,10 +12993,11 @@
       <c r="F400" s="11" t="n"/>
       <c r="G400" s="12" t="n"/>
       <c r="H400" s="12" t="n"/>
-      <c r="I400" s="9" t="n"/>
-      <c r="J400" s="13" t="n"/>
-      <c r="K400" s="9">
-        <f>IF(OR(E400&lt;&gt;"",I400&lt;&gt;""),"Занято",IF(AND(F399="Повторный приём (1 час)",A399=A400),"Занято","Свободно"))</f>
+      <c r="I400" s="11" t="n"/>
+      <c r="J400" s="9" t="n"/>
+      <c r="K400" s="13" t="n"/>
+      <c r="L400" s="9">
+        <f>IF(OR(E400&lt;&gt;"",J400&lt;&gt;""),"Занято",IF(AND(F399="Повторный приём (1 час)",A399=A400),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12619,10 +13024,11 @@
       <c r="F401" s="11" t="n"/>
       <c r="G401" s="12" t="n"/>
       <c r="H401" s="12" t="n"/>
-      <c r="I401" s="9" t="n"/>
-      <c r="J401" s="13" t="n"/>
-      <c r="K401" s="9">
-        <f>IF(OR(E401&lt;&gt;"",I401&lt;&gt;""),"Занято",IF(AND(F400="Повторный приём (1 час)",A400=A401),"Занято","Свободно"))</f>
+      <c r="I401" s="11" t="n"/>
+      <c r="J401" s="9" t="n"/>
+      <c r="K401" s="13" t="n"/>
+      <c r="L401" s="9">
+        <f>IF(OR(E401&lt;&gt;"",J401&lt;&gt;""),"Занято",IF(AND(F400="Повторный приём (1 час)",A400=A401),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12649,10 +13055,11 @@
       <c r="F402" s="11" t="n"/>
       <c r="G402" s="12" t="n"/>
       <c r="H402" s="12" t="n"/>
-      <c r="I402" s="9" t="n"/>
-      <c r="J402" s="13" t="n"/>
-      <c r="K402" s="9">
-        <f>IF(OR(E402&lt;&gt;"",I402&lt;&gt;""),"Занято",IF(AND(F401="Повторный приём (1 час)",A401=A402),"Занято","Свободно"))</f>
+      <c r="I402" s="11" t="n"/>
+      <c r="J402" s="9" t="n"/>
+      <c r="K402" s="13" t="n"/>
+      <c r="L402" s="9">
+        <f>IF(OR(E402&lt;&gt;"",J402&lt;&gt;""),"Занято",IF(AND(F401="Повторный приём (1 час)",A401=A402),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12679,10 +13086,11 @@
       <c r="F403" s="11" t="n"/>
       <c r="G403" s="12" t="n"/>
       <c r="H403" s="12" t="n"/>
-      <c r="I403" s="9" t="n"/>
-      <c r="J403" s="13" t="n"/>
-      <c r="K403" s="9">
-        <f>IF(OR(E403&lt;&gt;"",I403&lt;&gt;""),"Занято",IF(AND(F402="Повторный приём (1 час)",A402=A403),"Занято","Свободно"))</f>
+      <c r="I403" s="11" t="n"/>
+      <c r="J403" s="9" t="n"/>
+      <c r="K403" s="13" t="n"/>
+      <c r="L403" s="9">
+        <f>IF(OR(E403&lt;&gt;"",J403&lt;&gt;""),"Занято",IF(AND(F402="Повторный приём (1 час)",A402=A403),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12709,10 +13117,11 @@
       <c r="F404" s="11" t="n"/>
       <c r="G404" s="12" t="n"/>
       <c r="H404" s="12" t="n"/>
-      <c r="I404" s="9" t="n"/>
-      <c r="J404" s="13" t="n"/>
-      <c r="K404" s="9">
-        <f>IF(OR(E404&lt;&gt;"",I404&lt;&gt;""),"Занято",IF(AND(F403="Повторный приём (1 час)",A403=A404),"Занято","Свободно"))</f>
+      <c r="I404" s="11" t="n"/>
+      <c r="J404" s="9" t="n"/>
+      <c r="K404" s="13" t="n"/>
+      <c r="L404" s="9">
+        <f>IF(OR(E404&lt;&gt;"",J404&lt;&gt;""),"Занято",IF(AND(F403="Повторный приём (1 час)",A403=A404),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12739,10 +13148,11 @@
       <c r="F405" s="11" t="n"/>
       <c r="G405" s="12" t="n"/>
       <c r="H405" s="12" t="n"/>
-      <c r="I405" s="9" t="n"/>
-      <c r="J405" s="13" t="n"/>
-      <c r="K405" s="9">
-        <f>IF(OR(E405&lt;&gt;"",I405&lt;&gt;""),"Занято",IF(AND(F404="Повторный приём (1 час)",A404=A405),"Занято","Свободно"))</f>
+      <c r="I405" s="11" t="n"/>
+      <c r="J405" s="9" t="n"/>
+      <c r="K405" s="13" t="n"/>
+      <c r="L405" s="9">
+        <f>IF(OR(E405&lt;&gt;"",J405&lt;&gt;""),"Занято",IF(AND(F404="Повторный приём (1 час)",A404=A405),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12769,10 +13179,11 @@
       <c r="F406" s="11" t="n"/>
       <c r="G406" s="12" t="n"/>
       <c r="H406" s="12" t="n"/>
-      <c r="I406" s="9" t="n"/>
-      <c r="J406" s="13" t="n"/>
-      <c r="K406" s="9">
-        <f>IF(OR(E406&lt;&gt;"",I406&lt;&gt;""),"Занято",IF(AND(F405="Повторный приём (1 час)",A405=A406),"Занято","Свободно"))</f>
+      <c r="I406" s="11" t="n"/>
+      <c r="J406" s="9" t="n"/>
+      <c r="K406" s="13" t="n"/>
+      <c r="L406" s="9">
+        <f>IF(OR(E406&lt;&gt;"",J406&lt;&gt;""),"Занято",IF(AND(F405="Повторный приём (1 час)",A405=A406),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12799,10 +13210,11 @@
       <c r="F407" s="11" t="n"/>
       <c r="G407" s="12" t="n"/>
       <c r="H407" s="12" t="n"/>
-      <c r="I407" s="9" t="n"/>
-      <c r="J407" s="13" t="n"/>
-      <c r="K407" s="9">
-        <f>IF(OR(E407&lt;&gt;"",I407&lt;&gt;""),"Занято",IF(AND(F406="Повторный приём (1 час)",A406=A407),"Занято","Свободно"))</f>
+      <c r="I407" s="11" t="n"/>
+      <c r="J407" s="9" t="n"/>
+      <c r="K407" s="13" t="n"/>
+      <c r="L407" s="9">
+        <f>IF(OR(E407&lt;&gt;"",J407&lt;&gt;""),"Занято",IF(AND(F406="Повторный приём (1 час)",A406=A407),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12829,10 +13241,11 @@
       <c r="F408" s="11" t="n"/>
       <c r="G408" s="12" t="n"/>
       <c r="H408" s="12" t="n"/>
-      <c r="I408" s="9" t="n"/>
-      <c r="J408" s="13" t="n"/>
-      <c r="K408" s="9">
-        <f>IF(OR(E408&lt;&gt;"",I408&lt;&gt;""),"Занято",IF(AND(F407="Повторный приём (1 час)",A407=A408),"Занято","Свободно"))</f>
+      <c r="I408" s="11" t="n"/>
+      <c r="J408" s="9" t="n"/>
+      <c r="K408" s="13" t="n"/>
+      <c r="L408" s="9">
+        <f>IF(OR(E408&lt;&gt;"",J408&lt;&gt;""),"Занято",IF(AND(F407="Повторный приём (1 час)",A407=A408),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12859,10 +13272,11 @@
       <c r="F409" s="11" t="n"/>
       <c r="G409" s="12" t="n"/>
       <c r="H409" s="12" t="n"/>
-      <c r="I409" s="9" t="n"/>
-      <c r="J409" s="13" t="n"/>
-      <c r="K409" s="9">
-        <f>IF(OR(E409&lt;&gt;"",I409&lt;&gt;""),"Занято",IF(AND(F408="Повторный приём (1 час)",A408=A409),"Занято","Свободно"))</f>
+      <c r="I409" s="11" t="n"/>
+      <c r="J409" s="9" t="n"/>
+      <c r="K409" s="13" t="n"/>
+      <c r="L409" s="9">
+        <f>IF(OR(E409&lt;&gt;"",J409&lt;&gt;""),"Занято",IF(AND(F408="Повторный приём (1 час)",A408=A409),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12889,10 +13303,11 @@
       <c r="F410" s="11" t="n"/>
       <c r="G410" s="12" t="n"/>
       <c r="H410" s="12" t="n"/>
-      <c r="I410" s="9" t="n"/>
-      <c r="J410" s="13" t="n"/>
-      <c r="K410" s="9">
-        <f>IF(OR(E410&lt;&gt;"",I410&lt;&gt;""),"Занято",IF(AND(F409="Повторный приём (1 час)",A409=A410),"Занято","Свободно"))</f>
+      <c r="I410" s="11" t="n"/>
+      <c r="J410" s="9" t="n"/>
+      <c r="K410" s="13" t="n"/>
+      <c r="L410" s="9">
+        <f>IF(OR(E410&lt;&gt;"",J410&lt;&gt;""),"Занято",IF(AND(F409="Повторный приём (1 час)",A409=A410),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12919,10 +13334,11 @@
       <c r="F411" s="11" t="n"/>
       <c r="G411" s="12" t="n"/>
       <c r="H411" s="12" t="n"/>
-      <c r="I411" s="9" t="n"/>
-      <c r="J411" s="13" t="n"/>
-      <c r="K411" s="9">
-        <f>IF(OR(E411&lt;&gt;"",I411&lt;&gt;""),"Занято",IF(AND(F410="Повторный приём (1 час)",A410=A411),"Занято","Свободно"))</f>
+      <c r="I411" s="11" t="n"/>
+      <c r="J411" s="9" t="n"/>
+      <c r="K411" s="13" t="n"/>
+      <c r="L411" s="9">
+        <f>IF(OR(E411&lt;&gt;"",J411&lt;&gt;""),"Занято",IF(AND(F410="Повторный приём (1 час)",A410=A411),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12949,10 +13365,11 @@
       <c r="F412" s="17" t="n"/>
       <c r="G412" s="18" t="n"/>
       <c r="H412" s="18" t="n"/>
-      <c r="I412" s="15" t="n"/>
-      <c r="J412" s="19" t="n"/>
-      <c r="K412" s="15">
-        <f>IF(OR(E412&lt;&gt;"",I412&lt;&gt;""),"Занято",IF(AND(F411="Повторный приём (1 час)",A411=A412),"Занято","Свободно"))</f>
+      <c r="I412" s="17" t="n"/>
+      <c r="J412" s="15" t="n"/>
+      <c r="K412" s="19" t="n"/>
+      <c r="L412" s="15">
+        <f>IF(OR(E412&lt;&gt;"",J412&lt;&gt;""),"Занято",IF(AND(F411="Повторный приём (1 час)",A411=A412),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -12979,10 +13396,11 @@
       <c r="F413" s="23" t="n"/>
       <c r="G413" s="24" t="n"/>
       <c r="H413" s="24" t="n"/>
-      <c r="I413" s="21" t="n"/>
-      <c r="J413" s="25" t="n"/>
-      <c r="K413" s="21">
-        <f>IF(OR(E413&lt;&gt;"",I413&lt;&gt;""),"Занято",IF(AND(F412="Повторный приём (1 час)",A412=A413),"Занято","Свободно"))</f>
+      <c r="I413" s="23" t="n"/>
+      <c r="J413" s="21" t="n"/>
+      <c r="K413" s="25" t="n"/>
+      <c r="L413" s="21">
+        <f>IF(OR(E413&lt;&gt;"",J413&lt;&gt;""),"Занято",IF(AND(F412="Повторный приём (1 час)",A412=A413),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13009,10 +13427,11 @@
       <c r="F414" s="23" t="n"/>
       <c r="G414" s="24" t="n"/>
       <c r="H414" s="24" t="n"/>
-      <c r="I414" s="21" t="n"/>
-      <c r="J414" s="25" t="n"/>
-      <c r="K414" s="21">
-        <f>IF(OR(E414&lt;&gt;"",I414&lt;&gt;""),"Занято",IF(AND(F413="Повторный приём (1 час)",A413=A414),"Занято","Свободно"))</f>
+      <c r="I414" s="23" t="n"/>
+      <c r="J414" s="21" t="n"/>
+      <c r="K414" s="25" t="n"/>
+      <c r="L414" s="21">
+        <f>IF(OR(E414&lt;&gt;"",J414&lt;&gt;""),"Занято",IF(AND(F413="Повторный приём (1 час)",A413=A414),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13039,10 +13458,11 @@
       <c r="F415" s="23" t="n"/>
       <c r="G415" s="24" t="n"/>
       <c r="H415" s="24" t="n"/>
-      <c r="I415" s="21" t="n"/>
-      <c r="J415" s="25" t="n"/>
-      <c r="K415" s="21">
-        <f>IF(OR(E415&lt;&gt;"",I415&lt;&gt;""),"Занято",IF(AND(F414="Повторный приём (1 час)",A414=A415),"Занято","Свободно"))</f>
+      <c r="I415" s="23" t="n"/>
+      <c r="J415" s="21" t="n"/>
+      <c r="K415" s="25" t="n"/>
+      <c r="L415" s="21">
+        <f>IF(OR(E415&lt;&gt;"",J415&lt;&gt;""),"Занято",IF(AND(F414="Повторный приём (1 час)",A414=A415),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13069,10 +13489,11 @@
       <c r="F416" s="23" t="n"/>
       <c r="G416" s="24" t="n"/>
       <c r="H416" s="24" t="n"/>
-      <c r="I416" s="21" t="n"/>
-      <c r="J416" s="25" t="n"/>
-      <c r="K416" s="21">
-        <f>IF(OR(E416&lt;&gt;"",I416&lt;&gt;""),"Занято",IF(AND(F415="Повторный приём (1 час)",A415=A416),"Занято","Свободно"))</f>
+      <c r="I416" s="23" t="n"/>
+      <c r="J416" s="21" t="n"/>
+      <c r="K416" s="25" t="n"/>
+      <c r="L416" s="21">
+        <f>IF(OR(E416&lt;&gt;"",J416&lt;&gt;""),"Занято",IF(AND(F415="Повторный приём (1 час)",A415=A416),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13099,10 +13520,11 @@
       <c r="F417" s="23" t="n"/>
       <c r="G417" s="24" t="n"/>
       <c r="H417" s="24" t="n"/>
-      <c r="I417" s="21" t="n"/>
-      <c r="J417" s="25" t="n"/>
-      <c r="K417" s="21">
-        <f>IF(OR(E417&lt;&gt;"",I417&lt;&gt;""),"Занято",IF(AND(F416="Повторный приём (1 час)",A416=A417),"Занято","Свободно"))</f>
+      <c r="I417" s="23" t="n"/>
+      <c r="J417" s="21" t="n"/>
+      <c r="K417" s="25" t="n"/>
+      <c r="L417" s="21">
+        <f>IF(OR(E417&lt;&gt;"",J417&lt;&gt;""),"Занято",IF(AND(F416="Повторный приём (1 час)",A416=A417),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13129,10 +13551,11 @@
       <c r="F418" s="23" t="n"/>
       <c r="G418" s="24" t="n"/>
       <c r="H418" s="24" t="n"/>
-      <c r="I418" s="21" t="n"/>
-      <c r="J418" s="25" t="n"/>
-      <c r="K418" s="21">
-        <f>IF(OR(E418&lt;&gt;"",I418&lt;&gt;""),"Занято",IF(AND(F417="Повторный приём (1 час)",A417=A418),"Занято","Свободно"))</f>
+      <c r="I418" s="23" t="n"/>
+      <c r="J418" s="21" t="n"/>
+      <c r="K418" s="25" t="n"/>
+      <c r="L418" s="21">
+        <f>IF(OR(E418&lt;&gt;"",J418&lt;&gt;""),"Занято",IF(AND(F417="Повторный приём (1 час)",A417=A418),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13159,10 +13582,11 @@
       <c r="F419" s="23" t="n"/>
       <c r="G419" s="24" t="n"/>
       <c r="H419" s="24" t="n"/>
-      <c r="I419" s="21" t="n"/>
-      <c r="J419" s="25" t="n"/>
-      <c r="K419" s="21">
-        <f>IF(OR(E419&lt;&gt;"",I419&lt;&gt;""),"Занято",IF(AND(F418="Повторный приём (1 час)",A418=A419),"Занято","Свободно"))</f>
+      <c r="I419" s="23" t="n"/>
+      <c r="J419" s="21" t="n"/>
+      <c r="K419" s="25" t="n"/>
+      <c r="L419" s="21">
+        <f>IF(OR(E419&lt;&gt;"",J419&lt;&gt;""),"Занято",IF(AND(F418="Повторный приём (1 час)",A418=A419),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13189,10 +13613,11 @@
       <c r="F420" s="23" t="n"/>
       <c r="G420" s="24" t="n"/>
       <c r="H420" s="24" t="n"/>
-      <c r="I420" s="21" t="n"/>
-      <c r="J420" s="25" t="n"/>
-      <c r="K420" s="21">
-        <f>IF(OR(E420&lt;&gt;"",I420&lt;&gt;""),"Занято",IF(AND(F419="Повторный приём (1 час)",A419=A420),"Занято","Свободно"))</f>
+      <c r="I420" s="23" t="n"/>
+      <c r="J420" s="21" t="n"/>
+      <c r="K420" s="25" t="n"/>
+      <c r="L420" s="21">
+        <f>IF(OR(E420&lt;&gt;"",J420&lt;&gt;""),"Занято",IF(AND(F419="Повторный приём (1 час)",A419=A420),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13219,10 +13644,11 @@
       <c r="F421" s="23" t="n"/>
       <c r="G421" s="24" t="n"/>
       <c r="H421" s="24" t="n"/>
-      <c r="I421" s="21" t="n"/>
-      <c r="J421" s="25" t="n"/>
-      <c r="K421" s="21">
-        <f>IF(OR(E421&lt;&gt;"",I421&lt;&gt;""),"Занято",IF(AND(F420="Повторный приём (1 час)",A420=A421),"Занято","Свободно"))</f>
+      <c r="I421" s="23" t="n"/>
+      <c r="J421" s="21" t="n"/>
+      <c r="K421" s="25" t="n"/>
+      <c r="L421" s="21">
+        <f>IF(OR(E421&lt;&gt;"",J421&lt;&gt;""),"Занято",IF(AND(F420="Повторный приём (1 час)",A420=A421),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13249,10 +13675,11 @@
       <c r="F422" s="23" t="n"/>
       <c r="G422" s="24" t="n"/>
       <c r="H422" s="24" t="n"/>
-      <c r="I422" s="21" t="n"/>
-      <c r="J422" s="25" t="n"/>
-      <c r="K422" s="21">
-        <f>IF(OR(E422&lt;&gt;"",I422&lt;&gt;""),"Занято",IF(AND(F421="Повторный приём (1 час)",A421=A422),"Занято","Свободно"))</f>
+      <c r="I422" s="23" t="n"/>
+      <c r="J422" s="21" t="n"/>
+      <c r="K422" s="25" t="n"/>
+      <c r="L422" s="21">
+        <f>IF(OR(E422&lt;&gt;"",J422&lt;&gt;""),"Занято",IF(AND(F421="Повторный приём (1 час)",A421=A422),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13279,10 +13706,11 @@
       <c r="F423" s="23" t="n"/>
       <c r="G423" s="24" t="n"/>
       <c r="H423" s="24" t="n"/>
-      <c r="I423" s="21" t="n"/>
-      <c r="J423" s="25" t="n"/>
-      <c r="K423" s="21">
-        <f>IF(OR(E423&lt;&gt;"",I423&lt;&gt;""),"Занято",IF(AND(F422="Повторный приём (1 час)",A422=A423),"Занято","Свободно"))</f>
+      <c r="I423" s="23" t="n"/>
+      <c r="J423" s="21" t="n"/>
+      <c r="K423" s="25" t="n"/>
+      <c r="L423" s="21">
+        <f>IF(OR(E423&lt;&gt;"",J423&lt;&gt;""),"Занято",IF(AND(F422="Повторный приём (1 час)",A422=A423),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13309,10 +13737,11 @@
       <c r="F424" s="23" t="n"/>
       <c r="G424" s="24" t="n"/>
       <c r="H424" s="24" t="n"/>
-      <c r="I424" s="21" t="n"/>
-      <c r="J424" s="25" t="n"/>
-      <c r="K424" s="21">
-        <f>IF(OR(E424&lt;&gt;"",I424&lt;&gt;""),"Занято",IF(AND(F423="Повторный приём (1 час)",A423=A424),"Занято","Свободно"))</f>
+      <c r="I424" s="23" t="n"/>
+      <c r="J424" s="21" t="n"/>
+      <c r="K424" s="25" t="n"/>
+      <c r="L424" s="21">
+        <f>IF(OR(E424&lt;&gt;"",J424&lt;&gt;""),"Занято",IF(AND(F423="Повторный приём (1 час)",A423=A424),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13339,10 +13768,11 @@
       <c r="F425" s="23" t="n"/>
       <c r="G425" s="24" t="n"/>
       <c r="H425" s="24" t="n"/>
-      <c r="I425" s="21" t="n"/>
-      <c r="J425" s="25" t="n"/>
-      <c r="K425" s="21">
-        <f>IF(OR(E425&lt;&gt;"",I425&lt;&gt;""),"Занято",IF(AND(F424="Повторный приём (1 час)",A424=A425),"Занято","Свободно"))</f>
+      <c r="I425" s="23" t="n"/>
+      <c r="J425" s="21" t="n"/>
+      <c r="K425" s="25" t="n"/>
+      <c r="L425" s="21">
+        <f>IF(OR(E425&lt;&gt;"",J425&lt;&gt;""),"Занято",IF(AND(F424="Повторный приём (1 час)",A424=A425),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13369,10 +13799,11 @@
       <c r="F426" s="23" t="n"/>
       <c r="G426" s="24" t="n"/>
       <c r="H426" s="24" t="n"/>
-      <c r="I426" s="21" t="n"/>
-      <c r="J426" s="25" t="n"/>
-      <c r="K426" s="21">
-        <f>IF(OR(E426&lt;&gt;"",I426&lt;&gt;""),"Занято",IF(AND(F425="Повторный приём (1 час)",A425=A426),"Занято","Свободно"))</f>
+      <c r="I426" s="23" t="n"/>
+      <c r="J426" s="21" t="n"/>
+      <c r="K426" s="25" t="n"/>
+      <c r="L426" s="21">
+        <f>IF(OR(E426&lt;&gt;"",J426&lt;&gt;""),"Занято",IF(AND(F425="Повторный приём (1 час)",A425=A426),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13399,10 +13830,11 @@
       <c r="F427" s="23" t="n"/>
       <c r="G427" s="24" t="n"/>
       <c r="H427" s="24" t="n"/>
-      <c r="I427" s="21" t="n"/>
-      <c r="J427" s="25" t="n"/>
-      <c r="K427" s="21">
-        <f>IF(OR(E427&lt;&gt;"",I427&lt;&gt;""),"Занято",IF(AND(F426="Повторный приём (1 час)",A426=A427),"Занято","Свободно"))</f>
+      <c r="I427" s="23" t="n"/>
+      <c r="J427" s="21" t="n"/>
+      <c r="K427" s="25" t="n"/>
+      <c r="L427" s="21">
+        <f>IF(OR(E427&lt;&gt;"",J427&lt;&gt;""),"Занято",IF(AND(F426="Повторный приём (1 час)",A426=A427),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13429,10 +13861,11 @@
       <c r="F428" s="23" t="n"/>
       <c r="G428" s="24" t="n"/>
       <c r="H428" s="24" t="n"/>
-      <c r="I428" s="21" t="n"/>
-      <c r="J428" s="25" t="n"/>
-      <c r="K428" s="21">
-        <f>IF(OR(E428&lt;&gt;"",I428&lt;&gt;""),"Занято",IF(AND(F427="Повторный приём (1 час)",A427=A428),"Занято","Свободно"))</f>
+      <c r="I428" s="23" t="n"/>
+      <c r="J428" s="21" t="n"/>
+      <c r="K428" s="25" t="n"/>
+      <c r="L428" s="21">
+        <f>IF(OR(E428&lt;&gt;"",J428&lt;&gt;""),"Занято",IF(AND(F427="Повторный приём (1 час)",A427=A428),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13459,10 +13892,11 @@
       <c r="F429" s="23" t="n"/>
       <c r="G429" s="24" t="n"/>
       <c r="H429" s="24" t="n"/>
-      <c r="I429" s="21" t="n"/>
-      <c r="J429" s="25" t="n"/>
-      <c r="K429" s="21">
-        <f>IF(OR(E429&lt;&gt;"",I429&lt;&gt;""),"Занято",IF(AND(F428="Повторный приём (1 час)",A428=A429),"Занято","Свободно"))</f>
+      <c r="I429" s="23" t="n"/>
+      <c r="J429" s="21" t="n"/>
+      <c r="K429" s="25" t="n"/>
+      <c r="L429" s="21">
+        <f>IF(OR(E429&lt;&gt;"",J429&lt;&gt;""),"Занято",IF(AND(F428="Повторный приём (1 час)",A428=A429),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13489,10 +13923,11 @@
       <c r="F430" s="5" t="n"/>
       <c r="G430" s="6" t="n"/>
       <c r="H430" s="6" t="n"/>
-      <c r="I430" s="3" t="n"/>
-      <c r="J430" s="7" t="n"/>
-      <c r="K430" s="3">
-        <f>IF(OR(E430&lt;&gt;"",I430&lt;&gt;""),"Занято",IF(AND(F429="Повторный приём (1 час)",A429=A430),"Занято","Свободно"))</f>
+      <c r="I430" s="5" t="n"/>
+      <c r="J430" s="3" t="n"/>
+      <c r="K430" s="7" t="n"/>
+      <c r="L430" s="3">
+        <f>IF(OR(E430&lt;&gt;"",J430&lt;&gt;""),"Занято",IF(AND(F429="Повторный приём (1 час)",A429=A430),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13519,10 +13954,11 @@
       <c r="F431" s="11" t="n"/>
       <c r="G431" s="12" t="n"/>
       <c r="H431" s="12" t="n"/>
-      <c r="I431" s="9" t="n"/>
-      <c r="J431" s="13" t="n"/>
-      <c r="K431" s="9">
-        <f>IF(OR(E431&lt;&gt;"",I431&lt;&gt;""),"Занято",IF(AND(F430="Повторный приём (1 час)",A430=A431),"Занято","Свободно"))</f>
+      <c r="I431" s="11" t="n"/>
+      <c r="J431" s="9" t="n"/>
+      <c r="K431" s="13" t="n"/>
+      <c r="L431" s="9">
+        <f>IF(OR(E431&lt;&gt;"",J431&lt;&gt;""),"Занято",IF(AND(F430="Повторный приём (1 час)",A430=A431),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13549,10 +13985,11 @@
       <c r="F432" s="11" t="n"/>
       <c r="G432" s="12" t="n"/>
       <c r="H432" s="12" t="n"/>
-      <c r="I432" s="9" t="n"/>
-      <c r="J432" s="13" t="n"/>
-      <c r="K432" s="9">
-        <f>IF(OR(E432&lt;&gt;"",I432&lt;&gt;""),"Занято",IF(AND(F431="Повторный приём (1 час)",A431=A432),"Занято","Свободно"))</f>
+      <c r="I432" s="11" t="n"/>
+      <c r="J432" s="9" t="n"/>
+      <c r="K432" s="13" t="n"/>
+      <c r="L432" s="9">
+        <f>IF(OR(E432&lt;&gt;"",J432&lt;&gt;""),"Занято",IF(AND(F431="Повторный приём (1 час)",A431=A432),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13579,10 +14016,11 @@
       <c r="F433" s="11" t="n"/>
       <c r="G433" s="12" t="n"/>
       <c r="H433" s="12" t="n"/>
-      <c r="I433" s="9" t="n"/>
-      <c r="J433" s="13" t="n"/>
-      <c r="K433" s="9">
-        <f>IF(OR(E433&lt;&gt;"",I433&lt;&gt;""),"Занято",IF(AND(F432="Повторный приём (1 час)",A432=A433),"Занято","Свободно"))</f>
+      <c r="I433" s="11" t="n"/>
+      <c r="J433" s="9" t="n"/>
+      <c r="K433" s="13" t="n"/>
+      <c r="L433" s="9">
+        <f>IF(OR(E433&lt;&gt;"",J433&lt;&gt;""),"Занято",IF(AND(F432="Повторный приём (1 час)",A432=A433),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13609,10 +14047,11 @@
       <c r="F434" s="11" t="n"/>
       <c r="G434" s="12" t="n"/>
       <c r="H434" s="12" t="n"/>
-      <c r="I434" s="9" t="n"/>
-      <c r="J434" s="13" t="n"/>
-      <c r="K434" s="9">
-        <f>IF(OR(E434&lt;&gt;"",I434&lt;&gt;""),"Занято",IF(AND(F433="Повторный приём (1 час)",A433=A434),"Занято","Свободно"))</f>
+      <c r="I434" s="11" t="n"/>
+      <c r="J434" s="9" t="n"/>
+      <c r="K434" s="13" t="n"/>
+      <c r="L434" s="9">
+        <f>IF(OR(E434&lt;&gt;"",J434&lt;&gt;""),"Занято",IF(AND(F433="Повторный приём (1 час)",A433=A434),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13639,10 +14078,11 @@
       <c r="F435" s="11" t="n"/>
       <c r="G435" s="12" t="n"/>
       <c r="H435" s="12" t="n"/>
-      <c r="I435" s="9" t="n"/>
-      <c r="J435" s="13" t="n"/>
-      <c r="K435" s="9">
-        <f>IF(OR(E435&lt;&gt;"",I435&lt;&gt;""),"Занято",IF(AND(F434="Повторный приём (1 час)",A434=A435),"Занято","Свободно"))</f>
+      <c r="I435" s="11" t="n"/>
+      <c r="J435" s="9" t="n"/>
+      <c r="K435" s="13" t="n"/>
+      <c r="L435" s="9">
+        <f>IF(OR(E435&lt;&gt;"",J435&lt;&gt;""),"Занято",IF(AND(F434="Повторный приём (1 час)",A434=A435),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13669,10 +14109,11 @@
       <c r="F436" s="11" t="n"/>
       <c r="G436" s="12" t="n"/>
       <c r="H436" s="12" t="n"/>
-      <c r="I436" s="9" t="n"/>
-      <c r="J436" s="13" t="n"/>
-      <c r="K436" s="9">
-        <f>IF(OR(E436&lt;&gt;"",I436&lt;&gt;""),"Занято",IF(AND(F435="Повторный приём (1 час)",A435=A436),"Занято","Свободно"))</f>
+      <c r="I436" s="11" t="n"/>
+      <c r="J436" s="9" t="n"/>
+      <c r="K436" s="13" t="n"/>
+      <c r="L436" s="9">
+        <f>IF(OR(E436&lt;&gt;"",J436&lt;&gt;""),"Занято",IF(AND(F435="Повторный приём (1 час)",A435=A436),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
@@ -13699,29 +14140,33 @@
       <c r="F437" s="11" t="n"/>
       <c r="G437" s="12" t="n"/>
       <c r="H437" s="12" t="n"/>
-      <c r="I437" s="9" t="n"/>
-      <c r="J437" s="13" t="n"/>
-      <c r="K437" s="9">
-        <f>IF(OR(E437&lt;&gt;"",I437&lt;&gt;""),"Занято",IF(AND(F436="Повторный приём (1 час)",A436=A437),"Занято","Свободно"))</f>
+      <c r="I437" s="11" t="n"/>
+      <c r="J437" s="9" t="n"/>
+      <c r="K437" s="13" t="n"/>
+      <c r="L437" s="9">
+        <f>IF(OR(E437&lt;&gt;"",J437&lt;&gt;""),"Занято",IF(AND(F436="Повторный приём (1 час)",A436=A437),"Занято","Свободно"))</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K437"/>
-  <conditionalFormatting sqref="K2:K437">
+  <autoFilter ref="A1:L437"/>
+  <conditionalFormatting sqref="L2:L437">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$K2="Занято"</formula>
+      <formula>$L2="Занято"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>$K2="Свободно"</formula>
+      <formula>$L2="Свободно"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation sqref="F2:F437" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Первичная диагностика ЖКТ,Повторный приём (1 час)"</formula1>
     </dataValidation>
+    <dataValidation sqref="J2:J437" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Бронь,Записан"</formula1>
+    </dataValidation>
     <dataValidation sqref="I2:I437" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Бронь,Записан"</formula1>
+      <formula1>"Instagram — платная реклама,Instagram — бесплатно,Facebook — платная реклама,Facebook — бесплатно,2ГИС,Рекомендация,Другое,Не указан"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13734,7 +14179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -13748,6 +14193,7 @@
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="16" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13766,6 +14212,7 @@
       <c r="I1" s="27" t="n"/>
       <c r="J1" s="27" t="n"/>
       <c r="K1" s="27" t="n"/>
+      <c r="L1" s="27" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="27" t="n"/>
@@ -13779,6 +14226,7 @@
       <c r="I2" s="27" t="n"/>
       <c r="J2" s="27" t="n"/>
       <c r="K2" s="27" t="n"/>
+      <c r="L2" s="27" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="28" t="inlineStr">
@@ -13800,6 +14248,7 @@
       <c r="I3" s="27" t="n"/>
       <c r="J3" s="27" t="n"/>
       <c r="K3" s="27" t="n"/>
+      <c r="L3" s="27" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="28" t="inlineStr">
@@ -13809,7 +14258,7 @@
       </c>
       <c r="B4" s="27" t="inlineStr">
         <is>
-          <t>ФИО, Процедура, ИИН, Телефон, Статус записи и Создано. Второго клиента на занятое время бот не запишет.</t>
+          <t>ФИО, Процедура, ИИН, Телефон, Источник, Статус записи и Создано. Второго клиента на занятое время бот не запишет.</t>
         </is>
       </c>
       <c r="C4" s="27" t="n"/>
@@ -13821,16 +14270,17 @@
       <c r="I4" s="27" t="n"/>
       <c r="J4" s="27" t="n"/>
       <c r="K4" s="27" t="n"/>
+      <c r="L4" s="27" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="28" t="inlineStr">
         <is>
-          <t>Статус записи</t>
+          <t>Источник</t>
         </is>
       </c>
       <c r="B5" s="27" t="inlineStr">
         <is>
-          <t>«Бронь» — клиент выбрал время и оплачивает (держится 60 минут); «Записан» — оплата получена.</t>
+          <t>Откуда пришёл клиент. Платная реклама — только если клиент пришёл с рекламного объявления (данные платформы) или сам говорит, что увидел рекламу. «Я с Инстаграм / с Фейсбука» без упоминания рекламы — бесплатно.</t>
         </is>
       </c>
       <c r="C5" s="27" t="n"/>
@@ -13842,16 +14292,17 @@
       <c r="I5" s="27" t="n"/>
       <c r="J5" s="27" t="n"/>
       <c r="K5" s="27" t="n"/>
+      <c r="L5" s="27" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="28" t="inlineStr">
         <is>
-          <t>Не трогать</t>
+          <t>Статус записи</t>
         </is>
       </c>
       <c r="B6" s="27" t="inlineStr">
         <is>
-          <t>Дата, День недели, Начало, Окончание и Статус слота (считается сам: «Свободно» / «Занято»).</t>
+          <t>«Бронь» — клиент выбрал время и оплачивает (держится 60 минут); «Записан» — оплата получена.</t>
         </is>
       </c>
       <c r="C6" s="27" t="n"/>
@@ -13863,16 +14314,17 @@
       <c r="I6" s="27" t="n"/>
       <c r="J6" s="27" t="n"/>
       <c r="K6" s="27" t="n"/>
+      <c r="L6" s="27" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="28" t="inlineStr">
         <is>
-          <t>Первичная диагностика</t>
+          <t>Не трогать</t>
         </is>
       </c>
       <c r="B7" s="27" t="inlineStr">
         <is>
-          <t>1 слот (30 минут). Записывает бот.</t>
+          <t>Дата, День недели, Начало, Окончание и Статус слота (считается сам: «Свободно» / «Занято»).</t>
         </is>
       </c>
       <c r="C7" s="27" t="n"/>
@@ -13884,16 +14336,17 @@
       <c r="I7" s="27" t="n"/>
       <c r="J7" s="27" t="n"/>
       <c r="K7" s="27" t="n"/>
+      <c r="L7" s="27" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="28" t="inlineStr">
         <is>
-          <t>Повторный приём</t>
+          <t>Первичная диагностика</t>
         </is>
       </c>
       <c r="B8" s="27" t="inlineStr">
         <is>
-          <t>1 час: выберите «Повторный приём (1 час)» в первом слоте — следующий слот станет «Занято» сам. Записывает администратор.</t>
+          <t>1 слот (30 минут). Записывает бот.</t>
         </is>
       </c>
       <c r="C8" s="27" t="n"/>
@@ -13905,10 +14358,19 @@
       <c r="I8" s="27" t="n"/>
       <c r="J8" s="27" t="n"/>
       <c r="K8" s="27" t="n"/>
+      <c r="L8" s="27" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="27" t="n"/>
-      <c r="B9" s="27" t="n"/>
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Повторный приём</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>1 час: выберите «Повторный приём (1 час)» в первом слоте — следующий слот станет «Занято» сам. Записывает администратор.</t>
+        </is>
+      </c>
       <c r="C9" s="27" t="n"/>
       <c r="D9" s="27" t="n"/>
       <c r="E9" s="27" t="n"/>
@@ -13918,13 +14380,10 @@
       <c r="I9" s="27" t="n"/>
       <c r="J9" s="27" t="n"/>
       <c r="K9" s="27" t="n"/>
+      <c r="L9" s="27" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="28" t="inlineStr">
-        <is>
-          <t>Пример строки:</t>
-        </is>
-      </c>
+      <c r="A10" s="27" t="n"/>
       <c r="B10" s="27" t="n"/>
       <c r="C10" s="27" t="n"/>
       <c r="D10" s="27" t="n"/>
@@ -13935,116 +14394,145 @@
       <c r="I10" s="27" t="n"/>
       <c r="J10" s="27" t="n"/>
       <c r="K10" s="27" t="n"/>
+      <c r="L10" s="27" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="28" t="inlineStr">
         <is>
+          <t>Пример строки:</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="n"/>
+      <c r="C11" s="27" t="n"/>
+      <c r="D11" s="27" t="n"/>
+      <c r="E11" s="27" t="n"/>
+      <c r="F11" s="27" t="n"/>
+      <c r="G11" s="27" t="n"/>
+      <c r="H11" s="27" t="n"/>
+      <c r="I11" s="27" t="n"/>
+      <c r="J11" s="27" t="n"/>
+      <c r="K11" s="27" t="n"/>
+      <c r="L11" s="27" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="B11" s="28" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>День недели</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C12" s="28" t="inlineStr">
         <is>
           <t>Начало</t>
         </is>
       </c>
-      <c r="D11" s="28" t="inlineStr">
+      <c r="D12" s="28" t="inlineStr">
         <is>
           <t>Окончание</t>
         </is>
       </c>
-      <c r="E11" s="28" t="inlineStr">
+      <c r="E12" s="28" t="inlineStr">
         <is>
           <t>ФИО</t>
         </is>
       </c>
-      <c r="F11" s="28" t="inlineStr">
+      <c r="F12" s="28" t="inlineStr">
         <is>
           <t>Процедура</t>
         </is>
       </c>
-      <c r="G11" s="28" t="inlineStr">
+      <c r="G12" s="28" t="inlineStr">
         <is>
           <t>ИИН</t>
         </is>
       </c>
-      <c r="H11" s="28" t="inlineStr">
+      <c r="H12" s="28" t="inlineStr">
         <is>
           <t>Телефон</t>
         </is>
       </c>
-      <c r="I11" s="28" t="inlineStr">
+      <c r="I12" s="28" t="inlineStr">
+        <is>
+          <t>Источник</t>
+        </is>
+      </c>
+      <c r="J12" s="28" t="inlineStr">
         <is>
           <t>Статус записи</t>
         </is>
       </c>
-      <c r="J11" s="28" t="inlineStr">
+      <c r="K12" s="28" t="inlineStr">
         <is>
           <t>Создано</t>
         </is>
       </c>
-      <c r="K11" s="28" t="inlineStr">
+      <c r="L12" s="28" t="inlineStr">
         <is>
           <t>Статус слота</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>10.10.2026</t>
         </is>
       </c>
-      <c r="B12" s="27" t="inlineStr">
+      <c r="B13" s="27" t="inlineStr">
         <is>
           <t>Суббота</t>
         </is>
       </c>
-      <c r="C12" s="27" t="inlineStr">
+      <c r="C13" s="27" t="inlineStr">
         <is>
           <t>12:30</t>
         </is>
       </c>
-      <c r="D12" s="27" t="inlineStr">
+      <c r="D13" s="27" t="inlineStr">
         <is>
           <t>13:00</t>
         </is>
       </c>
-      <c r="E12" s="27" t="inlineStr">
+      <c r="E13" s="27" t="inlineStr">
         <is>
           <t>Пономарева Наталья Сергеевна</t>
         </is>
       </c>
-      <c r="F12" s="27" t="inlineStr">
+      <c r="F13" s="27" t="inlineStr">
         <is>
           <t>Первичная диагностика ЖКТ</t>
         </is>
       </c>
-      <c r="G12" s="27" t="inlineStr">
+      <c r="G13" s="27" t="inlineStr">
         <is>
           <t>123456789012</t>
         </is>
       </c>
-      <c r="H12" s="27" t="inlineStr">
+      <c r="H13" s="27" t="inlineStr">
         <is>
           <t>77770000000</t>
         </is>
       </c>
-      <c r="I12" s="27" t="inlineStr">
+      <c r="I13" s="27" t="inlineStr">
+        <is>
+          <t>Instagram — платная реклама</t>
+        </is>
+      </c>
+      <c r="J13" s="27" t="inlineStr">
         <is>
           <t>Записан</t>
         </is>
       </c>
-      <c r="J12" s="27" t="inlineStr">
+      <c r="K13" s="27" t="inlineStr">
         <is>
           <t>10.10.2026 10:15</t>
         </is>
       </c>
-      <c r="K12" s="27" t="inlineStr">
+      <c r="L13" s="27" t="inlineStr">
         <is>
           <t>Занято</t>
         </is>
